--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685843</v>
+        <v>128685790</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810858</v>
+        <v>810977</v>
       </c>
       <c r="R2" t="n">
-        <v>7392973</v>
+        <v>7393016</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685837</v>
+        <v>128685783</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810756</v>
+        <v>811497</v>
       </c>
       <c r="R3" t="n">
-        <v>7393036</v>
+        <v>7393112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685756</v>
+        <v>128685843</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811013</v>
+        <v>810858</v>
       </c>
       <c r="R4" t="n">
-        <v>7393006</v>
+        <v>7392973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685790</v>
+        <v>128685837</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810977</v>
+        <v>810756</v>
       </c>
       <c r="R5" t="n">
-        <v>7393016</v>
+        <v>7393036</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685783</v>
+        <v>128685836</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811497</v>
+        <v>811057</v>
       </c>
       <c r="R6" t="n">
-        <v>7393112</v>
+        <v>7393046</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685836</v>
+        <v>128685756</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811057</v>
+        <v>811013</v>
       </c>
       <c r="R7" t="n">
-        <v>7393046</v>
+        <v>7393006</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685853</v>
+        <v>128685804</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811044</v>
+        <v>810710</v>
       </c>
       <c r="R8" t="n">
-        <v>7392879</v>
+        <v>7393058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685804</v>
+        <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810710</v>
+        <v>811044</v>
       </c>
       <c r="R9" t="n">
-        <v>7393058</v>
+        <v>7392879</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685866</v>
+        <v>128685874</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810789</v>
+        <v>811502</v>
       </c>
       <c r="R12" t="n">
-        <v>7393036</v>
+        <v>7393150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685810</v>
+        <v>128685866</v>
       </c>
       <c r="B13" t="n">
-        <v>79068</v>
+        <v>92835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811027</v>
+        <v>810789</v>
       </c>
       <c r="R13" t="n">
-        <v>7393051</v>
+        <v>7393036</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685874</v>
+        <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>92829</v>
+        <v>79068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811502</v>
+        <v>811027</v>
       </c>
       <c r="R15" t="n">
-        <v>7393150</v>
+        <v>7393051</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685760</v>
+        <v>128685753</v>
       </c>
       <c r="B17" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R17" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685773</v>
+        <v>128685826</v>
       </c>
       <c r="B19" t="n">
-        <v>86984</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811089</v>
+        <v>811021</v>
       </c>
       <c r="R19" t="n">
-        <v>7393040</v>
+        <v>7392844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2408,7 +2408,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685826</v>
+        <v>128685773</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>86984</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811021</v>
+        <v>811089</v>
       </c>
       <c r="R20" t="n">
-        <v>7392844</v>
+        <v>7393040</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2506,6 +2505,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685753</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R21" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685869</v>
+        <v>128685831</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>78801</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810738</v>
+        <v>810853</v>
       </c>
       <c r="R22" t="n">
-        <v>7393051</v>
+        <v>7393047</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685802</v>
+        <v>128685778</v>
       </c>
       <c r="B23" t="n">
-        <v>92847</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811027</v>
+        <v>811517</v>
       </c>
       <c r="R23" t="n">
-        <v>7393042</v>
+        <v>7393148</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685778</v>
+        <v>128685854</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811517</v>
+        <v>811441</v>
       </c>
       <c r="R25" t="n">
-        <v>7393148</v>
+        <v>7393097</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685854</v>
+        <v>128685873</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>92829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811441</v>
+        <v>811303</v>
       </c>
       <c r="R26" t="n">
-        <v>7393097</v>
+        <v>7392893</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685802</v>
       </c>
       <c r="B27" t="n">
-        <v>78801</v>
+        <v>92847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>811027</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7393042</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685873</v>
+        <v>128685869</v>
       </c>
       <c r="B28" t="n">
-        <v>92829</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811303</v>
+        <v>810738</v>
       </c>
       <c r="R28" t="n">
-        <v>7392893</v>
+        <v>7393051</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685861</v>
+        <v>128685799</v>
       </c>
       <c r="B29" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810965</v>
+        <v>810790</v>
       </c>
       <c r="R29" t="n">
-        <v>7393009</v>
+        <v>7392931</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685785</v>
+        <v>128685861</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811518</v>
+        <v>810965</v>
       </c>
       <c r="R30" t="n">
-        <v>7393070</v>
+        <v>7393009</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685799</v>
+        <v>128685808</v>
       </c>
       <c r="B31" t="n">
-        <v>92847</v>
+        <v>79068</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810790</v>
+        <v>811520</v>
       </c>
       <c r="R31" t="n">
-        <v>7392931</v>
+        <v>7393156</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685808</v>
+        <v>128685758</v>
       </c>
       <c r="B32" t="n">
-        <v>79068</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811520</v>
+        <v>810717</v>
       </c>
       <c r="R32" t="n">
-        <v>7393156</v>
+        <v>7393072</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685839</v>
+        <v>128685785</v>
       </c>
       <c r="B33" t="n">
-        <v>78710</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811034</v>
+        <v>811518</v>
       </c>
       <c r="R33" t="n">
-        <v>7393002</v>
+        <v>7393070</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685758</v>
+        <v>128685839</v>
       </c>
       <c r="B34" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810717</v>
+        <v>811034</v>
       </c>
       <c r="R34" t="n">
-        <v>7393072</v>
+        <v>7393002</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685833</v>
+        <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811464</v>
+        <v>810812</v>
       </c>
       <c r="R37" t="n">
-        <v>7393013</v>
+        <v>7392934</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685841</v>
+        <v>128685833</v>
       </c>
       <c r="B39" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>810812</v>
+        <v>811464</v>
       </c>
       <c r="R39" t="n">
-        <v>7392934</v>
+        <v>7393013</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685828</v>
+        <v>128685818</v>
       </c>
       <c r="B41" t="n">
-        <v>78801</v>
+        <v>90178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>4962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811225</v>
+        <v>811120</v>
       </c>
       <c r="R41" t="n">
-        <v>7392837</v>
+        <v>7392983</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685818</v>
+        <v>128685828</v>
       </c>
       <c r="B42" t="n">
-        <v>90178</v>
+        <v>78801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4962</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811120</v>
+        <v>811225</v>
       </c>
       <c r="R42" t="n">
-        <v>7392983</v>
+        <v>7392837</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685814</v>
+        <v>128685798</v>
       </c>
       <c r="B43" t="n">
-        <v>78802</v>
+        <v>92847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810773</v>
+        <v>810767</v>
       </c>
       <c r="R43" t="n">
-        <v>7392966</v>
+        <v>7393075</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685798</v>
+        <v>128685877</v>
       </c>
       <c r="B44" t="n">
-        <v>92847</v>
+        <v>92829</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810767</v>
+        <v>811258</v>
       </c>
       <c r="R44" t="n">
-        <v>7393075</v>
+        <v>7392822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4852,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685877</v>
+        <v>128685761</v>
       </c>
       <c r="B45" t="n">
-        <v>92829</v>
+        <v>86984</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4863,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811258</v>
+        <v>811014</v>
       </c>
       <c r="R45" t="n">
-        <v>7392822</v>
+        <v>7392891</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4931,6 +4931,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4949,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685761</v>
+        <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>86984</v>
+        <v>78802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4960,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3690</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4984,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811014</v>
+        <v>810773</v>
       </c>
       <c r="R46" t="n">
-        <v>7392891</v>
+        <v>7392966</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5028,7 +5029,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685793</v>
+        <v>128685809</v>
       </c>
       <c r="B47" t="n">
-        <v>92860</v>
+        <v>79068</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3100</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810740</v>
+        <v>811105</v>
       </c>
       <c r="R47" t="n">
-        <v>7393062</v>
+        <v>7393054</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B48" t="n">
         <v>92860</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R48" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685875</v>
+        <v>128685792</v>
       </c>
       <c r="B49" t="n">
-        <v>92829</v>
+        <v>92860</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811283</v>
+        <v>811023</v>
       </c>
       <c r="R49" t="n">
-        <v>7392844</v>
+        <v>7392776</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685777</v>
+        <v>128685875</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>92829</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811015</v>
+        <v>811283</v>
       </c>
       <c r="R50" t="n">
-        <v>7392800</v>
+        <v>7392844</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685809</v>
+        <v>128685777</v>
       </c>
       <c r="B51" t="n">
-        <v>79068</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811105</v>
+        <v>811015</v>
       </c>
       <c r="R51" t="n">
-        <v>7393054</v>
+        <v>7392800</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685844</v>
+        <v>128685767</v>
       </c>
       <c r="B52" t="n">
-        <v>92835</v>
+        <v>86984</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810873</v>
+        <v>811516</v>
       </c>
       <c r="R52" t="n">
-        <v>7392973</v>
+        <v>7393158</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685803</v>
+        <v>128685844</v>
       </c>
       <c r="B53" t="n">
-        <v>92847</v>
+        <v>92835</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810733</v>
+        <v>810873</v>
       </c>
       <c r="R53" t="n">
-        <v>7393068</v>
+        <v>7392973</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685767</v>
+        <v>128685803</v>
       </c>
       <c r="B54" t="n">
-        <v>86984</v>
+        <v>92847</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811516</v>
+        <v>810733</v>
       </c>
       <c r="R54" t="n">
-        <v>7393158</v>
+        <v>7393068</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685850</v>
+        <v>128685868</v>
       </c>
       <c r="B55" t="n">
         <v>92835</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810978</v>
+        <v>810757</v>
       </c>
       <c r="R55" t="n">
-        <v>7392914</v>
+        <v>7393053</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685868</v>
+        <v>128685850</v>
       </c>
       <c r="B58" t="n">
         <v>92835</v>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810757</v>
+        <v>810978</v>
       </c>
       <c r="R58" t="n">
-        <v>7393053</v>
+        <v>7392914</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,32 +6211,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685815</v>
+        <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>78802</v>
+        <v>58097</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810946</v>
+        <v>811127</v>
       </c>
       <c r="R59" t="n">
-        <v>7392983</v>
+        <v>7392976</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685823</v>
+        <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>58097</v>
+        <v>78802</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811127</v>
+        <v>810946</v>
       </c>
       <c r="R60" t="n">
-        <v>7392976</v>
+        <v>7392983</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685812</v>
+        <v>128685800</v>
       </c>
       <c r="B62" t="n">
-        <v>79068</v>
+        <v>92847</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810948</v>
+        <v>810861</v>
       </c>
       <c r="R62" t="n">
-        <v>7392987</v>
+        <v>7392976</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685752</v>
+        <v>128685859</v>
       </c>
       <c r="B63" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811410</v>
+        <v>811498</v>
       </c>
       <c r="R63" t="n">
-        <v>7392970</v>
+        <v>7393147</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6795,32 +6795,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685788</v>
+        <v>128685812</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811107</v>
+        <v>810948</v>
       </c>
       <c r="R65" t="n">
-        <v>7393022</v>
+        <v>7392987</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6892,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685859</v>
+        <v>128685752</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811498</v>
+        <v>811410</v>
       </c>
       <c r="R66" t="n">
-        <v>7393147</v>
+        <v>7392970</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685800</v>
+        <v>128685806</v>
       </c>
       <c r="B67" t="n">
-        <v>92847</v>
+        <v>79068</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>810861</v>
+        <v>811056</v>
       </c>
       <c r="R67" t="n">
-        <v>7392976</v>
+        <v>7392881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685806</v>
+        <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>79068</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811056</v>
+        <v>811107</v>
       </c>
       <c r="R68" t="n">
-        <v>7392881</v>
+        <v>7393022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685840</v>
+        <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>82878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810762</v>
+        <v>810781</v>
       </c>
       <c r="R69" t="n">
-        <v>7393078</v>
+        <v>7392936</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685838</v>
+        <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>82878</v>
+        <v>91606</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810781</v>
+        <v>810934</v>
       </c>
       <c r="R70" t="n">
-        <v>7392936</v>
+        <v>7393019</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685813</v>
+        <v>128685840</v>
       </c>
       <c r="B71" t="n">
-        <v>91606</v>
+        <v>92835</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810934</v>
+        <v>810762</v>
       </c>
       <c r="R71" t="n">
-        <v>7393019</v>
+        <v>7393078</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685754</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811026</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7393053</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,7 +7765,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685848</v>
+        <v>128685864</v>
       </c>
       <c r="B75" t="n">
         <v>92835</v>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810952</v>
+        <v>810814</v>
       </c>
       <c r="R75" t="n">
-        <v>7392920</v>
+        <v>7393022</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685846</v>
+        <v>128685848</v>
       </c>
       <c r="B76" t="n">
         <v>92835</v>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810911</v>
+        <v>810952</v>
       </c>
       <c r="R76" t="n">
-        <v>7392927</v>
+        <v>7392920</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685822</v>
+        <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>57831</v>
+        <v>92835</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7970,21 +7970,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810901</v>
+        <v>810911</v>
       </c>
       <c r="R77" t="n">
-        <v>7393040</v>
+        <v>7392927</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685864</v>
+        <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>92835</v>
+        <v>57831</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810814</v>
+        <v>810901</v>
       </c>
       <c r="R78" t="n">
-        <v>7393022</v>
+        <v>7393040</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685781</v>
+        <v>128685780</v>
       </c>
       <c r="B79" t="n">
         <v>57727</v>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811507</v>
+        <v>811531</v>
       </c>
       <c r="R79" t="n">
-        <v>7393120</v>
+        <v>7393153</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685780</v>
+        <v>128685781</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811531</v>
+        <v>811507</v>
       </c>
       <c r="R80" t="n">
-        <v>7393153</v>
+        <v>7393120</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,32 +8347,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685851</v>
+        <v>128685819</v>
       </c>
       <c r="B81" t="n">
-        <v>92835</v>
+        <v>90178</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811062</v>
+        <v>810744</v>
       </c>
       <c r="R81" t="n">
-        <v>7392883</v>
+        <v>7393058</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,32 +8444,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B82" t="n">
-        <v>90178</v>
+        <v>92835</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R82" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685748</v>
+        <v>128685817</v>
       </c>
       <c r="B83" t="n">
-        <v>79663</v>
+        <v>90178</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810767</v>
+        <v>811007</v>
       </c>
       <c r="R83" t="n">
-        <v>7392968</v>
+        <v>7392796</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B84" t="n">
-        <v>90178</v>
+        <v>79663</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8649,21 +8649,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>79663</v>
+        <v>92835</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R86" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R87" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>92835</v>
+        <v>78801</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R88" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685796</v>
+        <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>92866</v>
+        <v>86984</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>232140</v>
+        <v>3690</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810795</v>
+        <v>810867</v>
       </c>
       <c r="R89" t="n">
-        <v>7393042</v>
+        <v>7392967</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685764</v>
+        <v>128685852</v>
       </c>
       <c r="B90" t="n">
-        <v>86984</v>
+        <v>92835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>810867</v>
+        <v>811057</v>
       </c>
       <c r="R90" t="n">
-        <v>7392967</v>
+        <v>7392877</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>86984</v>
+        <v>92847</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R91" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,7 +9396,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,32 +9414,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B92" t="n">
-        <v>92847</v>
+        <v>86984</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9449,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R92" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9494,6 +9493,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9512,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685852</v>
+        <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92835</v>
+        <v>92866</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811057</v>
+        <v>810795</v>
       </c>
       <c r="R93" t="n">
-        <v>7392877</v>
+        <v>7393042</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9809,32 +9809,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685849</v>
+        <v>128685834</v>
       </c>
       <c r="B96" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810964</v>
+        <v>811525</v>
       </c>
       <c r="R96" t="n">
-        <v>7392920</v>
+        <v>7393139</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,32 +9906,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685834</v>
+        <v>128685849</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811525</v>
+        <v>810964</v>
       </c>
       <c r="R97" t="n">
-        <v>7393139</v>
+        <v>7392920</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685790</v>
+        <v>128685843</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810977</v>
+        <v>810858</v>
       </c>
       <c r="R2" t="n">
-        <v>7393016</v>
+        <v>7392973</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685783</v>
+        <v>128685837</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811497</v>
+        <v>810756</v>
       </c>
       <c r="R3" t="n">
-        <v>7393112</v>
+        <v>7393036</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685843</v>
+        <v>128685836</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810858</v>
+        <v>811057</v>
       </c>
       <c r="R4" t="n">
-        <v>7392973</v>
+        <v>7393046</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685837</v>
+        <v>128685756</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810756</v>
+        <v>811013</v>
       </c>
       <c r="R5" t="n">
-        <v>7393036</v>
+        <v>7393006</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685836</v>
+        <v>128685790</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>56917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811057</v>
+        <v>810977</v>
       </c>
       <c r="R6" t="n">
-        <v>7393046</v>
+        <v>7393016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685756</v>
+        <v>128685783</v>
       </c>
       <c r="B7" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811013</v>
+        <v>811497</v>
       </c>
       <c r="R7" t="n">
-        <v>7393006</v>
+        <v>7393112</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685795</v>
+        <v>128685874</v>
       </c>
       <c r="B11" t="n">
-        <v>92480</v>
+        <v>92829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810915</v>
+        <v>811502</v>
       </c>
       <c r="R11" t="n">
-        <v>7393042</v>
+        <v>7393150</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685874</v>
+        <v>128685866</v>
       </c>
       <c r="B12" t="n">
-        <v>92829</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811502</v>
+        <v>810789</v>
       </c>
       <c r="R12" t="n">
-        <v>7393150</v>
+        <v>7393036</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685866</v>
+        <v>128685769</v>
       </c>
       <c r="B13" t="n">
-        <v>92835</v>
+        <v>86984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810789</v>
+        <v>810725</v>
       </c>
       <c r="R13" t="n">
-        <v>7393036</v>
+        <v>7393066</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685769</v>
+        <v>128685810</v>
       </c>
       <c r="B14" t="n">
-        <v>86984</v>
+        <v>79068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3690</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810725</v>
+        <v>811027</v>
       </c>
       <c r="R14" t="n">
-        <v>7393066</v>
+        <v>7393051</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685810</v>
+        <v>128685795</v>
       </c>
       <c r="B15" t="n">
-        <v>79068</v>
+        <v>92480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811027</v>
+        <v>810915</v>
       </c>
       <c r="R15" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685753</v>
+        <v>128685773</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>86984</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811087</v>
+        <v>811089</v>
       </c>
       <c r="R17" t="n">
-        <v>7393042</v>
+        <v>7393040</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685829</v>
+        <v>128685753</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2329,7 +2330,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685826</v>
+        <v>128685829</v>
       </c>
       <c r="B19" t="n">
         <v>78801</v>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R19" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2426,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685773</v>
+        <v>128685826</v>
       </c>
       <c r="B20" t="n">
-        <v>86984</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811089</v>
+        <v>811021</v>
       </c>
       <c r="R20" t="n">
-        <v>7393040</v>
+        <v>7392844</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2505,7 +2506,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685785</v>
+        <v>128685839</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>78710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811518</v>
+        <v>811034</v>
       </c>
       <c r="R33" t="n">
-        <v>7393070</v>
+        <v>7393002</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685839</v>
+        <v>128685785</v>
       </c>
       <c r="B34" t="n">
-        <v>78710</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811034</v>
+        <v>811518</v>
       </c>
       <c r="R34" t="n">
-        <v>7393002</v>
+        <v>7393070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685818</v>
+        <v>128685798</v>
       </c>
       <c r="B41" t="n">
-        <v>90178</v>
+        <v>92847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811120</v>
+        <v>810767</v>
       </c>
       <c r="R41" t="n">
-        <v>7392983</v>
+        <v>7393075</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685828</v>
+        <v>128685877</v>
       </c>
       <c r="B42" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811225</v>
+        <v>811258</v>
       </c>
       <c r="R42" t="n">
-        <v>7392837</v>
+        <v>7392822</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685798</v>
+        <v>128685761</v>
       </c>
       <c r="B43" t="n">
-        <v>92847</v>
+        <v>86984</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810767</v>
+        <v>811014</v>
       </c>
       <c r="R43" t="n">
-        <v>7393075</v>
+        <v>7392891</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4737,6 +4737,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4755,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685877</v>
+        <v>128685828</v>
       </c>
       <c r="B44" t="n">
-        <v>92829</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811258</v>
+        <v>811225</v>
       </c>
       <c r="R44" t="n">
-        <v>7392822</v>
+        <v>7392837</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685761</v>
+        <v>128685818</v>
       </c>
       <c r="B45" t="n">
-        <v>86984</v>
+        <v>90178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811014</v>
+        <v>811120</v>
       </c>
       <c r="R45" t="n">
-        <v>7392891</v>
+        <v>7392983</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4931,7 +4932,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685809</v>
+        <v>128685793</v>
       </c>
       <c r="B47" t="n">
-        <v>79068</v>
+        <v>92860</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>3100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811105</v>
+        <v>810740</v>
       </c>
       <c r="R47" t="n">
-        <v>7393054</v>
+        <v>7393062</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B48" t="n">
         <v>92860</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R48" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685792</v>
+        <v>128685777</v>
       </c>
       <c r="B49" t="n">
-        <v>92860</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811023</v>
+        <v>811015</v>
       </c>
       <c r="R49" t="n">
-        <v>7392776</v>
+        <v>7392800</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R51" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685771</v>
+        <v>128685788</v>
       </c>
       <c r="B61" t="n">
-        <v>86984</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3690</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811112</v>
+        <v>811107</v>
       </c>
       <c r="R61" t="n">
-        <v>7393038</v>
+        <v>7393022</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,7 +6484,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6503,32 +6502,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685800</v>
+        <v>128685771</v>
       </c>
       <c r="B62" t="n">
-        <v>92847</v>
+        <v>86984</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6537,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810861</v>
+        <v>811112</v>
       </c>
       <c r="R62" t="n">
-        <v>7392976</v>
+        <v>7393038</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6582,6 +6581,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685859</v>
+        <v>128685800</v>
       </c>
       <c r="B63" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6611,21 +6611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811498</v>
+        <v>810861</v>
       </c>
       <c r="R63" t="n">
-        <v>7393147</v>
+        <v>7392976</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685789</v>
+        <v>128685859</v>
       </c>
       <c r="B64" t="n">
-        <v>90376</v>
+        <v>92835</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811258</v>
+        <v>811498</v>
       </c>
       <c r="R64" t="n">
-        <v>7392822</v>
+        <v>7393147</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6776,7 +6776,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6795,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685812</v>
+        <v>128685789</v>
       </c>
       <c r="B65" t="n">
-        <v>79068</v>
+        <v>90376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810948</v>
+        <v>811258</v>
       </c>
       <c r="R65" t="n">
-        <v>7392987</v>
+        <v>7392822</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6874,6 +6873,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6892,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685752</v>
+        <v>128685812</v>
       </c>
       <c r="B66" t="n">
-        <v>79663</v>
+        <v>79068</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811410</v>
+        <v>810948</v>
       </c>
       <c r="R66" t="n">
-        <v>7392970</v>
+        <v>7392987</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685806</v>
+        <v>128685752</v>
       </c>
       <c r="B67" t="n">
-        <v>79068</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811056</v>
+        <v>811410</v>
       </c>
       <c r="R67" t="n">
-        <v>7392881</v>
+        <v>7392970</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685788</v>
+        <v>128685806</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811107</v>
+        <v>811056</v>
       </c>
       <c r="R68" t="n">
-        <v>7393022</v>
+        <v>7392881</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685838</v>
+        <v>128685840</v>
       </c>
       <c r="B69" t="n">
-        <v>82878</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810781</v>
+        <v>810762</v>
       </c>
       <c r="R69" t="n">
-        <v>7392936</v>
+        <v>7393078</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685813</v>
+        <v>128685872</v>
       </c>
       <c r="B70" t="n">
-        <v>91606</v>
+        <v>92829</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810934</v>
+        <v>811269</v>
       </c>
       <c r="R70" t="n">
-        <v>7393019</v>
+        <v>7392839</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685840</v>
+        <v>128685856</v>
       </c>
       <c r="B71" t="n">
         <v>92835</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810762</v>
+        <v>811494</v>
       </c>
       <c r="R71" t="n">
-        <v>7393078</v>
+        <v>7393153</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685838</v>
       </c>
       <c r="B72" t="n">
-        <v>92829</v>
+        <v>82878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>810781</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7392936</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685813</v>
       </c>
       <c r="B73" t="n">
-        <v>92835</v>
+        <v>91606</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>810934</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7393019</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685864</v>
+        <v>128685822</v>
       </c>
       <c r="B75" t="n">
-        <v>92835</v>
+        <v>57831</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810814</v>
+        <v>810901</v>
       </c>
       <c r="R75" t="n">
-        <v>7393022</v>
+        <v>7393040</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685848</v>
+        <v>128685864</v>
       </c>
       <c r="B76" t="n">
         <v>92835</v>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810952</v>
+        <v>810814</v>
       </c>
       <c r="R76" t="n">
-        <v>7392920</v>
+        <v>7393022</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685846</v>
+        <v>128685848</v>
       </c>
       <c r="B77" t="n">
         <v>92835</v>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810911</v>
+        <v>810952</v>
       </c>
       <c r="R77" t="n">
-        <v>7392927</v>
+        <v>7392920</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685822</v>
+        <v>128685846</v>
       </c>
       <c r="B78" t="n">
-        <v>57831</v>
+        <v>92835</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810901</v>
+        <v>810911</v>
       </c>
       <c r="R78" t="n">
-        <v>7393040</v>
+        <v>7392927</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685780</v>
+        <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>90178</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8164,21 +8164,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811531</v>
+        <v>810744</v>
       </c>
       <c r="R79" t="n">
-        <v>7393153</v>
+        <v>7393058</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685781</v>
+        <v>128685780</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811507</v>
+        <v>811531</v>
       </c>
       <c r="R80" t="n">
-        <v>7393120</v>
+        <v>7393153</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685819</v>
+        <v>128685781</v>
       </c>
       <c r="B81" t="n">
-        <v>90178</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8358,21 +8358,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4962</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>810744</v>
+        <v>811507</v>
       </c>
       <c r="R81" t="n">
-        <v>7393058</v>
+        <v>7393120</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B83" t="n">
-        <v>90178</v>
+        <v>92835</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R83" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B85" t="n">
-        <v>92835</v>
+        <v>90178</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R85" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9809,32 +9809,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685834</v>
+        <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811525</v>
+        <v>810964</v>
       </c>
       <c r="R96" t="n">
-        <v>7393139</v>
+        <v>7392920</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685849</v>
+        <v>128685863</v>
       </c>
       <c r="B97" t="n">
         <v>92835</v>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810964</v>
+        <v>810854</v>
       </c>
       <c r="R97" t="n">
-        <v>7392920</v>
+        <v>7393015</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10003,32 +10003,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128685863</v>
+        <v>128685834</v>
       </c>
       <c r="B98" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>810854</v>
+        <v>811525</v>
       </c>
       <c r="R98" t="n">
-        <v>7393015</v>
+        <v>7393139</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685790</v>
+        <v>128685783</v>
       </c>
       <c r="B6" t="n">
-        <v>56917</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810977</v>
+        <v>811497</v>
       </c>
       <c r="R6" t="n">
-        <v>7393016</v>
+        <v>7393112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685783</v>
+        <v>128685790</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>56917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811497</v>
+        <v>810977</v>
       </c>
       <c r="R7" t="n">
-        <v>7393112</v>
+        <v>7393016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685810</v>
+        <v>128685795</v>
       </c>
       <c r="B14" t="n">
-        <v>79068</v>
+        <v>92480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811027</v>
+        <v>810915</v>
       </c>
       <c r="R14" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685795</v>
+        <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>92480</v>
+        <v>79068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810915</v>
+        <v>811027</v>
       </c>
       <c r="R15" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685773</v>
+        <v>128685753</v>
       </c>
       <c r="B17" t="n">
-        <v>86984</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811089</v>
+        <v>811087</v>
       </c>
       <c r="R17" t="n">
-        <v>7393040</v>
+        <v>7393042</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685753</v>
+        <v>128685829</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R18" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685829</v>
+        <v>128685826</v>
       </c>
       <c r="B19" t="n">
         <v>78801</v>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810920</v>
+        <v>811021</v>
       </c>
       <c r="R19" t="n">
-        <v>7393003</v>
+        <v>7392844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685826</v>
+        <v>128685760</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R20" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2524,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685773</v>
       </c>
       <c r="B21" t="n">
-        <v>79634</v>
+        <v>86984</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R21" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2603,6 +2602,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685831</v>
+        <v>128685854</v>
       </c>
       <c r="B22" t="n">
-        <v>78801</v>
+        <v>92835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810853</v>
+        <v>811441</v>
       </c>
       <c r="R22" t="n">
-        <v>7393047</v>
+        <v>7393097</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685778</v>
+        <v>128685873</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>92829</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811517</v>
+        <v>811303</v>
       </c>
       <c r="R23" t="n">
-        <v>7393148</v>
+        <v>7392893</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685816</v>
+        <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>78802</v>
+        <v>92847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>810920</v>
+        <v>811027</v>
       </c>
       <c r="R24" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685854</v>
+        <v>128685869</v>
       </c>
       <c r="B25" t="n">
         <v>92835</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811441</v>
+        <v>810738</v>
       </c>
       <c r="R25" t="n">
-        <v>7393097</v>
+        <v>7393051</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685873</v>
+        <v>128685816</v>
       </c>
       <c r="B26" t="n">
-        <v>92829</v>
+        <v>78802</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3020,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811303</v>
+        <v>810920</v>
       </c>
       <c r="R26" t="n">
-        <v>7392893</v>
+        <v>7393003</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685802</v>
+        <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>92847</v>
+        <v>78801</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811027</v>
+        <v>810853</v>
       </c>
       <c r="R27" t="n">
-        <v>7393042</v>
+        <v>7393047</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685869</v>
+        <v>128685778</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810738</v>
+        <v>811517</v>
       </c>
       <c r="R28" t="n">
-        <v>7393051</v>
+        <v>7393148</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685799</v>
+        <v>128685839</v>
       </c>
       <c r="B29" t="n">
-        <v>92847</v>
+        <v>78710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810790</v>
+        <v>811034</v>
       </c>
       <c r="R29" t="n">
-        <v>7392931</v>
+        <v>7393002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685861</v>
+        <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810965</v>
+        <v>810790</v>
       </c>
       <c r="R30" t="n">
-        <v>7393009</v>
+        <v>7392931</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685808</v>
+        <v>128685861</v>
       </c>
       <c r="B31" t="n">
-        <v>79068</v>
+        <v>92835</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811520</v>
+        <v>810965</v>
       </c>
       <c r="R31" t="n">
-        <v>7393156</v>
+        <v>7393009</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685758</v>
+        <v>128685808</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>79068</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810717</v>
+        <v>811520</v>
       </c>
       <c r="R32" t="n">
-        <v>7393072</v>
+        <v>7393156</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685839</v>
+        <v>128685758</v>
       </c>
       <c r="B33" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811034</v>
+        <v>810717</v>
       </c>
       <c r="R33" t="n">
-        <v>7393002</v>
+        <v>7393072</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685857</v>
+        <v>128685807</v>
       </c>
       <c r="B36" t="n">
-        <v>92835</v>
+        <v>79068</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811492</v>
+        <v>811004</v>
       </c>
       <c r="R36" t="n">
-        <v>7393149</v>
+        <v>7392787</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685841</v>
+        <v>128685833</v>
       </c>
       <c r="B37" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810812</v>
+        <v>811464</v>
       </c>
       <c r="R37" t="n">
-        <v>7392934</v>
+        <v>7393013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685807</v>
+        <v>128685805</v>
       </c>
       <c r="B38" t="n">
         <v>79068</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811004</v>
+        <v>810973</v>
       </c>
       <c r="R38" t="n">
-        <v>7392787</v>
+        <v>7392910</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685833</v>
+        <v>128685841</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811464</v>
+        <v>810812</v>
       </c>
       <c r="R39" t="n">
-        <v>7393013</v>
+        <v>7392934</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685805</v>
+        <v>128685857</v>
       </c>
       <c r="B40" t="n">
-        <v>79068</v>
+        <v>92835</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810973</v>
+        <v>811492</v>
       </c>
       <c r="R40" t="n">
-        <v>7392910</v>
+        <v>7393149</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685798</v>
+        <v>128685828</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>78801</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810767</v>
+        <v>811225</v>
       </c>
       <c r="R41" t="n">
-        <v>7393075</v>
+        <v>7392837</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685877</v>
+        <v>128685814</v>
       </c>
       <c r="B42" t="n">
-        <v>92829</v>
+        <v>78802</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811258</v>
+        <v>810773</v>
       </c>
       <c r="R42" t="n">
-        <v>7392822</v>
+        <v>7392966</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685761</v>
+        <v>128685798</v>
       </c>
       <c r="B43" t="n">
-        <v>86984</v>
+        <v>92847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811014</v>
+        <v>810767</v>
       </c>
       <c r="R43" t="n">
-        <v>7392891</v>
+        <v>7393075</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4737,7 +4737,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685828</v>
+        <v>128685877</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>92829</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811225</v>
+        <v>811258</v>
       </c>
       <c r="R44" t="n">
-        <v>7392837</v>
+        <v>7392822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685818</v>
+        <v>128685761</v>
       </c>
       <c r="B45" t="n">
-        <v>90178</v>
+        <v>86984</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4863,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4962</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4887,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811120</v>
+        <v>811014</v>
       </c>
       <c r="R45" t="n">
-        <v>7392983</v>
+        <v>7392891</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4932,6 +4931,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685814</v>
+        <v>128685818</v>
       </c>
       <c r="B46" t="n">
-        <v>78802</v>
+        <v>90178</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810773</v>
+        <v>811120</v>
       </c>
       <c r="R46" t="n">
-        <v>7392966</v>
+        <v>7392983</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685793</v>
+        <v>128685875</v>
       </c>
       <c r="B47" t="n">
-        <v>92860</v>
+        <v>92829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810740</v>
+        <v>811283</v>
       </c>
       <c r="R47" t="n">
-        <v>7393062</v>
+        <v>7392844</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685777</v>
+        <v>128685793</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>92860</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811015</v>
+        <v>810740</v>
       </c>
       <c r="R49" t="n">
-        <v>7392800</v>
+        <v>7393062</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685875</v>
+        <v>128685809</v>
       </c>
       <c r="B50" t="n">
-        <v>92829</v>
+        <v>79068</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811283</v>
+        <v>811105</v>
       </c>
       <c r="R50" t="n">
-        <v>7392844</v>
+        <v>7393054</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685809</v>
+        <v>128685777</v>
       </c>
       <c r="B51" t="n">
-        <v>79068</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811105</v>
+        <v>811015</v>
       </c>
       <c r="R51" t="n">
-        <v>7393054</v>
+        <v>7392800</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685767</v>
+        <v>128685823</v>
       </c>
       <c r="B52" t="n">
-        <v>86984</v>
+        <v>58097</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3690</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811516</v>
+        <v>811127</v>
       </c>
       <c r="R52" t="n">
-        <v>7393158</v>
+        <v>7392976</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685844</v>
+        <v>128685815</v>
       </c>
       <c r="B53" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810873</v>
+        <v>810946</v>
       </c>
       <c r="R53" t="n">
-        <v>7392973</v>
+        <v>7392983</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685803</v>
+        <v>128685767</v>
       </c>
       <c r="B54" t="n">
-        <v>92847</v>
+        <v>86984</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810733</v>
+        <v>811516</v>
       </c>
       <c r="R54" t="n">
-        <v>7393068</v>
+        <v>7393158</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685868</v>
+        <v>128685844</v>
       </c>
       <c r="B55" t="n">
         <v>92835</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810757</v>
+        <v>810873</v>
       </c>
       <c r="R55" t="n">
-        <v>7393053</v>
+        <v>7392973</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685876</v>
+        <v>128685803</v>
       </c>
       <c r="B56" t="n">
-        <v>92829</v>
+        <v>92847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811269</v>
+        <v>810733</v>
       </c>
       <c r="R56" t="n">
-        <v>7392821</v>
+        <v>7393068</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685855</v>
+        <v>128685868</v>
       </c>
       <c r="B57" t="n">
         <v>92835</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811502</v>
+        <v>810757</v>
       </c>
       <c r="R57" t="n">
-        <v>7393143</v>
+        <v>7393053</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685850</v>
+        <v>128685876</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>92829</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810978</v>
+        <v>811269</v>
       </c>
       <c r="R58" t="n">
-        <v>7392914</v>
+        <v>7392821</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685823</v>
+        <v>128685855</v>
       </c>
       <c r="B59" t="n">
-        <v>58097</v>
+        <v>92835</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811127</v>
+        <v>811502</v>
       </c>
       <c r="R59" t="n">
-        <v>7392976</v>
+        <v>7393143</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685815</v>
+        <v>128685850</v>
       </c>
       <c r="B60" t="n">
-        <v>78802</v>
+        <v>92835</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810946</v>
+        <v>810978</v>
       </c>
       <c r="R60" t="n">
-        <v>7392983</v>
+        <v>7392914</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685788</v>
+        <v>128685771</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>86984</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>3690</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811107</v>
+        <v>811112</v>
       </c>
       <c r="R61" t="n">
-        <v>7393022</v>
+        <v>7393038</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,6 +6484,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6502,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685771</v>
+        <v>128685859</v>
       </c>
       <c r="B62" t="n">
-        <v>86984</v>
+        <v>92835</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6537,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811112</v>
+        <v>811498</v>
       </c>
       <c r="R62" t="n">
-        <v>7393038</v>
+        <v>7393147</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6581,7 +6582,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685800</v>
+        <v>128685789</v>
       </c>
       <c r="B63" t="n">
-        <v>92847</v>
+        <v>90376</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>810861</v>
+        <v>811258</v>
       </c>
       <c r="R63" t="n">
-        <v>7392976</v>
+        <v>7392822</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6679,6 +6679,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6697,10 +6698,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685859</v>
+        <v>128685812</v>
       </c>
       <c r="B64" t="n">
-        <v>92835</v>
+        <v>79068</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6708,21 +6709,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6733,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811498</v>
+        <v>810948</v>
       </c>
       <c r="R64" t="n">
-        <v>7393147</v>
+        <v>7392987</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,32 +6795,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685789</v>
+        <v>128685752</v>
       </c>
       <c r="B65" t="n">
-        <v>90376</v>
+        <v>79663</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6286</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811258</v>
+        <v>811410</v>
       </c>
       <c r="R65" t="n">
-        <v>7392822</v>
+        <v>7392970</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6873,7 +6874,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6892,7 +6892,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685812</v>
+        <v>128685806</v>
       </c>
       <c r="B66" t="n">
         <v>79068</v>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>810948</v>
+        <v>811056</v>
       </c>
       <c r="R66" t="n">
-        <v>7392987</v>
+        <v>7392881</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685752</v>
+        <v>128685788</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811410</v>
+        <v>811107</v>
       </c>
       <c r="R67" t="n">
-        <v>7392970</v>
+        <v>7393022</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,10 +7086,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685806</v>
+        <v>128685800</v>
       </c>
       <c r="B68" t="n">
-        <v>79068</v>
+        <v>92847</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7097,21 +7097,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811056</v>
+        <v>810861</v>
       </c>
       <c r="R68" t="n">
-        <v>7392881</v>
+        <v>7392976</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685840</v>
+        <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>82878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810762</v>
+        <v>810781</v>
       </c>
       <c r="R69" t="n">
-        <v>7393078</v>
+        <v>7392936</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685872</v>
+        <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>92829</v>
+        <v>91606</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811269</v>
+        <v>810934</v>
       </c>
       <c r="R70" t="n">
-        <v>7392839</v>
+        <v>7393019</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685856</v>
+        <v>128685840</v>
       </c>
       <c r="B71" t="n">
         <v>92835</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811494</v>
+        <v>810762</v>
       </c>
       <c r="R71" t="n">
-        <v>7393153</v>
+        <v>7393078</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685838</v>
+        <v>128685872</v>
       </c>
       <c r="B72" t="n">
-        <v>82878</v>
+        <v>92829</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810781</v>
+        <v>811269</v>
       </c>
       <c r="R72" t="n">
-        <v>7392936</v>
+        <v>7392839</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685813</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>91606</v>
+        <v>92835</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>810934</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7393019</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685822</v>
+        <v>128685864</v>
       </c>
       <c r="B75" t="n">
-        <v>57831</v>
+        <v>92835</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810901</v>
+        <v>810814</v>
       </c>
       <c r="R75" t="n">
-        <v>7393040</v>
+        <v>7393022</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685864</v>
+        <v>128685848</v>
       </c>
       <c r="B76" t="n">
         <v>92835</v>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810814</v>
+        <v>810952</v>
       </c>
       <c r="R76" t="n">
-        <v>7393022</v>
+        <v>7392920</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685848</v>
+        <v>128685846</v>
       </c>
       <c r="B77" t="n">
         <v>92835</v>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810952</v>
+        <v>810911</v>
       </c>
       <c r="R77" t="n">
-        <v>7392920</v>
+        <v>7392927</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685846</v>
+        <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>92835</v>
+        <v>57831</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810911</v>
+        <v>810901</v>
       </c>
       <c r="R78" t="n">
-        <v>7392927</v>
+        <v>7393040</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685819</v>
+        <v>128685780</v>
       </c>
       <c r="B79" t="n">
-        <v>90178</v>
+        <v>57727</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8164,21 +8164,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>810744</v>
+        <v>811531</v>
       </c>
       <c r="R79" t="n">
-        <v>7393058</v>
+        <v>7393153</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685780</v>
+        <v>128685781</v>
       </c>
       <c r="B80" t="n">
         <v>57727</v>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811531</v>
+        <v>811507</v>
       </c>
       <c r="R80" t="n">
-        <v>7393153</v>
+        <v>7393120</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685781</v>
+        <v>128685819</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>90178</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8358,21 +8358,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811507</v>
+        <v>810744</v>
       </c>
       <c r="R81" t="n">
-        <v>7393120</v>
+        <v>7393058</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685748</v>
+        <v>128685817</v>
       </c>
       <c r="B84" t="n">
-        <v>79663</v>
+        <v>90178</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8649,21 +8649,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810767</v>
+        <v>811007</v>
       </c>
       <c r="R84" t="n">
-        <v>7392968</v>
+        <v>7392796</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B85" t="n">
-        <v>90178</v>
+        <v>79663</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8746,21 +8746,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R85" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685804</v>
+        <v>128685835</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810710</v>
+        <v>811420</v>
       </c>
       <c r="R8" t="n">
-        <v>7393058</v>
+        <v>7392954</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685853</v>
+        <v>128685804</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811044</v>
+        <v>810710</v>
       </c>
       <c r="R9" t="n">
-        <v>7392879</v>
+        <v>7393058</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685835</v>
+        <v>128685853</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811420</v>
+        <v>811044</v>
       </c>
       <c r="R10" t="n">
-        <v>7392954</v>
+        <v>7392879</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685874</v>
+        <v>128685769</v>
       </c>
       <c r="B11" t="n">
-        <v>92829</v>
+        <v>86984</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811502</v>
+        <v>810725</v>
       </c>
       <c r="R11" t="n">
-        <v>7393150</v>
+        <v>7393066</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685866</v>
+        <v>128685874</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810789</v>
+        <v>811502</v>
       </c>
       <c r="R12" t="n">
-        <v>7393036</v>
+        <v>7393150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685769</v>
+        <v>128685795</v>
       </c>
       <c r="B13" t="n">
-        <v>86984</v>
+        <v>92480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810725</v>
+        <v>810915</v>
       </c>
       <c r="R13" t="n">
-        <v>7393066</v>
+        <v>7393042</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685795</v>
+        <v>128685866</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810915</v>
+        <v>810789</v>
       </c>
       <c r="R14" t="n">
-        <v>7393042</v>
+        <v>7393036</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685854</v>
+        <v>128685778</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811441</v>
+        <v>811517</v>
       </c>
       <c r="R22" t="n">
-        <v>7393097</v>
+        <v>7393148</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685873</v>
+        <v>128685816</v>
       </c>
       <c r="B23" t="n">
-        <v>92829</v>
+        <v>78802</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811303</v>
+        <v>810920</v>
       </c>
       <c r="R23" t="n">
-        <v>7392893</v>
+        <v>7393003</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685802</v>
+        <v>128685854</v>
       </c>
       <c r="B24" t="n">
-        <v>92847</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811027</v>
+        <v>811441</v>
       </c>
       <c r="R24" t="n">
-        <v>7393042</v>
+        <v>7393097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685869</v>
+        <v>128685873</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>92829</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810738</v>
+        <v>811303</v>
       </c>
       <c r="R25" t="n">
-        <v>7393051</v>
+        <v>7392893</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685816</v>
+        <v>128685802</v>
       </c>
       <c r="B26" t="n">
-        <v>78802</v>
+        <v>92847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810920</v>
+        <v>811027</v>
       </c>
       <c r="R26" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685869</v>
       </c>
       <c r="B27" t="n">
-        <v>78801</v>
+        <v>92835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>810738</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7393051</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685778</v>
+        <v>128685831</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811517</v>
+        <v>810853</v>
       </c>
       <c r="R28" t="n">
-        <v>7393148</v>
+        <v>7393047</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685785</v>
+        <v>128685776</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811518</v>
+        <v>810803</v>
       </c>
       <c r="R34" t="n">
-        <v>7393070</v>
+        <v>7392998</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685776</v>
+        <v>128685785</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810803</v>
+        <v>811518</v>
       </c>
       <c r="R35" t="n">
-        <v>7392998</v>
+        <v>7393070</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685807</v>
+        <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>79068</v>
+        <v>92835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811004</v>
+        <v>811492</v>
       </c>
       <c r="R36" t="n">
-        <v>7392787</v>
+        <v>7393149</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685833</v>
+        <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811464</v>
+        <v>810812</v>
       </c>
       <c r="R37" t="n">
-        <v>7393013</v>
+        <v>7392934</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685805</v>
+        <v>128685807</v>
       </c>
       <c r="B38" t="n">
         <v>79068</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810973</v>
+        <v>811004</v>
       </c>
       <c r="R38" t="n">
-        <v>7392910</v>
+        <v>7392787</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685841</v>
+        <v>128685833</v>
       </c>
       <c r="B39" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>810812</v>
+        <v>811464</v>
       </c>
       <c r="R39" t="n">
-        <v>7392934</v>
+        <v>7393013</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685857</v>
+        <v>128685805</v>
       </c>
       <c r="B40" t="n">
-        <v>92835</v>
+        <v>79068</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811492</v>
+        <v>810973</v>
       </c>
       <c r="R40" t="n">
-        <v>7393149</v>
+        <v>7392910</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685828</v>
+        <v>128685761</v>
       </c>
       <c r="B41" t="n">
-        <v>78801</v>
+        <v>86984</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811225</v>
+        <v>811014</v>
       </c>
       <c r="R41" t="n">
-        <v>7392837</v>
+        <v>7392891</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4543,6 +4543,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4561,32 +4562,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685814</v>
+        <v>128685798</v>
       </c>
       <c r="B42" t="n">
-        <v>78802</v>
+        <v>92847</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4597,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810773</v>
+        <v>810767</v>
       </c>
       <c r="R42" t="n">
-        <v>7392966</v>
+        <v>7393075</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4659,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685798</v>
+        <v>128685818</v>
       </c>
       <c r="B43" t="n">
-        <v>92847</v>
+        <v>90178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810767</v>
+        <v>811120</v>
       </c>
       <c r="R43" t="n">
-        <v>7393075</v>
+        <v>7392983</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685761</v>
+        <v>128685828</v>
       </c>
       <c r="B45" t="n">
-        <v>86984</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811014</v>
+        <v>811225</v>
       </c>
       <c r="R45" t="n">
-        <v>7392891</v>
+        <v>7392837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4931,7 +4932,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685818</v>
+        <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>90178</v>
+        <v>78802</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811120</v>
+        <v>810773</v>
       </c>
       <c r="R46" t="n">
-        <v>7392983</v>
+        <v>7392966</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685875</v>
+        <v>128685777</v>
       </c>
       <c r="B47" t="n">
-        <v>92829</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811283</v>
+        <v>811015</v>
       </c>
       <c r="R47" t="n">
-        <v>7392844</v>
+        <v>7392800</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B50" t="n">
-        <v>79068</v>
+        <v>92829</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R50" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R51" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685823</v>
+        <v>128685767</v>
       </c>
       <c r="B52" t="n">
-        <v>58097</v>
+        <v>86984</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>3690</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811127</v>
+        <v>811516</v>
       </c>
       <c r="R52" t="n">
-        <v>7392976</v>
+        <v>7393158</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685815</v>
+        <v>128685823</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>58097</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810946</v>
+        <v>811127</v>
       </c>
       <c r="R53" t="n">
-        <v>7392983</v>
+        <v>7392976</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685767</v>
+        <v>128685844</v>
       </c>
       <c r="B54" t="n">
-        <v>86984</v>
+        <v>92835</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811516</v>
+        <v>810873</v>
       </c>
       <c r="R54" t="n">
-        <v>7393158</v>
+        <v>7392973</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685844</v>
+        <v>128685803</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810873</v>
+        <v>810733</v>
       </c>
       <c r="R55" t="n">
-        <v>7392973</v>
+        <v>7393068</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685803</v>
+        <v>128685868</v>
       </c>
       <c r="B56" t="n">
-        <v>92847</v>
+        <v>92835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810733</v>
+        <v>810757</v>
       </c>
       <c r="R56" t="n">
-        <v>7393068</v>
+        <v>7393053</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6017,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685868</v>
+        <v>128685876</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>92829</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810757</v>
+        <v>811269</v>
       </c>
       <c r="R57" t="n">
-        <v>7393053</v>
+        <v>7392821</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B58" t="n">
-        <v>92829</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R58" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685855</v>
+        <v>128685850</v>
       </c>
       <c r="B59" t="n">
         <v>92835</v>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811502</v>
+        <v>810978</v>
       </c>
       <c r="R59" t="n">
-        <v>7393143</v>
+        <v>7392914</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685850</v>
+        <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>92835</v>
+        <v>78802</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810978</v>
+        <v>810946</v>
       </c>
       <c r="R60" t="n">
-        <v>7392914</v>
+        <v>7392983</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B61" t="n">
-        <v>86984</v>
+        <v>90376</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R61" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6503,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685859</v>
+        <v>128685752</v>
       </c>
       <c r="B62" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811498</v>
+        <v>811410</v>
       </c>
       <c r="R62" t="n">
-        <v>7393147</v>
+        <v>7392970</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685789</v>
+        <v>128685788</v>
       </c>
       <c r="B63" t="n">
-        <v>90376</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6286</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811258</v>
+        <v>811107</v>
       </c>
       <c r="R63" t="n">
-        <v>7392822</v>
+        <v>7393022</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6679,7 +6679,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6698,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685812</v>
+        <v>128685771</v>
       </c>
       <c r="B64" t="n">
-        <v>79068</v>
+        <v>86984</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>3690</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6733,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>810948</v>
+        <v>811112</v>
       </c>
       <c r="R64" t="n">
-        <v>7392987</v>
+        <v>7393038</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6777,6 +6776,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6795,32 +6795,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685752</v>
+        <v>128685800</v>
       </c>
       <c r="B65" t="n">
-        <v>79663</v>
+        <v>92847</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811410</v>
+        <v>810861</v>
       </c>
       <c r="R65" t="n">
-        <v>7392970</v>
+        <v>7392976</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685806</v>
+        <v>128685859</v>
       </c>
       <c r="B66" t="n">
-        <v>79068</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811056</v>
+        <v>811498</v>
       </c>
       <c r="R66" t="n">
-        <v>7392881</v>
+        <v>7393147</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685788</v>
+        <v>128685812</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811107</v>
+        <v>810948</v>
       </c>
       <c r="R67" t="n">
-        <v>7393022</v>
+        <v>7392987</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,10 +7086,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685800</v>
+        <v>128685806</v>
       </c>
       <c r="B68" t="n">
-        <v>92847</v>
+        <v>79068</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7097,21 +7097,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>810861</v>
+        <v>811056</v>
       </c>
       <c r="R68" t="n">
-        <v>7392976</v>
+        <v>7392881</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685838</v>
+        <v>128685813</v>
       </c>
       <c r="B69" t="n">
-        <v>82878</v>
+        <v>91606</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810781</v>
+        <v>810934</v>
       </c>
       <c r="R69" t="n">
-        <v>7392936</v>
+        <v>7393019</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685813</v>
+        <v>128685838</v>
       </c>
       <c r="B70" t="n">
-        <v>91606</v>
+        <v>82878</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810934</v>
+        <v>810781</v>
       </c>
       <c r="R70" t="n">
-        <v>7393019</v>
+        <v>7392936</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685780</v>
+        <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>90178</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8164,21 +8164,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811531</v>
+        <v>810744</v>
       </c>
       <c r="R79" t="n">
-        <v>7393153</v>
+        <v>7393058</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685781</v>
+        <v>128685851</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811507</v>
+        <v>811062</v>
       </c>
       <c r="R80" t="n">
-        <v>7393120</v>
+        <v>7392883</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685819</v>
+        <v>128685780</v>
       </c>
       <c r="B81" t="n">
-        <v>90178</v>
+        <v>57727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8358,21 +8358,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4962</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>810744</v>
+        <v>811531</v>
       </c>
       <c r="R81" t="n">
-        <v>7393058</v>
+        <v>7393153</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,32 +8444,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685851</v>
+        <v>128685781</v>
       </c>
       <c r="B82" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811062</v>
+        <v>811507</v>
       </c>
       <c r="R82" t="n">
-        <v>7392883</v>
+        <v>7393120</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B83" t="n">
-        <v>92835</v>
+        <v>90178</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R83" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B84" t="n">
-        <v>90178</v>
+        <v>92835</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685852</v>
+        <v>128685763</v>
       </c>
       <c r="B90" t="n">
-        <v>92835</v>
+        <v>86984</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811057</v>
+        <v>811097</v>
       </c>
       <c r="R90" t="n">
-        <v>7392877</v>
+        <v>7392723</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,6 +9299,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9317,32 +9318,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685801</v>
+        <v>128685796</v>
       </c>
       <c r="B91" t="n">
-        <v>92847</v>
+        <v>92866</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>232140</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9353,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811116</v>
+        <v>810795</v>
       </c>
       <c r="R91" t="n">
-        <v>7392980</v>
+        <v>7393042</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9414,32 +9415,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685763</v>
+        <v>128685852</v>
       </c>
       <c r="B92" t="n">
-        <v>86984</v>
+        <v>92835</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9449,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811097</v>
+        <v>811057</v>
       </c>
       <c r="R92" t="n">
-        <v>7392723</v>
+        <v>7392877</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9493,7 +9494,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9512,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685796</v>
+        <v>128685801</v>
       </c>
       <c r="B93" t="n">
-        <v>92866</v>
+        <v>92847</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>810795</v>
+        <v>811116</v>
       </c>
       <c r="R93" t="n">
-        <v>7393042</v>
+        <v>7392980</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685843</v>
+        <v>128685837</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810858</v>
+        <v>810756</v>
       </c>
       <c r="R2" t="n">
-        <v>7392973</v>
+        <v>7393036</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685837</v>
+        <v>128685836</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810756</v>
+        <v>811057</v>
       </c>
       <c r="R3" t="n">
-        <v>7393036</v>
+        <v>7393046</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685836</v>
+        <v>128685756</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811057</v>
+        <v>811013</v>
       </c>
       <c r="R4" t="n">
-        <v>7393046</v>
+        <v>7393006</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685756</v>
+        <v>128685790</v>
       </c>
       <c r="B5" t="n">
-        <v>79663</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811013</v>
+        <v>810977</v>
       </c>
       <c r="R5" t="n">
-        <v>7393006</v>
+        <v>7393016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685790</v>
+        <v>128685843</v>
       </c>
       <c r="B7" t="n">
-        <v>56917</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810977</v>
+        <v>810858</v>
       </c>
       <c r="R7" t="n">
-        <v>7393016</v>
+        <v>7392973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685769</v>
+        <v>128685874</v>
       </c>
       <c r="B11" t="n">
-        <v>86984</v>
+        <v>92829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810725</v>
+        <v>811502</v>
       </c>
       <c r="R11" t="n">
-        <v>7393066</v>
+        <v>7393150</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685874</v>
+        <v>128685866</v>
       </c>
       <c r="B12" t="n">
-        <v>92829</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811502</v>
+        <v>810789</v>
       </c>
       <c r="R12" t="n">
-        <v>7393150</v>
+        <v>7393036</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B13" t="n">
-        <v>92480</v>
+        <v>86984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R13" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685866</v>
+        <v>128685795</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>92480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810789</v>
+        <v>810915</v>
       </c>
       <c r="R14" t="n">
-        <v>7393036</v>
+        <v>7393042</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685760</v>
+        <v>128685773</v>
       </c>
       <c r="B20" t="n">
-        <v>79634</v>
+        <v>86984</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R20" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2505,6 +2505,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685773</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>86984</v>
+        <v>79634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3690</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811089</v>
+        <v>810920</v>
       </c>
       <c r="R21" t="n">
-        <v>7393040</v>
+        <v>7393003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2602,7 +2603,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685816</v>
+        <v>128685831</v>
       </c>
       <c r="B23" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810920</v>
+        <v>810853</v>
       </c>
       <c r="R23" t="n">
-        <v>7393003</v>
+        <v>7393047</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685831</v>
+        <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810853</v>
+        <v>810920</v>
       </c>
       <c r="R28" t="n">
-        <v>7393047</v>
+        <v>7393003</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685808</v>
+        <v>128685785</v>
       </c>
       <c r="B32" t="n">
-        <v>79068</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811520</v>
+        <v>811518</v>
       </c>
       <c r="R32" t="n">
-        <v>7393156</v>
+        <v>7393070</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685758</v>
+        <v>128685776</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810717</v>
+        <v>810803</v>
       </c>
       <c r="R33" t="n">
-        <v>7393072</v>
+        <v>7392998</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685776</v>
+        <v>128685808</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810803</v>
+        <v>811520</v>
       </c>
       <c r="R34" t="n">
-        <v>7392998</v>
+        <v>7393156</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685785</v>
+        <v>128685758</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811518</v>
+        <v>810717</v>
       </c>
       <c r="R35" t="n">
-        <v>7393070</v>
+        <v>7393072</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685807</v>
+        <v>128685805</v>
       </c>
       <c r="B38" t="n">
         <v>79068</v>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811004</v>
+        <v>810973</v>
       </c>
       <c r="R38" t="n">
-        <v>7392787</v>
+        <v>7392910</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685833</v>
+        <v>128685807</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>79068</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811464</v>
+        <v>811004</v>
       </c>
       <c r="R39" t="n">
-        <v>7393013</v>
+        <v>7392787</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,32 +4367,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685805</v>
+        <v>128685833</v>
       </c>
       <c r="B40" t="n">
-        <v>79068</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810973</v>
+        <v>811464</v>
       </c>
       <c r="R40" t="n">
-        <v>7392910</v>
+        <v>7393013</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685761</v>
+        <v>128685798</v>
       </c>
       <c r="B41" t="n">
-        <v>86984</v>
+        <v>92847</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811014</v>
+        <v>810767</v>
       </c>
       <c r="R41" t="n">
-        <v>7392891</v>
+        <v>7393075</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4543,7 +4543,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4562,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685798</v>
+        <v>128685877</v>
       </c>
       <c r="B42" t="n">
-        <v>92847</v>
+        <v>92829</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4597,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810767</v>
+        <v>811258</v>
       </c>
       <c r="R42" t="n">
-        <v>7393075</v>
+        <v>7392822</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4659,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685818</v>
+        <v>128685761</v>
       </c>
       <c r="B43" t="n">
-        <v>90178</v>
+        <v>86984</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4670,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4962</v>
+        <v>3690</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4694,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811120</v>
+        <v>811014</v>
       </c>
       <c r="R43" t="n">
-        <v>7392983</v>
+        <v>7392891</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4738,6 +4737,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685877</v>
+        <v>128685828</v>
       </c>
       <c r="B44" t="n">
-        <v>92829</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811258</v>
+        <v>811225</v>
       </c>
       <c r="R44" t="n">
-        <v>7392822</v>
+        <v>7392837</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685828</v>
+        <v>128685818</v>
       </c>
       <c r="B45" t="n">
-        <v>78801</v>
+        <v>90178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811225</v>
+        <v>811120</v>
       </c>
       <c r="R45" t="n">
-        <v>7392837</v>
+        <v>7392983</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R47" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685792</v>
+        <v>128685777</v>
       </c>
       <c r="B48" t="n">
-        <v>92860</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811023</v>
+        <v>811015</v>
       </c>
       <c r="R48" t="n">
-        <v>7392776</v>
+        <v>7392800</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,7 +5241,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B49" t="n">
         <v>92860</v>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R49" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685875</v>
+        <v>128685793</v>
       </c>
       <c r="B50" t="n">
-        <v>92829</v>
+        <v>92860</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811283</v>
+        <v>810740</v>
       </c>
       <c r="R50" t="n">
-        <v>7392844</v>
+        <v>7393062</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B51" t="n">
-        <v>79068</v>
+        <v>92829</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R51" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685767</v>
+        <v>128685868</v>
       </c>
       <c r="B52" t="n">
-        <v>86984</v>
+        <v>92835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811516</v>
+        <v>810757</v>
       </c>
       <c r="R52" t="n">
-        <v>7393158</v>
+        <v>7393053</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685823</v>
+        <v>128685876</v>
       </c>
       <c r="B53" t="n">
-        <v>58097</v>
+        <v>92829</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811127</v>
+        <v>811269</v>
       </c>
       <c r="R53" t="n">
-        <v>7392976</v>
+        <v>7392821</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685844</v>
+        <v>128685855</v>
       </c>
       <c r="B54" t="n">
         <v>92835</v>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810873</v>
+        <v>811502</v>
       </c>
       <c r="R54" t="n">
-        <v>7392973</v>
+        <v>7393143</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685803</v>
+        <v>128685850</v>
       </c>
       <c r="B55" t="n">
-        <v>92847</v>
+        <v>92835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810733</v>
+        <v>810978</v>
       </c>
       <c r="R55" t="n">
-        <v>7393068</v>
+        <v>7392914</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685868</v>
+        <v>128685767</v>
       </c>
       <c r="B56" t="n">
-        <v>92835</v>
+        <v>86984</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810757</v>
+        <v>811516</v>
       </c>
       <c r="R56" t="n">
-        <v>7393053</v>
+        <v>7393158</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6017,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685876</v>
+        <v>128685844</v>
       </c>
       <c r="B57" t="n">
-        <v>92829</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811269</v>
+        <v>810873</v>
       </c>
       <c r="R57" t="n">
-        <v>7392821</v>
+        <v>7392973</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685855</v>
+        <v>128685803</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>92847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811502</v>
+        <v>810733</v>
       </c>
       <c r="R58" t="n">
-        <v>7393143</v>
+        <v>7393068</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685850</v>
+        <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>92835</v>
+        <v>58097</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810978</v>
+        <v>811127</v>
       </c>
       <c r="R59" t="n">
-        <v>7392914</v>
+        <v>7392976</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685789</v>
+        <v>128685859</v>
       </c>
       <c r="B61" t="n">
-        <v>90376</v>
+        <v>92835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811258</v>
+        <v>811498</v>
       </c>
       <c r="R61" t="n">
-        <v>7392822</v>
+        <v>7393147</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,7 +6484,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6503,10 +6502,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685752</v>
+        <v>128685771</v>
       </c>
       <c r="B62" t="n">
-        <v>79663</v>
+        <v>86984</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6514,21 +6513,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6537,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811410</v>
+        <v>811112</v>
       </c>
       <c r="R62" t="n">
-        <v>7392970</v>
+        <v>7393038</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6582,6 +6581,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685788</v>
+        <v>128685800</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>92847</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811107</v>
+        <v>810861</v>
       </c>
       <c r="R63" t="n">
-        <v>7393022</v>
+        <v>7392976</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B64" t="n">
-        <v>86984</v>
+        <v>90376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R64" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6795,10 +6795,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685800</v>
+        <v>128685812</v>
       </c>
       <c r="B65" t="n">
-        <v>92847</v>
+        <v>79068</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6806,21 +6806,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810861</v>
+        <v>810948</v>
       </c>
       <c r="R65" t="n">
-        <v>7392976</v>
+        <v>7392987</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6892,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685859</v>
+        <v>128685752</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>79663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811498</v>
+        <v>811410</v>
       </c>
       <c r="R66" t="n">
-        <v>7393147</v>
+        <v>7392970</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685812</v>
+        <v>128685806</v>
       </c>
       <c r="B67" t="n">
         <v>79068</v>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>810948</v>
+        <v>811056</v>
       </c>
       <c r="R67" t="n">
-        <v>7392987</v>
+        <v>7392881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685806</v>
+        <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>79068</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811056</v>
+        <v>811107</v>
       </c>
       <c r="R68" t="n">
-        <v>7392881</v>
+        <v>7393022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685813</v>
+        <v>128685840</v>
       </c>
       <c r="B69" t="n">
-        <v>91606</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810934</v>
+        <v>810762</v>
       </c>
       <c r="R69" t="n">
-        <v>7393019</v>
+        <v>7393078</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685838</v>
+        <v>128685872</v>
       </c>
       <c r="B70" t="n">
-        <v>82878</v>
+        <v>92829</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810781</v>
+        <v>811269</v>
       </c>
       <c r="R70" t="n">
-        <v>7392936</v>
+        <v>7392839</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685840</v>
+        <v>128685856</v>
       </c>
       <c r="B71" t="n">
         <v>92835</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810762</v>
+        <v>811494</v>
       </c>
       <c r="R71" t="n">
-        <v>7393078</v>
+        <v>7393153</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685754</v>
       </c>
       <c r="B72" t="n">
-        <v>92829</v>
+        <v>79663</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>811026</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7393053</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685838</v>
       </c>
       <c r="B73" t="n">
-        <v>92835</v>
+        <v>82878</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>810781</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7392936</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685813</v>
       </c>
       <c r="B74" t="n">
-        <v>79663</v>
+        <v>91606</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7679,21 +7679,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>810934</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7393019</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>90178</v>
+        <v>92835</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R79" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685851</v>
+        <v>128685780</v>
       </c>
       <c r="B80" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811062</v>
+        <v>811531</v>
       </c>
       <c r="R80" t="n">
-        <v>7392883</v>
+        <v>7393153</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685780</v>
+        <v>128685819</v>
       </c>
       <c r="B81" t="n">
-        <v>57727</v>
+        <v>90178</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8358,21 +8358,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811531</v>
+        <v>810744</v>
       </c>
       <c r="R81" t="n">
-        <v>7393153</v>
+        <v>7393058</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685763</v>
+        <v>128685852</v>
       </c>
       <c r="B90" t="n">
-        <v>86984</v>
+        <v>92835</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811097</v>
+        <v>811057</v>
       </c>
       <c r="R90" t="n">
-        <v>7392723</v>
+        <v>7392877</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,7 +9299,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9318,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685796</v>
+        <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>92866</v>
+        <v>92847</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9353,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>810795</v>
+        <v>811116</v>
       </c>
       <c r="R91" t="n">
-        <v>7393042</v>
+        <v>7392980</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9415,32 +9414,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685852</v>
+        <v>128685763</v>
       </c>
       <c r="B92" t="n">
-        <v>92835</v>
+        <v>86984</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9449,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811057</v>
+        <v>811097</v>
       </c>
       <c r="R92" t="n">
-        <v>7392877</v>
+        <v>7392723</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9494,6 +9493,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9512,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685801</v>
+        <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92847</v>
+        <v>92866</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4366</v>
+        <v>232140</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811116</v>
+        <v>810795</v>
       </c>
       <c r="R93" t="n">
-        <v>7392980</v>
+        <v>7393042</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9809,7 +9809,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685849</v>
+        <v>128685863</v>
       </c>
       <c r="B96" t="n">
         <v>92835</v>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810964</v>
+        <v>810854</v>
       </c>
       <c r="R96" t="n">
-        <v>7392920</v>
+        <v>7393015</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685863</v>
+        <v>128685849</v>
       </c>
       <c r="B97" t="n">
         <v>92835</v>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810854</v>
+        <v>810964</v>
       </c>
       <c r="R97" t="n">
-        <v>7393015</v>
+        <v>7392920</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685837</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128685836</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128685756</v>
       </c>
       <c r="B4" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685790</v>
+        <v>128685843</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810977</v>
+        <v>810858</v>
       </c>
       <c r="R5" t="n">
-        <v>7393016</v>
+        <v>7392973</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685783</v>
+        <v>128685790</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>56920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811497</v>
+        <v>810977</v>
       </c>
       <c r="R6" t="n">
-        <v>7393112</v>
+        <v>7393016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685843</v>
+        <v>128685783</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810858</v>
+        <v>811497</v>
       </c>
       <c r="R7" t="n">
-        <v>7392973</v>
+        <v>7393112</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685835</v>
+        <v>128685804</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>92875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811420</v>
+        <v>810710</v>
       </c>
       <c r="R8" t="n">
-        <v>7392954</v>
+        <v>7393058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685804</v>
+        <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92863</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810710</v>
+        <v>811044</v>
       </c>
       <c r="R9" t="n">
-        <v>7393058</v>
+        <v>7392879</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685853</v>
+        <v>128685835</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811044</v>
+        <v>811420</v>
       </c>
       <c r="R10" t="n">
-        <v>7392879</v>
+        <v>7392954</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1556,7 +1556,7 @@
         <v>128685874</v>
       </c>
       <c r="B11" t="n">
-        <v>92829</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685866</v>
+        <v>128685795</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810789</v>
+        <v>810915</v>
       </c>
       <c r="R12" t="n">
-        <v>7393036</v>
+        <v>7393042</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685769</v>
+        <v>128685866</v>
       </c>
       <c r="B13" t="n">
-        <v>86984</v>
+        <v>92863</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810725</v>
+        <v>810789</v>
       </c>
       <c r="R13" t="n">
-        <v>7393066</v>
+        <v>7393036</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>87012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R14" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1944,7 +1944,7 @@
         <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>79068</v>
+        <v>79094</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>86984</v>
+        <v>87012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685753</v>
+        <v>128685773</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>87012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811087</v>
+        <v>811089</v>
       </c>
       <c r="R17" t="n">
-        <v>7393042</v>
+        <v>7393040</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685829</v>
+        <v>128685753</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>79689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685826</v>
+        <v>128685829</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R19" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2426,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685773</v>
+        <v>128685826</v>
       </c>
       <c r="B20" t="n">
-        <v>86984</v>
+        <v>78827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811089</v>
+        <v>811021</v>
       </c>
       <c r="R20" t="n">
-        <v>7393040</v>
+        <v>7392844</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2505,7 +2506,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685778</v>
+        <v>128685854</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>92863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811517</v>
+        <v>811441</v>
       </c>
       <c r="R22" t="n">
-        <v>7393148</v>
+        <v>7393097</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685831</v>
+        <v>128685873</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>92857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810853</v>
+        <v>811303</v>
       </c>
       <c r="R23" t="n">
-        <v>7393047</v>
+        <v>7392893</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685854</v>
+        <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811441</v>
+        <v>811027</v>
       </c>
       <c r="R24" t="n">
-        <v>7393097</v>
+        <v>7393042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685873</v>
+        <v>128685869</v>
       </c>
       <c r="B25" t="n">
-        <v>92829</v>
+        <v>92863</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811303</v>
+        <v>810738</v>
       </c>
       <c r="R25" t="n">
-        <v>7392893</v>
+        <v>7393051</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685802</v>
+        <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>92847</v>
+        <v>78827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811027</v>
+        <v>810853</v>
       </c>
       <c r="R26" t="n">
-        <v>7393042</v>
+        <v>7393047</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685869</v>
+        <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>92835</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810738</v>
+        <v>811517</v>
       </c>
       <c r="R27" t="n">
-        <v>7393051</v>
+        <v>7393148</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3206,7 +3206,7 @@
         <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685839</v>
+        <v>128685799</v>
       </c>
       <c r="B29" t="n">
-        <v>78710</v>
+        <v>92875</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811034</v>
+        <v>810790</v>
       </c>
       <c r="R29" t="n">
-        <v>7393002</v>
+        <v>7392931</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685799</v>
+        <v>128685861</v>
       </c>
       <c r="B30" t="n">
-        <v>92847</v>
+        <v>92863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810790</v>
+        <v>810965</v>
       </c>
       <c r="R30" t="n">
-        <v>7392931</v>
+        <v>7393009</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685861</v>
+        <v>128685839</v>
       </c>
       <c r="B31" t="n">
-        <v>92835</v>
+        <v>78736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810965</v>
+        <v>811034</v>
       </c>
       <c r="R31" t="n">
-        <v>7393009</v>
+        <v>7393002</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685785</v>
+        <v>128685808</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79094</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811518</v>
+        <v>811520</v>
       </c>
       <c r="R32" t="n">
-        <v>7393070</v>
+        <v>7393156</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685776</v>
+        <v>128685758</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79689</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810803</v>
+        <v>810717</v>
       </c>
       <c r="R33" t="n">
-        <v>7392998</v>
+        <v>7393072</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685808</v>
+        <v>128685785</v>
       </c>
       <c r="B34" t="n">
-        <v>79068</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811520</v>
+        <v>811518</v>
       </c>
       <c r="R34" t="n">
-        <v>7393156</v>
+        <v>7393070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685758</v>
+        <v>128685776</v>
       </c>
       <c r="B35" t="n">
-        <v>79663</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810717</v>
+        <v>810803</v>
       </c>
       <c r="R35" t="n">
-        <v>7393072</v>
+        <v>7392998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
         <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685805</v>
+        <v>128685807</v>
       </c>
       <c r="B38" t="n">
-        <v>79068</v>
+        <v>79094</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810973</v>
+        <v>811004</v>
       </c>
       <c r="R38" t="n">
-        <v>7392910</v>
+        <v>7392787</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685807</v>
+        <v>128685833</v>
       </c>
       <c r="B39" t="n">
-        <v>79068</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811004</v>
+        <v>811464</v>
       </c>
       <c r="R39" t="n">
-        <v>7392787</v>
+        <v>7393013</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,32 +4367,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685833</v>
+        <v>128685805</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79094</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811464</v>
+        <v>810973</v>
       </c>
       <c r="R40" t="n">
-        <v>7393013</v>
+        <v>7392910</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685798</v>
+        <v>128685877</v>
       </c>
       <c r="B41" t="n">
-        <v>92847</v>
+        <v>92857</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810767</v>
+        <v>811258</v>
       </c>
       <c r="R41" t="n">
-        <v>7393075</v>
+        <v>7392822</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685877</v>
+        <v>128685761</v>
       </c>
       <c r="B42" t="n">
-        <v>92829</v>
+        <v>87012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811258</v>
+        <v>811014</v>
       </c>
       <c r="R42" t="n">
-        <v>7392822</v>
+        <v>7392891</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4640,6 +4640,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4658,10 +4659,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685761</v>
+        <v>128685828</v>
       </c>
       <c r="B43" t="n">
-        <v>86984</v>
+        <v>78827</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4669,21 +4670,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811014</v>
+        <v>811225</v>
       </c>
       <c r="R43" t="n">
-        <v>7392891</v>
+        <v>7392837</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4737,7 +4738,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685828</v>
+        <v>128685818</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>90206</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811225</v>
+        <v>811120</v>
       </c>
       <c r="R44" t="n">
-        <v>7392837</v>
+        <v>7392983</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,32 +4853,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685818</v>
+        <v>128685798</v>
       </c>
       <c r="B45" t="n">
-        <v>90178</v>
+        <v>92875</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811120</v>
+        <v>810767</v>
       </c>
       <c r="R45" t="n">
-        <v>7392983</v>
+        <v>7393075</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4953,7 +4953,7 @@
         <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B47" t="n">
-        <v>79068</v>
+        <v>92857</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R47" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79094</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R48" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685792</v>
+        <v>128685777</v>
       </c>
       <c r="B49" t="n">
-        <v>92860</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811023</v>
+        <v>811015</v>
       </c>
       <c r="R49" t="n">
-        <v>7392776</v>
+        <v>7392800</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B50" t="n">
-        <v>92860</v>
+        <v>92888</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R50" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685875</v>
+        <v>128685793</v>
       </c>
       <c r="B51" t="n">
-        <v>92829</v>
+        <v>92888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811283</v>
+        <v>810740</v>
       </c>
       <c r="R51" t="n">
-        <v>7392844</v>
+        <v>7393062</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685868</v>
+        <v>128685844</v>
       </c>
       <c r="B52" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810757</v>
+        <v>810873</v>
       </c>
       <c r="R52" t="n">
-        <v>7393053</v>
+        <v>7392973</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685876</v>
+        <v>128685803</v>
       </c>
       <c r="B53" t="n">
-        <v>92829</v>
+        <v>92875</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811269</v>
+        <v>810733</v>
       </c>
       <c r="R53" t="n">
-        <v>7392821</v>
+        <v>7393068</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685855</v>
+        <v>128685868</v>
       </c>
       <c r="B54" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811502</v>
+        <v>810757</v>
       </c>
       <c r="R54" t="n">
-        <v>7393143</v>
+        <v>7393053</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685850</v>
+        <v>128685876</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>92857</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810978</v>
+        <v>811269</v>
       </c>
       <c r="R55" t="n">
-        <v>7392914</v>
+        <v>7392821</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685767</v>
+        <v>128685855</v>
       </c>
       <c r="B56" t="n">
-        <v>86984</v>
+        <v>92863</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811516</v>
+        <v>811502</v>
       </c>
       <c r="R56" t="n">
-        <v>7393158</v>
+        <v>7393143</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685844</v>
+        <v>128685850</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810873</v>
+        <v>810978</v>
       </c>
       <c r="R57" t="n">
-        <v>7392973</v>
+        <v>7392914</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685803</v>
+        <v>128685767</v>
       </c>
       <c r="B58" t="n">
-        <v>92847</v>
+        <v>87012</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810733</v>
+        <v>811516</v>
       </c>
       <c r="R58" t="n">
-        <v>7393068</v>
+        <v>7393158</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6214,7 +6214,7 @@
         <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685859</v>
+        <v>128685771</v>
       </c>
       <c r="B61" t="n">
-        <v>92835</v>
+        <v>87012</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811498</v>
+        <v>811112</v>
       </c>
       <c r="R61" t="n">
-        <v>7393147</v>
+        <v>7393038</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,6 +6484,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6502,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685771</v>
+        <v>128685800</v>
       </c>
       <c r="B62" t="n">
-        <v>86984</v>
+        <v>92875</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6537,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811112</v>
+        <v>810861</v>
       </c>
       <c r="R62" t="n">
-        <v>7393038</v>
+        <v>7392976</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6581,7 +6582,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685800</v>
+        <v>128685859</v>
       </c>
       <c r="B63" t="n">
-        <v>92847</v>
+        <v>92863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6611,21 +6611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>810861</v>
+        <v>811498</v>
       </c>
       <c r="R63" t="n">
-        <v>7392976</v>
+        <v>7393147</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685789</v>
+        <v>128685812</v>
       </c>
       <c r="B64" t="n">
-        <v>90376</v>
+        <v>79094</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811258</v>
+        <v>810948</v>
       </c>
       <c r="R64" t="n">
-        <v>7392822</v>
+        <v>7392987</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6776,7 +6776,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6795,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685812</v>
+        <v>128685752</v>
       </c>
       <c r="B65" t="n">
-        <v>79068</v>
+        <v>79689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810948</v>
+        <v>811410</v>
       </c>
       <c r="R65" t="n">
-        <v>7392987</v>
+        <v>7392970</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6892,32 +6891,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685752</v>
+        <v>128685789</v>
       </c>
       <c r="B66" t="n">
-        <v>79663</v>
+        <v>90404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6926,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811410</v>
+        <v>811258</v>
       </c>
       <c r="R66" t="n">
-        <v>7392970</v>
+        <v>7392822</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6971,6 +6970,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>128685806</v>
       </c>
       <c r="B67" t="n">
-        <v>79068</v>
+        <v>79094</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685840</v>
+        <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>82905</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810762</v>
+        <v>810781</v>
       </c>
       <c r="R69" t="n">
-        <v>7393078</v>
+        <v>7392936</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685872</v>
+        <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>92829</v>
+        <v>91634</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811269</v>
+        <v>810934</v>
       </c>
       <c r="R70" t="n">
-        <v>7392839</v>
+        <v>7393019</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B71" t="n">
-        <v>92835</v>
+        <v>79689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R71" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685754</v>
+        <v>128685840</v>
       </c>
       <c r="B72" t="n">
-        <v>79663</v>
+        <v>92863</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811026</v>
+        <v>810762</v>
       </c>
       <c r="R72" t="n">
-        <v>7393053</v>
+        <v>7393078</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,10 +7571,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685838</v>
+        <v>128685872</v>
       </c>
       <c r="B73" t="n">
-        <v>82878</v>
+        <v>92857</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7582,21 +7582,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>810781</v>
+        <v>811269</v>
       </c>
       <c r="R73" t="n">
-        <v>7392936</v>
+        <v>7392839</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685813</v>
+        <v>128685856</v>
       </c>
       <c r="B74" t="n">
-        <v>91606</v>
+        <v>92863</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>810934</v>
+        <v>811494</v>
       </c>
       <c r="R74" t="n">
-        <v>7393019</v>
+        <v>7393153</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7768,7 +7768,7 @@
         <v>128685864</v>
       </c>
       <c r="B75" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>128685848</v>
       </c>
       <c r="B76" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685780</v>
+        <v>128685819</v>
       </c>
       <c r="B80" t="n">
-        <v>57727</v>
+        <v>90206</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8261,21 +8261,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811531</v>
+        <v>810744</v>
       </c>
       <c r="R80" t="n">
-        <v>7393153</v>
+        <v>7393058</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685819</v>
+        <v>128685780</v>
       </c>
       <c r="B81" t="n">
-        <v>90178</v>
+        <v>57730</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8358,21 +8358,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4962</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>810744</v>
+        <v>811531</v>
       </c>
       <c r="R81" t="n">
-        <v>7393058</v>
+        <v>7393153</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8447,7 +8447,7 @@
         <v>128685781</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B83" t="n">
-        <v>90178</v>
+        <v>79689</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R83" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B84" t="n">
-        <v>92835</v>
+        <v>90206</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R84" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685748</v>
+        <v>128685847</v>
       </c>
       <c r="B85" t="n">
-        <v>79663</v>
+        <v>92863</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810767</v>
+        <v>810944</v>
       </c>
       <c r="R85" t="n">
-        <v>7392968</v>
+        <v>7392948</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8835,7 +8835,7 @@
         <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>86984</v>
+        <v>87012</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>128685852</v>
       </c>
       <c r="B90" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>92847</v>
+        <v>92875</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>128685763</v>
       </c>
       <c r="B92" t="n">
-        <v>86984</v>
+        <v>87012</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92866</v>
+        <v>92894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>86984</v>
+        <v>87012</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685863</v>
+        <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810854</v>
+        <v>810964</v>
       </c>
       <c r="R96" t="n">
-        <v>7393015</v>
+        <v>7392920</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,10 +9906,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685849</v>
+        <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810964</v>
+        <v>810854</v>
       </c>
       <c r="R97" t="n">
-        <v>7392920</v>
+        <v>7393015</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10006,7 +10006,7 @@
         <v>128685834</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685804</v>
+        <v>128685853</v>
       </c>
       <c r="B8" t="n">
-        <v>92875</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810710</v>
+        <v>811044</v>
       </c>
       <c r="R8" t="n">
-        <v>7393058</v>
+        <v>7392879</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685853</v>
+        <v>128685804</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811044</v>
+        <v>810710</v>
       </c>
       <c r="R9" t="n">
-        <v>7392879</v>
+        <v>7393058</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685807</v>
+        <v>128685833</v>
       </c>
       <c r="B38" t="n">
-        <v>79094</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811004</v>
+        <v>811464</v>
       </c>
       <c r="R38" t="n">
-        <v>7392787</v>
+        <v>7393013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685833</v>
+        <v>128685807</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>79094</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811464</v>
+        <v>811004</v>
       </c>
       <c r="R39" t="n">
-        <v>7393013</v>
+        <v>7392787</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685877</v>
+        <v>128685818</v>
       </c>
       <c r="B41" t="n">
-        <v>92857</v>
+        <v>90206</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811258</v>
+        <v>811120</v>
       </c>
       <c r="R41" t="n">
-        <v>7392822</v>
+        <v>7392983</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685761</v>
+        <v>128685798</v>
       </c>
       <c r="B42" t="n">
-        <v>87012</v>
+        <v>92875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811014</v>
+        <v>810767</v>
       </c>
       <c r="R42" t="n">
-        <v>7392891</v>
+        <v>7393075</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4640,7 +4640,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4659,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685828</v>
+        <v>128685877</v>
       </c>
       <c r="B43" t="n">
-        <v>78827</v>
+        <v>92857</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4670,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4694,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811225</v>
+        <v>811258</v>
       </c>
       <c r="R43" t="n">
-        <v>7392837</v>
+        <v>7392822</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4756,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685818</v>
+        <v>128685761</v>
       </c>
       <c r="B44" t="n">
-        <v>90206</v>
+        <v>87012</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4962</v>
+        <v>3690</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811120</v>
+        <v>811014</v>
       </c>
       <c r="R44" t="n">
-        <v>7392983</v>
+        <v>7392891</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4835,6 +4834,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4853,32 +4853,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685798</v>
+        <v>128685828</v>
       </c>
       <c r="B45" t="n">
-        <v>92875</v>
+        <v>78827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810767</v>
+        <v>811225</v>
       </c>
       <c r="R45" t="n">
-        <v>7393075</v>
+        <v>7392837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B61" t="n">
-        <v>87012</v>
+        <v>90404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R61" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685800</v>
+        <v>128685806</v>
       </c>
       <c r="B62" t="n">
-        <v>92875</v>
+        <v>79094</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810861</v>
+        <v>811056</v>
       </c>
       <c r="R62" t="n">
-        <v>7392976</v>
+        <v>7392881</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685859</v>
+        <v>128685788</v>
       </c>
       <c r="B63" t="n">
-        <v>92863</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811498</v>
+        <v>811107</v>
       </c>
       <c r="R63" t="n">
-        <v>7393147</v>
+        <v>7393022</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685812</v>
+        <v>128685771</v>
       </c>
       <c r="B64" t="n">
-        <v>79094</v>
+        <v>87012</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>3690</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>810948</v>
+        <v>811112</v>
       </c>
       <c r="R64" t="n">
-        <v>7392987</v>
+        <v>7393038</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6776,6 +6776,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6794,32 +6795,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685752</v>
+        <v>128685800</v>
       </c>
       <c r="B65" t="n">
-        <v>79689</v>
+        <v>92875</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811410</v>
+        <v>810861</v>
       </c>
       <c r="R65" t="n">
-        <v>7392970</v>
+        <v>7392976</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6891,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685789</v>
+        <v>128685859</v>
       </c>
       <c r="B66" t="n">
-        <v>90404</v>
+        <v>92863</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6926,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811258</v>
+        <v>811498</v>
       </c>
       <c r="R66" t="n">
-        <v>7392822</v>
+        <v>7393147</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6970,7 +6971,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685806</v>
+        <v>128685812</v>
       </c>
       <c r="B67" t="n">
         <v>79094</v>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811056</v>
+        <v>810948</v>
       </c>
       <c r="R67" t="n">
-        <v>7392881</v>
+        <v>7392987</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,10 +7086,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685788</v>
+        <v>128685752</v>
       </c>
       <c r="B68" t="n">
-        <v>57730</v>
+        <v>79689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7097,21 +7097,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811107</v>
+        <v>811410</v>
       </c>
       <c r="R68" t="n">
-        <v>7393022</v>
+        <v>7392970</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685851</v>
+        <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>92863</v>
+        <v>90206</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811062</v>
+        <v>810744</v>
       </c>
       <c r="R79" t="n">
-        <v>7392883</v>
+        <v>7393058</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B80" t="n">
-        <v>90206</v>
+        <v>92863</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R80" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685764</v>
+        <v>128685852</v>
       </c>
       <c r="B89" t="n">
-        <v>87012</v>
+        <v>92863</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810867</v>
+        <v>811057</v>
       </c>
       <c r="R89" t="n">
-        <v>7392967</v>
+        <v>7392877</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685852</v>
+        <v>128685801</v>
       </c>
       <c r="B90" t="n">
-        <v>92863</v>
+        <v>92875</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9231,21 +9231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811057</v>
+        <v>811116</v>
       </c>
       <c r="R90" t="n">
-        <v>7392877</v>
+        <v>7392980</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B91" t="n">
-        <v>92875</v>
+        <v>87012</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R91" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,6 +9396,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9414,7 +9415,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685763</v>
+        <v>128685764</v>
       </c>
       <c r="B92" t="n">
         <v>87012</v>
@@ -9449,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811097</v>
+        <v>810867</v>
       </c>
       <c r="R92" t="n">
-        <v>7392723</v>
+        <v>7392967</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9493,7 +9494,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685770</v>
+        <v>128685751</v>
       </c>
       <c r="B94" t="n">
-        <v>87012</v>
+        <v>79689</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811050</v>
+        <v>811254</v>
       </c>
       <c r="R94" t="n">
-        <v>7393050</v>
+        <v>7392831</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,18 +9682,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9712,10 +9706,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685751</v>
+        <v>128685770</v>
       </c>
       <c r="B95" t="n">
-        <v>79689</v>
+        <v>87012</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9723,21 +9717,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9747,10 +9741,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811254</v>
+        <v>811050</v>
       </c>
       <c r="R95" t="n">
-        <v>7392831</v>
+        <v>7393050</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9785,12 +9779,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128685837</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128685836</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128685756</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128685843</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128685790</v>
       </c>
       <c r="B6" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128685783</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685853</v>
+        <v>128685804</v>
       </c>
       <c r="B8" t="n">
-        <v>92863</v>
+        <v>92881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811044</v>
+        <v>810710</v>
       </c>
       <c r="R8" t="n">
-        <v>7392879</v>
+        <v>7393058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685804</v>
+        <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810710</v>
+        <v>811044</v>
       </c>
       <c r="R9" t="n">
-        <v>7393058</v>
+        <v>7392879</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1459,7 +1459,7 @@
         <v>128685835</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685874</v>
+        <v>128685795</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811502</v>
+        <v>810915</v>
       </c>
       <c r="R11" t="n">
-        <v>7393150</v>
+        <v>7393042</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685795</v>
+        <v>128685874</v>
       </c>
       <c r="B12" t="n">
-        <v>92508</v>
+        <v>92863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810915</v>
+        <v>811502</v>
       </c>
       <c r="R12" t="n">
-        <v>7393042</v>
+        <v>7393150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1750,7 +1750,7 @@
         <v>128685866</v>
       </c>
       <c r="B13" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128685769</v>
       </c>
       <c r="B14" t="n">
-        <v>87012</v>
+        <v>87018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>79094</v>
+        <v>79099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87012</v>
+        <v>87018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>128685773</v>
       </c>
       <c r="B17" t="n">
-        <v>87012</v>
+        <v>87018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685753</v>
+        <v>128685760</v>
       </c>
       <c r="B18" t="n">
-        <v>79689</v>
+        <v>79665</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R18" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685829</v>
+        <v>128685753</v>
       </c>
       <c r="B19" t="n">
-        <v>78827</v>
+        <v>79694</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R19" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685826</v>
+        <v>128685829</v>
       </c>
       <c r="B20" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R20" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685826</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>78832</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810920</v>
+        <v>811021</v>
       </c>
       <c r="R21" t="n">
-        <v>7393003</v>
+        <v>7392844</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2624,7 +2624,7 @@
         <v>128685854</v>
       </c>
       <c r="B22" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>128685873</v>
       </c>
       <c r="B23" t="n">
-        <v>92857</v>
+        <v>92863</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128685869</v>
       </c>
       <c r="B25" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685799</v>
+        <v>128685839</v>
       </c>
       <c r="B29" t="n">
-        <v>92875</v>
+        <v>78741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810790</v>
+        <v>811034</v>
       </c>
       <c r="R29" t="n">
-        <v>7392931</v>
+        <v>7393002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685861</v>
+        <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>92863</v>
+        <v>92881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810965</v>
+        <v>810790</v>
       </c>
       <c r="R30" t="n">
-        <v>7393009</v>
+        <v>7392931</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685839</v>
+        <v>128685861</v>
       </c>
       <c r="B31" t="n">
-        <v>78736</v>
+        <v>92869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811034</v>
+        <v>810965</v>
       </c>
       <c r="R31" t="n">
-        <v>7393002</v>
+        <v>7393009</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3594,7 +3594,7 @@
         <v>128685808</v>
       </c>
       <c r="B32" t="n">
-        <v>79094</v>
+        <v>79099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>128685758</v>
       </c>
       <c r="B33" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>128685785</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>128685776</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685857</v>
+        <v>128685807</v>
       </c>
       <c r="B36" t="n">
-        <v>92863</v>
+        <v>79099</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811492</v>
+        <v>811004</v>
       </c>
       <c r="R36" t="n">
-        <v>7393149</v>
+        <v>7392787</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685841</v>
+        <v>128685833</v>
       </c>
       <c r="B37" t="n">
-        <v>92863</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810812</v>
+        <v>811464</v>
       </c>
       <c r="R37" t="n">
-        <v>7392934</v>
+        <v>7393013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685833</v>
+        <v>128685805</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79099</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811464</v>
+        <v>810973</v>
       </c>
       <c r="R38" t="n">
-        <v>7393013</v>
+        <v>7392910</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685807</v>
+        <v>128685857</v>
       </c>
       <c r="B39" t="n">
-        <v>79094</v>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811004</v>
+        <v>811492</v>
       </c>
       <c r="R39" t="n">
-        <v>7392787</v>
+        <v>7393149</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685805</v>
+        <v>128685841</v>
       </c>
       <c r="B40" t="n">
-        <v>79094</v>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810973</v>
+        <v>810812</v>
       </c>
       <c r="R40" t="n">
-        <v>7392910</v>
+        <v>7392934</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685818</v>
+        <v>128685828</v>
       </c>
       <c r="B41" t="n">
-        <v>90206</v>
+        <v>78832</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4962</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811120</v>
+        <v>811225</v>
       </c>
       <c r="R41" t="n">
-        <v>7392983</v>
+        <v>7392837</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685798</v>
+        <v>128685818</v>
       </c>
       <c r="B42" t="n">
-        <v>92875</v>
+        <v>90212</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810767</v>
+        <v>811120</v>
       </c>
       <c r="R42" t="n">
-        <v>7393075</v>
+        <v>7392983</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685877</v>
+        <v>128685798</v>
       </c>
       <c r="B43" t="n">
-        <v>92857</v>
+        <v>92881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811258</v>
+        <v>810767</v>
       </c>
       <c r="R43" t="n">
-        <v>7392822</v>
+        <v>7393075</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685761</v>
+        <v>128685877</v>
       </c>
       <c r="B44" t="n">
-        <v>87012</v>
+        <v>92863</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811014</v>
+        <v>811258</v>
       </c>
       <c r="R44" t="n">
-        <v>7392891</v>
+        <v>7392822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4834,7 +4834,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4853,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685828</v>
+        <v>128685761</v>
       </c>
       <c r="B45" t="n">
-        <v>78827</v>
+        <v>87018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4863,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4887,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811225</v>
+        <v>811014</v>
       </c>
       <c r="R45" t="n">
-        <v>7392837</v>
+        <v>7392891</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4932,6 +4931,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685875</v>
+        <v>128685777</v>
       </c>
       <c r="B47" t="n">
-        <v>92857</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811283</v>
+        <v>811015</v>
       </c>
       <c r="R47" t="n">
-        <v>7392844</v>
+        <v>7392800</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,32 +5144,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685809</v>
+        <v>128685792</v>
       </c>
       <c r="B48" t="n">
-        <v>79094</v>
+        <v>92894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6434</v>
+        <v>3100</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811105</v>
+        <v>811023</v>
       </c>
       <c r="R48" t="n">
-        <v>7393054</v>
+        <v>7392776</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685777</v>
+        <v>128685793</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>92894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811015</v>
+        <v>810740</v>
       </c>
       <c r="R49" t="n">
-        <v>7392800</v>
+        <v>7393062</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685792</v>
+        <v>128685875</v>
       </c>
       <c r="B50" t="n">
-        <v>92888</v>
+        <v>92863</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811023</v>
+        <v>811283</v>
       </c>
       <c r="R50" t="n">
-        <v>7392776</v>
+        <v>7392844</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685793</v>
+        <v>128685809</v>
       </c>
       <c r="B51" t="n">
-        <v>92888</v>
+        <v>79099</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>810740</v>
+        <v>811105</v>
       </c>
       <c r="R51" t="n">
-        <v>7393062</v>
+        <v>7393054</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685844</v>
+        <v>128685815</v>
       </c>
       <c r="B52" t="n">
-        <v>92863</v>
+        <v>78833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810873</v>
+        <v>810946</v>
       </c>
       <c r="R52" t="n">
-        <v>7392973</v>
+        <v>7392983</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685803</v>
+        <v>128685823</v>
       </c>
       <c r="B53" t="n">
-        <v>92875</v>
+        <v>58105</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810733</v>
+        <v>811127</v>
       </c>
       <c r="R53" t="n">
-        <v>7393068</v>
+        <v>7392976</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685868</v>
+        <v>128685767</v>
       </c>
       <c r="B54" t="n">
-        <v>92863</v>
+        <v>87018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810757</v>
+        <v>811516</v>
       </c>
       <c r="R54" t="n">
-        <v>7393053</v>
+        <v>7393158</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685876</v>
+        <v>128685844</v>
       </c>
       <c r="B55" t="n">
-        <v>92857</v>
+        <v>92869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811269</v>
+        <v>810873</v>
       </c>
       <c r="R55" t="n">
-        <v>7392821</v>
+        <v>7392973</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685855</v>
+        <v>128685803</v>
       </c>
       <c r="B56" t="n">
-        <v>92863</v>
+        <v>92881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811502</v>
+        <v>810733</v>
       </c>
       <c r="R56" t="n">
-        <v>7393143</v>
+        <v>7393068</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685850</v>
+        <v>128685868</v>
       </c>
       <c r="B57" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810978</v>
+        <v>810757</v>
       </c>
       <c r="R57" t="n">
-        <v>7392914</v>
+        <v>7393053</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685767</v>
+        <v>128685876</v>
       </c>
       <c r="B58" t="n">
-        <v>87012</v>
+        <v>92863</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811516</v>
+        <v>811269</v>
       </c>
       <c r="R58" t="n">
-        <v>7393158</v>
+        <v>7392821</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685823</v>
+        <v>128685855</v>
       </c>
       <c r="B59" t="n">
-        <v>58100</v>
+        <v>92869</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811127</v>
+        <v>811502</v>
       </c>
       <c r="R59" t="n">
-        <v>7392976</v>
+        <v>7393143</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685815</v>
+        <v>128685850</v>
       </c>
       <c r="B60" t="n">
-        <v>78828</v>
+        <v>92869</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810946</v>
+        <v>810978</v>
       </c>
       <c r="R60" t="n">
-        <v>7392983</v>
+        <v>7392914</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685789</v>
+        <v>128685788</v>
       </c>
       <c r="B61" t="n">
-        <v>90404</v>
+        <v>57735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811258</v>
+        <v>811107</v>
       </c>
       <c r="R61" t="n">
-        <v>7392822</v>
+        <v>7393022</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,7 +6484,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6503,32 +6502,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685806</v>
+        <v>128685771</v>
       </c>
       <c r="B62" t="n">
-        <v>79094</v>
+        <v>87018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>3690</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6537,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811056</v>
+        <v>811112</v>
       </c>
       <c r="R62" t="n">
-        <v>7392881</v>
+        <v>7393038</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6582,6 +6581,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685788</v>
+        <v>128685800</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>92881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811107</v>
+        <v>810861</v>
       </c>
       <c r="R63" t="n">
-        <v>7393022</v>
+        <v>7392976</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685771</v>
+        <v>128685859</v>
       </c>
       <c r="B64" t="n">
-        <v>87012</v>
+        <v>92869</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811112</v>
+        <v>811498</v>
       </c>
       <c r="R64" t="n">
-        <v>7393038</v>
+        <v>7393147</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6776,7 +6776,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6795,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685800</v>
+        <v>128685789</v>
       </c>
       <c r="B65" t="n">
-        <v>92875</v>
+        <v>90410</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810861</v>
+        <v>811258</v>
       </c>
       <c r="R65" t="n">
-        <v>7392976</v>
+        <v>7392822</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6874,6 +6873,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685859</v>
+        <v>128685812</v>
       </c>
       <c r="B66" t="n">
-        <v>92863</v>
+        <v>79099</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811498</v>
+        <v>810948</v>
       </c>
       <c r="R66" t="n">
-        <v>7393147</v>
+        <v>7392987</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685812</v>
+        <v>128685752</v>
       </c>
       <c r="B67" t="n">
-        <v>79094</v>
+        <v>79694</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>810948</v>
+        <v>811410</v>
       </c>
       <c r="R67" t="n">
-        <v>7392987</v>
+        <v>7392970</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685752</v>
+        <v>128685806</v>
       </c>
       <c r="B68" t="n">
-        <v>79689</v>
+        <v>79099</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811410</v>
+        <v>811056</v>
       </c>
       <c r="R68" t="n">
-        <v>7392970</v>
+        <v>7392881</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
         <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>91634</v>
+        <v>91640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685754</v>
+        <v>128685840</v>
       </c>
       <c r="B71" t="n">
-        <v>79689</v>
+        <v>92869</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811026</v>
+        <v>810762</v>
       </c>
       <c r="R71" t="n">
-        <v>7393053</v>
+        <v>7393078</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685840</v>
+        <v>128685872</v>
       </c>
       <c r="B72" t="n">
         <v>92863</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810762</v>
+        <v>811269</v>
       </c>
       <c r="R72" t="n">
-        <v>7393078</v>
+        <v>7392839</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685872</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>92857</v>
+        <v>92869</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811269</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7392839</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92863</v>
+        <v>79694</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7768,7 +7768,7 @@
         <v>128685864</v>
       </c>
       <c r="B75" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>128685848</v>
       </c>
       <c r="B76" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>90206</v>
+        <v>90212</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128685851</v>
       </c>
       <c r="B80" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>128685780</v>
       </c>
       <c r="B81" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>128685781</v>
       </c>
       <c r="B82" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685748</v>
+        <v>128685847</v>
       </c>
       <c r="B83" t="n">
-        <v>79689</v>
+        <v>92869</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810767</v>
+        <v>810944</v>
       </c>
       <c r="R83" t="n">
-        <v>7392968</v>
+        <v>7392948</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B84" t="n">
-        <v>90206</v>
+        <v>79694</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8649,21 +8649,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B85" t="n">
-        <v>92863</v>
+        <v>90212</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R85" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8835,7 +8835,7 @@
         <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685852</v>
+        <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>92863</v>
+        <v>87018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811057</v>
+        <v>810867</v>
       </c>
       <c r="R89" t="n">
-        <v>7392877</v>
+        <v>7392967</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685801</v>
+        <v>128685852</v>
       </c>
       <c r="B90" t="n">
-        <v>92875</v>
+        <v>92869</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9231,21 +9231,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811116</v>
+        <v>811057</v>
       </c>
       <c r="R90" t="n">
-        <v>7392980</v>
+        <v>7392877</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>87012</v>
+        <v>92881</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R91" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,7 +9396,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9414,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685764</v>
+        <v>128685763</v>
       </c>
       <c r="B92" t="n">
-        <v>87012</v>
+        <v>87018</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9450,10 +9449,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>810867</v>
+        <v>811097</v>
       </c>
       <c r="R92" t="n">
-        <v>7392967</v>
+        <v>7392723</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9494,6 +9493,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92894</v>
+        <v>92900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685751</v>
+        <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>79689</v>
+        <v>87018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811254</v>
+        <v>811050</v>
       </c>
       <c r="R94" t="n">
-        <v>7392831</v>
+        <v>7393050</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,12 +9682,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9706,10 +9712,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685770</v>
+        <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>87012</v>
+        <v>79694</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9717,21 +9723,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9741,10 +9747,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811050</v>
+        <v>811254</v>
       </c>
       <c r="R95" t="n">
-        <v>7393050</v>
+        <v>7392831</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9779,18 +9785,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>128685834</v>
       </c>
       <c r="B98" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685837</v>
+        <v>128685756</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810756</v>
+        <v>811013</v>
       </c>
       <c r="R2" t="n">
-        <v>7393036</v>
+        <v>7393006</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685836</v>
+        <v>128685843</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811057</v>
+        <v>810858</v>
       </c>
       <c r="R3" t="n">
-        <v>7393046</v>
+        <v>7392973</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685756</v>
+        <v>128685837</v>
       </c>
       <c r="B4" t="n">
-        <v>79694</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811013</v>
+        <v>810756</v>
       </c>
       <c r="R4" t="n">
-        <v>7393006</v>
+        <v>7393036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685843</v>
+        <v>128685836</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810858</v>
+        <v>811057</v>
       </c>
       <c r="R5" t="n">
-        <v>7392973</v>
+        <v>7393046</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685790</v>
+        <v>128685783</v>
       </c>
       <c r="B6" t="n">
-        <v>56925</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810977</v>
+        <v>811497</v>
       </c>
       <c r="R6" t="n">
-        <v>7393016</v>
+        <v>7393112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685783</v>
+        <v>128685790</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>56926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811497</v>
+        <v>810977</v>
       </c>
       <c r="R7" t="n">
-        <v>7393112</v>
+        <v>7393016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685804</v>
+        <v>128685835</v>
       </c>
       <c r="B8" t="n">
-        <v>92881</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810710</v>
+        <v>811420</v>
       </c>
       <c r="R8" t="n">
-        <v>7393058</v>
+        <v>7392954</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1362,7 +1362,7 @@
         <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685835</v>
+        <v>128685804</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>92882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811420</v>
+        <v>810710</v>
       </c>
       <c r="R10" t="n">
-        <v>7392954</v>
+        <v>7393058</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B11" t="n">
-        <v>92514</v>
+        <v>87019</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R11" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685874</v>
+        <v>128685810</v>
       </c>
       <c r="B12" t="n">
-        <v>92863</v>
+        <v>79100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811502</v>
+        <v>811027</v>
       </c>
       <c r="R12" t="n">
-        <v>7393150</v>
+        <v>7393051</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685866</v>
+        <v>128685795</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>92515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810789</v>
+        <v>810915</v>
       </c>
       <c r="R13" t="n">
-        <v>7393036</v>
+        <v>7393042</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685769</v>
+        <v>128685866</v>
       </c>
       <c r="B14" t="n">
-        <v>87018</v>
+        <v>92870</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810725</v>
+        <v>810789</v>
       </c>
       <c r="R14" t="n">
-        <v>7393066</v>
+        <v>7393036</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685810</v>
+        <v>128685874</v>
       </c>
       <c r="B15" t="n">
-        <v>79099</v>
+        <v>92864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811027</v>
+        <v>811502</v>
       </c>
       <c r="R15" t="n">
-        <v>7393051</v>
+        <v>7393150</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87018</v>
+        <v>87019</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685773</v>
+        <v>128685760</v>
       </c>
       <c r="B17" t="n">
-        <v>87018</v>
+        <v>79666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3690</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811089</v>
+        <v>810920</v>
       </c>
       <c r="R17" t="n">
-        <v>7393040</v>
+        <v>7393003</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685760</v>
+        <v>128685773</v>
       </c>
       <c r="B18" t="n">
-        <v>79665</v>
+        <v>87019</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2312,6 +2311,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>128685753</v>
       </c>
       <c r="B19" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>128685829</v>
       </c>
       <c r="B20" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>128685826</v>
       </c>
       <c r="B21" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685854</v>
+        <v>128685778</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811441</v>
+        <v>811517</v>
       </c>
       <c r="R22" t="n">
-        <v>7393097</v>
+        <v>7393148</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685873</v>
+        <v>128685869</v>
       </c>
       <c r="B23" t="n">
-        <v>92863</v>
+        <v>92870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811303</v>
+        <v>810738</v>
       </c>
       <c r="R23" t="n">
-        <v>7392893</v>
+        <v>7393051</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685869</v>
+        <v>128685854</v>
       </c>
       <c r="B25" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810738</v>
+        <v>811441</v>
       </c>
       <c r="R25" t="n">
-        <v>7393051</v>
+        <v>7393097</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685831</v>
+        <v>128685873</v>
       </c>
       <c r="B26" t="n">
-        <v>78832</v>
+        <v>92864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3020,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810853</v>
+        <v>811303</v>
       </c>
       <c r="R26" t="n">
-        <v>7393047</v>
+        <v>7392893</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685778</v>
+        <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>78833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811517</v>
+        <v>810853</v>
       </c>
       <c r="R27" t="n">
-        <v>7393148</v>
+        <v>7393047</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3206,7 +3206,7 @@
         <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>128685839</v>
       </c>
       <c r="B29" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685799</v>
+        <v>128685758</v>
       </c>
       <c r="B30" t="n">
-        <v>92881</v>
+        <v>79695</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810790</v>
+        <v>810717</v>
       </c>
       <c r="R30" t="n">
-        <v>7392931</v>
+        <v>7393072</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3497,7 +3497,7 @@
         <v>128685861</v>
       </c>
       <c r="B31" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685808</v>
+        <v>128685799</v>
       </c>
       <c r="B32" t="n">
-        <v>79099</v>
+        <v>92882</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811520</v>
+        <v>810790</v>
       </c>
       <c r="R32" t="n">
-        <v>7393156</v>
+        <v>7392931</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685758</v>
+        <v>128685785</v>
       </c>
       <c r="B33" t="n">
-        <v>79694</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810717</v>
+        <v>811518</v>
       </c>
       <c r="R33" t="n">
-        <v>7393072</v>
+        <v>7393070</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685785</v>
+        <v>128685776</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811518</v>
+        <v>810803</v>
       </c>
       <c r="R34" t="n">
-        <v>7393070</v>
+        <v>7392998</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685776</v>
+        <v>128685808</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>79100</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810803</v>
+        <v>811520</v>
       </c>
       <c r="R35" t="n">
-        <v>7392998</v>
+        <v>7393156</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685807</v>
+        <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>79099</v>
+        <v>92870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811004</v>
+        <v>811492</v>
       </c>
       <c r="R36" t="n">
-        <v>7392787</v>
+        <v>7393149</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685833</v>
+        <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811464</v>
+        <v>810812</v>
       </c>
       <c r="R37" t="n">
-        <v>7393013</v>
+        <v>7392934</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685805</v>
+        <v>128685833</v>
       </c>
       <c r="B38" t="n">
-        <v>79099</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810973</v>
+        <v>811464</v>
       </c>
       <c r="R38" t="n">
-        <v>7392910</v>
+        <v>7393013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685857</v>
+        <v>128685807</v>
       </c>
       <c r="B39" t="n">
-        <v>92869</v>
+        <v>79100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811492</v>
+        <v>811004</v>
       </c>
       <c r="R39" t="n">
-        <v>7393149</v>
+        <v>7392787</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685841</v>
+        <v>128685805</v>
       </c>
       <c r="B40" t="n">
-        <v>92869</v>
+        <v>79100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810812</v>
+        <v>810973</v>
       </c>
       <c r="R40" t="n">
-        <v>7392934</v>
+        <v>7392910</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4467,7 +4467,7 @@
         <v>128685828</v>
       </c>
       <c r="B41" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4561,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685818</v>
+        <v>128685798</v>
       </c>
       <c r="B42" t="n">
-        <v>90212</v>
+        <v>92882</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811120</v>
+        <v>810767</v>
       </c>
       <c r="R42" t="n">
-        <v>7392983</v>
+        <v>7393075</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685798</v>
+        <v>128685877</v>
       </c>
       <c r="B43" t="n">
-        <v>92881</v>
+        <v>92864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810767</v>
+        <v>811258</v>
       </c>
       <c r="R43" t="n">
-        <v>7393075</v>
+        <v>7392822</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685877</v>
+        <v>128685814</v>
       </c>
       <c r="B44" t="n">
-        <v>92863</v>
+        <v>78834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811258</v>
+        <v>810773</v>
       </c>
       <c r="R44" t="n">
-        <v>7392822</v>
+        <v>7392966</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4855,7 +4855,7 @@
         <v>128685761</v>
       </c>
       <c r="B45" t="n">
-        <v>87018</v>
+        <v>87019</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685814</v>
+        <v>128685818</v>
       </c>
       <c r="B46" t="n">
-        <v>78833</v>
+        <v>90213</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810773</v>
+        <v>811120</v>
       </c>
       <c r="R46" t="n">
-        <v>7392966</v>
+        <v>7392983</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685777</v>
+        <v>128685792</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>92895</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811015</v>
+        <v>811023</v>
       </c>
       <c r="R47" t="n">
-        <v>7392800</v>
+        <v>7392776</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B48" t="n">
-        <v>92894</v>
+        <v>92895</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R48" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,32 +5241,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685793</v>
+        <v>128685809</v>
       </c>
       <c r="B49" t="n">
-        <v>92894</v>
+        <v>79100</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810740</v>
+        <v>811105</v>
       </c>
       <c r="R49" t="n">
-        <v>7393062</v>
+        <v>7393054</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685875</v>
+        <v>128685777</v>
       </c>
       <c r="B50" t="n">
-        <v>92863</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811283</v>
+        <v>811015</v>
       </c>
       <c r="R50" t="n">
-        <v>7392844</v>
+        <v>7392800</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B51" t="n">
-        <v>79099</v>
+        <v>92864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R51" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5535,7 +5535,7 @@
         <v>128685815</v>
       </c>
       <c r="B52" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685823</v>
+        <v>128685767</v>
       </c>
       <c r="B53" t="n">
-        <v>58105</v>
+        <v>87019</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>3690</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811127</v>
+        <v>811516</v>
       </c>
       <c r="R53" t="n">
-        <v>7392976</v>
+        <v>7393158</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685767</v>
+        <v>128685844</v>
       </c>
       <c r="B54" t="n">
-        <v>87018</v>
+        <v>92870</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811516</v>
+        <v>810873</v>
       </c>
       <c r="R54" t="n">
-        <v>7393158</v>
+        <v>7392973</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,10 +5823,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685844</v>
+        <v>128685803</v>
       </c>
       <c r="B55" t="n">
-        <v>92869</v>
+        <v>92882</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5834,21 +5834,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810873</v>
+        <v>810733</v>
       </c>
       <c r="R55" t="n">
-        <v>7392973</v>
+        <v>7393068</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685803</v>
+        <v>128685850</v>
       </c>
       <c r="B56" t="n">
-        <v>92881</v>
+        <v>92870</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810733</v>
+        <v>810978</v>
       </c>
       <c r="R56" t="n">
-        <v>7393068</v>
+        <v>7392914</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6017,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685868</v>
+        <v>128685876</v>
       </c>
       <c r="B57" t="n">
-        <v>92869</v>
+        <v>92864</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810757</v>
+        <v>811269</v>
       </c>
       <c r="R57" t="n">
-        <v>7393053</v>
+        <v>7392821</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B58" t="n">
-        <v>92863</v>
+        <v>92870</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R58" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685855</v>
+        <v>128685868</v>
       </c>
       <c r="B59" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811502</v>
+        <v>810757</v>
       </c>
       <c r="R59" t="n">
-        <v>7393143</v>
+        <v>7393053</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,10 +6308,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685850</v>
+        <v>128685823</v>
       </c>
       <c r="B60" t="n">
-        <v>92869</v>
+        <v>58106</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6319,21 +6319,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810978</v>
+        <v>811127</v>
       </c>
       <c r="R60" t="n">
-        <v>7392914</v>
+        <v>7392976</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685788</v>
+        <v>128685752</v>
       </c>
       <c r="B61" t="n">
-        <v>57735</v>
+        <v>79695</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811107</v>
+        <v>811410</v>
       </c>
       <c r="R61" t="n">
-        <v>7393022</v>
+        <v>7392970</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6502,32 +6502,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685771</v>
+        <v>128685859</v>
       </c>
       <c r="B62" t="n">
-        <v>87018</v>
+        <v>92870</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811112</v>
+        <v>811498</v>
       </c>
       <c r="R62" t="n">
-        <v>7393038</v>
+        <v>7393147</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6581,7 +6581,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6603,7 +6602,7 @@
         <v>128685800</v>
       </c>
       <c r="B63" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6697,32 +6696,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685859</v>
+        <v>128685788</v>
       </c>
       <c r="B64" t="n">
-        <v>92869</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6731,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811498</v>
+        <v>811107</v>
       </c>
       <c r="R64" t="n">
-        <v>7393147</v>
+        <v>7393022</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,32 +6793,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685789</v>
+        <v>128685771</v>
       </c>
       <c r="B65" t="n">
-        <v>90410</v>
+        <v>87019</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6828,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811258</v>
+        <v>811112</v>
       </c>
       <c r="R65" t="n">
-        <v>7392822</v>
+        <v>7393038</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6895,7 +6894,7 @@
         <v>128685812</v>
       </c>
       <c r="B66" t="n">
-        <v>79099</v>
+        <v>79100</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6989,32 +6988,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685752</v>
+        <v>128685789</v>
       </c>
       <c r="B67" t="n">
-        <v>79694</v>
+        <v>90411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7023,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811410</v>
+        <v>811258</v>
       </c>
       <c r="R67" t="n">
-        <v>7392970</v>
+        <v>7392822</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7068,6 +7067,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>128685806</v>
       </c>
       <c r="B68" t="n">
-        <v>79099</v>
+        <v>79100</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685813</v>
+        <v>128685754</v>
       </c>
       <c r="B70" t="n">
-        <v>91640</v>
+        <v>79695</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810934</v>
+        <v>811026</v>
       </c>
       <c r="R70" t="n">
-        <v>7393019</v>
+        <v>7393053</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685840</v>
+        <v>128685813</v>
       </c>
       <c r="B71" t="n">
-        <v>92869</v>
+        <v>91641</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810762</v>
+        <v>810934</v>
       </c>
       <c r="R71" t="n">
-        <v>7393078</v>
+        <v>7393019</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685840</v>
       </c>
       <c r="B72" t="n">
-        <v>92863</v>
+        <v>92870</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>810762</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7393078</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685872</v>
       </c>
       <c r="B73" t="n">
-        <v>92869</v>
+        <v>92864</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>811269</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7392839</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685856</v>
       </c>
       <c r="B74" t="n">
-        <v>79694</v>
+        <v>92870</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>811494</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7393153</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685864</v>
+        <v>128685848</v>
       </c>
       <c r="B75" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810814</v>
+        <v>810952</v>
       </c>
       <c r="R75" t="n">
-        <v>7393022</v>
+        <v>7392920</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685848</v>
+        <v>128685846</v>
       </c>
       <c r="B76" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810952</v>
+        <v>810911</v>
       </c>
       <c r="R76" t="n">
-        <v>7392920</v>
+        <v>7392927</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685846</v>
+        <v>128685864</v>
       </c>
       <c r="B77" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810911</v>
+        <v>810814</v>
       </c>
       <c r="R77" t="n">
-        <v>7392927</v>
+        <v>7393022</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8059,7 +8059,7 @@
         <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>90212</v>
+        <v>92870</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R79" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685851</v>
+        <v>128685781</v>
       </c>
       <c r="B80" t="n">
-        <v>92869</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811062</v>
+        <v>811507</v>
       </c>
       <c r="R80" t="n">
-        <v>7392883</v>
+        <v>7393120</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8350,7 +8350,7 @@
         <v>128685780</v>
       </c>
       <c r="B81" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685781</v>
+        <v>128685819</v>
       </c>
       <c r="B82" t="n">
-        <v>57735</v>
+        <v>90213</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8455,21 +8455,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811507</v>
+        <v>810744</v>
       </c>
       <c r="R82" t="n">
-        <v>7393120</v>
+        <v>7393058</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685847</v>
+        <v>128685748</v>
       </c>
       <c r="B83" t="n">
-        <v>92869</v>
+        <v>79695</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810944</v>
+        <v>810767</v>
       </c>
       <c r="R83" t="n">
-        <v>7392948</v>
+        <v>7392968</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685748</v>
+        <v>128685847</v>
       </c>
       <c r="B84" t="n">
-        <v>79694</v>
+        <v>92870</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810767</v>
+        <v>810944</v>
       </c>
       <c r="R84" t="n">
-        <v>7392968</v>
+        <v>7392948</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8738,7 +8738,7 @@
         <v>128685817</v>
       </c>
       <c r="B85" t="n">
-        <v>90212</v>
+        <v>90213</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685860</v>
+        <v>128685749</v>
       </c>
       <c r="B86" t="n">
-        <v>92869</v>
+        <v>79695</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811528</v>
+        <v>811061</v>
       </c>
       <c r="R86" t="n">
-        <v>7393160</v>
+        <v>7392880</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685749</v>
+        <v>128685825</v>
       </c>
       <c r="B87" t="n">
-        <v>79694</v>
+        <v>78833</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811061</v>
+        <v>810871</v>
       </c>
       <c r="R87" t="n">
-        <v>7392880</v>
+        <v>7392966</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685825</v>
+        <v>128685860</v>
       </c>
       <c r="B88" t="n">
-        <v>78832</v>
+        <v>92870</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>810871</v>
+        <v>811528</v>
       </c>
       <c r="R88" t="n">
-        <v>7392966</v>
+        <v>7393160</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685764</v>
+        <v>128685796</v>
       </c>
       <c r="B89" t="n">
-        <v>87018</v>
+        <v>92901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
+        <v>232140</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810867</v>
+        <v>810795</v>
       </c>
       <c r="R89" t="n">
-        <v>7392967</v>
+        <v>7393042</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685852</v>
+        <v>128685764</v>
       </c>
       <c r="B90" t="n">
-        <v>92869</v>
+        <v>87019</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811057</v>
+        <v>810867</v>
       </c>
       <c r="R90" t="n">
-        <v>7392877</v>
+        <v>7392967</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B91" t="n">
-        <v>92881</v>
+        <v>87019</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R91" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,6 +9396,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9414,32 +9415,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B92" t="n">
-        <v>87018</v>
+        <v>92882</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9449,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R92" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9493,7 +9494,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9512,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685796</v>
+        <v>128685852</v>
       </c>
       <c r="B93" t="n">
-        <v>92900</v>
+        <v>92870</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>810795</v>
+        <v>811057</v>
       </c>
       <c r="R93" t="n">
-        <v>7393042</v>
+        <v>7392877</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9612,7 +9612,7 @@
         <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>87018</v>
+        <v>87019</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9809,32 +9809,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685849</v>
+        <v>128685834</v>
       </c>
       <c r="B96" t="n">
-        <v>92869</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810964</v>
+        <v>811525</v>
       </c>
       <c r="R96" t="n">
-        <v>7392920</v>
+        <v>7393139</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,10 +9906,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685863</v>
+        <v>128685849</v>
       </c>
       <c r="B97" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810854</v>
+        <v>810964</v>
       </c>
       <c r="R97" t="n">
-        <v>7393015</v>
+        <v>7392920</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10003,32 +10003,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128685834</v>
+        <v>128685863</v>
       </c>
       <c r="B98" t="n">
-        <v>79075</v>
+        <v>92870</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811525</v>
+        <v>810854</v>
       </c>
       <c r="R98" t="n">
-        <v>7393139</v>
+        <v>7393015</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685828</v>
+        <v>128685761</v>
       </c>
       <c r="B41" t="n">
-        <v>78833</v>
+        <v>87019</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811225</v>
+        <v>811014</v>
       </c>
       <c r="R41" t="n">
-        <v>7392837</v>
+        <v>7392891</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4543,6 +4543,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4561,32 +4562,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685798</v>
+        <v>128685818</v>
       </c>
       <c r="B42" t="n">
-        <v>92882</v>
+        <v>90213</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4597,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810767</v>
+        <v>811120</v>
       </c>
       <c r="R42" t="n">
-        <v>7393075</v>
+        <v>7392983</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,10 +4659,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685877</v>
+        <v>128685828</v>
       </c>
       <c r="B43" t="n">
-        <v>92864</v>
+        <v>78833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4669,21 +4670,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811258</v>
+        <v>811225</v>
       </c>
       <c r="R43" t="n">
-        <v>7392822</v>
+        <v>7392837</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,32 +4756,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685814</v>
+        <v>128685798</v>
       </c>
       <c r="B44" t="n">
-        <v>78834</v>
+        <v>92882</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810773</v>
+        <v>810767</v>
       </c>
       <c r="R44" t="n">
-        <v>7392966</v>
+        <v>7393075</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685761</v>
+        <v>128685877</v>
       </c>
       <c r="B45" t="n">
-        <v>87019</v>
+        <v>92864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811014</v>
+        <v>811258</v>
       </c>
       <c r="R45" t="n">
-        <v>7392891</v>
+        <v>7392822</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4931,7 +4932,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685818</v>
+        <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>90213</v>
+        <v>78834</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811120</v>
+        <v>810773</v>
       </c>
       <c r="R46" t="n">
-        <v>7392983</v>
+        <v>7392966</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685815</v>
+        <v>128685767</v>
       </c>
       <c r="B52" t="n">
-        <v>78834</v>
+        <v>87019</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>3690</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810946</v>
+        <v>811516</v>
       </c>
       <c r="R52" t="n">
-        <v>7392983</v>
+        <v>7393158</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685767</v>
+        <v>128685855</v>
       </c>
       <c r="B53" t="n">
-        <v>87019</v>
+        <v>92870</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811516</v>
+        <v>811502</v>
       </c>
       <c r="R53" t="n">
-        <v>7393158</v>
+        <v>7393143</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685855</v>
+        <v>128685868</v>
       </c>
       <c r="B58" t="n">
         <v>92870</v>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811502</v>
+        <v>810757</v>
       </c>
       <c r="R58" t="n">
-        <v>7393143</v>
+        <v>7393053</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685868</v>
+        <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>92870</v>
+        <v>58106</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810757</v>
+        <v>811127</v>
       </c>
       <c r="R59" t="n">
-        <v>7393053</v>
+        <v>7392976</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685823</v>
+        <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>58106</v>
+        <v>78834</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811127</v>
+        <v>810946</v>
       </c>
       <c r="R60" t="n">
-        <v>7392976</v>
+        <v>7392983</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685838</v>
+        <v>128685840</v>
       </c>
       <c r="B69" t="n">
-        <v>82911</v>
+        <v>92870</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810781</v>
+        <v>810762</v>
       </c>
       <c r="R69" t="n">
-        <v>7392936</v>
+        <v>7393078</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685754</v>
+        <v>128685872</v>
       </c>
       <c r="B70" t="n">
-        <v>79695</v>
+        <v>92864</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811026</v>
+        <v>811269</v>
       </c>
       <c r="R70" t="n">
-        <v>7393053</v>
+        <v>7392839</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685813</v>
+        <v>128685856</v>
       </c>
       <c r="B71" t="n">
-        <v>91641</v>
+        <v>92870</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810934</v>
+        <v>811494</v>
       </c>
       <c r="R71" t="n">
-        <v>7393019</v>
+        <v>7393153</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685840</v>
+        <v>128685838</v>
       </c>
       <c r="B72" t="n">
-        <v>92870</v>
+        <v>82911</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810762</v>
+        <v>810781</v>
       </c>
       <c r="R72" t="n">
-        <v>7393078</v>
+        <v>7392936</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,10 +7571,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685872</v>
+        <v>128685813</v>
       </c>
       <c r="B73" t="n">
-        <v>92864</v>
+        <v>91641</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7582,21 +7582,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811269</v>
+        <v>810934</v>
       </c>
       <c r="R73" t="n">
-        <v>7392839</v>
+        <v>7393019</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92870</v>
+        <v>79695</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685756</v>
+        <v>128685836</v>
       </c>
       <c r="B2" t="n">
-        <v>79695</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811013</v>
+        <v>811057</v>
       </c>
       <c r="R2" t="n">
-        <v>7393006</v>
+        <v>7393046</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685843</v>
+        <v>128685790</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>56926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810858</v>
+        <v>810977</v>
       </c>
       <c r="R3" t="n">
-        <v>7392973</v>
+        <v>7393016</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685837</v>
+        <v>128685783</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810756</v>
+        <v>811497</v>
       </c>
       <c r="R4" t="n">
-        <v>7393036</v>
+        <v>7393112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685836</v>
+        <v>128685843</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811057</v>
+        <v>810858</v>
       </c>
       <c r="R5" t="n">
-        <v>7393046</v>
+        <v>7392973</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685783</v>
+        <v>128685837</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811497</v>
+        <v>810756</v>
       </c>
       <c r="R6" t="n">
-        <v>7393112</v>
+        <v>7393036</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685790</v>
+        <v>128685756</v>
       </c>
       <c r="B7" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810977</v>
+        <v>811013</v>
       </c>
       <c r="R7" t="n">
-        <v>7393016</v>
+        <v>7393006</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>128685835</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685853</v>
+        <v>128685804</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>92887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811044</v>
+        <v>810710</v>
       </c>
       <c r="R9" t="n">
-        <v>7392879</v>
+        <v>7393058</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685804</v>
+        <v>128685853</v>
       </c>
       <c r="B10" t="n">
-        <v>92882</v>
+        <v>92875</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810710</v>
+        <v>811044</v>
       </c>
       <c r="R10" t="n">
-        <v>7393058</v>
+        <v>7392879</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1556,7 +1556,7 @@
         <v>128685769</v>
       </c>
       <c r="B11" t="n">
-        <v>87019</v>
+        <v>87024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685810</v>
+        <v>128685874</v>
       </c>
       <c r="B12" t="n">
-        <v>79100</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811027</v>
+        <v>811502</v>
       </c>
       <c r="R12" t="n">
-        <v>7393051</v>
+        <v>7393150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1750,7 +1750,7 @@
         <v>128685795</v>
       </c>
       <c r="B13" t="n">
-        <v>92515</v>
+        <v>92520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>128685866</v>
       </c>
       <c r="B14" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685874</v>
+        <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>92864</v>
+        <v>79105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811502</v>
+        <v>811027</v>
       </c>
       <c r="R15" t="n">
-        <v>7393150</v>
+        <v>7393051</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87019</v>
+        <v>87024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685760</v>
+        <v>128685753</v>
       </c>
       <c r="B17" t="n">
-        <v>79666</v>
+        <v>79700</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R17" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685773</v>
+        <v>128685829</v>
       </c>
       <c r="B18" t="n">
-        <v>87019</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811089</v>
+        <v>810920</v>
       </c>
       <c r="R18" t="n">
-        <v>7393040</v>
+        <v>7393003</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2311,7 +2311,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685753</v>
+        <v>128685826</v>
       </c>
       <c r="B19" t="n">
-        <v>79695</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811087</v>
+        <v>811021</v>
       </c>
       <c r="R19" t="n">
-        <v>7393042</v>
+        <v>7392844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685829</v>
+        <v>128685773</v>
       </c>
       <c r="B20" t="n">
-        <v>78833</v>
+        <v>87024</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R20" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2506,6 +2505,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685826</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>78833</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R21" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685778</v>
+        <v>128685873</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811517</v>
+        <v>811303</v>
       </c>
       <c r="R22" t="n">
-        <v>7393148</v>
+        <v>7392893</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685869</v>
+        <v>128685854</v>
       </c>
       <c r="B23" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810738</v>
+        <v>811441</v>
       </c>
       <c r="R23" t="n">
-        <v>7393051</v>
+        <v>7393097</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685854</v>
+        <v>128685869</v>
       </c>
       <c r="B25" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811441</v>
+        <v>810738</v>
       </c>
       <c r="R25" t="n">
-        <v>7393097</v>
+        <v>7393051</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685873</v>
+        <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>92864</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3020,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811303</v>
+        <v>810853</v>
       </c>
       <c r="R26" t="n">
-        <v>7392893</v>
+        <v>7393047</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>811517</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7393148</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3206,7 +3206,7 @@
         <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>128685839</v>
       </c>
       <c r="B29" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685758</v>
+        <v>128685808</v>
       </c>
       <c r="B30" t="n">
-        <v>79695</v>
+        <v>79105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810717</v>
+        <v>811520</v>
       </c>
       <c r="R30" t="n">
-        <v>7393072</v>
+        <v>7393156</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685861</v>
+        <v>128685758</v>
       </c>
       <c r="B31" t="n">
-        <v>92870</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810965</v>
+        <v>810717</v>
       </c>
       <c r="R31" t="n">
-        <v>7393009</v>
+        <v>7393072</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3594,7 +3594,7 @@
         <v>128685799</v>
       </c>
       <c r="B32" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3688,32 +3688,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685785</v>
+        <v>128685861</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>92875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811518</v>
+        <v>810965</v>
       </c>
       <c r="R33" t="n">
-        <v>7393070</v>
+        <v>7393009</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685776</v>
+        <v>128685785</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810803</v>
+        <v>811518</v>
       </c>
       <c r="R34" t="n">
-        <v>7392998</v>
+        <v>7393070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685808</v>
+        <v>128685776</v>
       </c>
       <c r="B35" t="n">
-        <v>79100</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811520</v>
+        <v>810803</v>
       </c>
       <c r="R35" t="n">
-        <v>7393156</v>
+        <v>7392998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685857</v>
+        <v>128685807</v>
       </c>
       <c r="B36" t="n">
-        <v>92870</v>
+        <v>79105</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811492</v>
+        <v>811004</v>
       </c>
       <c r="R36" t="n">
-        <v>7393149</v>
+        <v>7392787</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685841</v>
+        <v>128685833</v>
       </c>
       <c r="B37" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810812</v>
+        <v>811464</v>
       </c>
       <c r="R37" t="n">
-        <v>7392934</v>
+        <v>7393013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685833</v>
+        <v>128685805</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79105</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811464</v>
+        <v>810973</v>
       </c>
       <c r="R38" t="n">
-        <v>7393013</v>
+        <v>7392910</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685807</v>
+        <v>128685857</v>
       </c>
       <c r="B39" t="n">
-        <v>79100</v>
+        <v>92875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811004</v>
+        <v>811492</v>
       </c>
       <c r="R39" t="n">
-        <v>7392787</v>
+        <v>7393149</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685805</v>
+        <v>128685841</v>
       </c>
       <c r="B40" t="n">
-        <v>79100</v>
+        <v>92875</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810973</v>
+        <v>810812</v>
       </c>
       <c r="R40" t="n">
-        <v>7392910</v>
+        <v>7392934</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685761</v>
+        <v>128685877</v>
       </c>
       <c r="B41" t="n">
-        <v>87019</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811014</v>
+        <v>811258</v>
       </c>
       <c r="R41" t="n">
-        <v>7392891</v>
+        <v>7392822</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4543,7 +4543,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4562,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685818</v>
+        <v>128685761</v>
       </c>
       <c r="B42" t="n">
-        <v>90213</v>
+        <v>87024</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4573,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4962</v>
+        <v>3690</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4597,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811120</v>
+        <v>811014</v>
       </c>
       <c r="R42" t="n">
-        <v>7392983</v>
+        <v>7392891</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4641,6 +4640,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>128685828</v>
       </c>
       <c r="B43" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>128685798</v>
       </c>
       <c r="B44" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685877</v>
+        <v>128685818</v>
       </c>
       <c r="B45" t="n">
-        <v>92864</v>
+        <v>90218</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811258</v>
+        <v>811120</v>
       </c>
       <c r="R45" t="n">
-        <v>7392822</v>
+        <v>7392983</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4953,7 +4953,7 @@
         <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685792</v>
+        <v>128685809</v>
       </c>
       <c r="B47" t="n">
-        <v>92895</v>
+        <v>79105</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3100</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811023</v>
+        <v>811105</v>
       </c>
       <c r="R47" t="n">
-        <v>7392776</v>
+        <v>7393054</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685793</v>
+        <v>128685777</v>
       </c>
       <c r="B48" t="n">
-        <v>92895</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810740</v>
+        <v>811015</v>
       </c>
       <c r="R48" t="n">
-        <v>7393062</v>
+        <v>7392800</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,32 +5241,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685809</v>
+        <v>128685793</v>
       </c>
       <c r="B49" t="n">
-        <v>79100</v>
+        <v>92900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811105</v>
+        <v>810740</v>
       </c>
       <c r="R49" t="n">
-        <v>7393054</v>
+        <v>7393062</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685777</v>
+        <v>128685792</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>92900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811015</v>
+        <v>811023</v>
       </c>
       <c r="R50" t="n">
-        <v>7392800</v>
+        <v>7392776</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5438,7 +5438,7 @@
         <v>128685875</v>
       </c>
       <c r="B51" t="n">
-        <v>92864</v>
+        <v>92869</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>128685767</v>
       </c>
       <c r="B52" t="n">
-        <v>87019</v>
+        <v>87024</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685855</v>
+        <v>128685876</v>
       </c>
       <c r="B53" t="n">
-        <v>92870</v>
+        <v>92869</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811502</v>
+        <v>811269</v>
       </c>
       <c r="R53" t="n">
-        <v>7393143</v>
+        <v>7392821</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5729,7 +5729,7 @@
         <v>128685844</v>
       </c>
       <c r="B54" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>128685803</v>
       </c>
       <c r="B55" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685850</v>
+        <v>128685868</v>
       </c>
       <c r="B56" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810978</v>
+        <v>810757</v>
       </c>
       <c r="R56" t="n">
-        <v>7392914</v>
+        <v>7393053</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6017,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B57" t="n">
-        <v>92864</v>
+        <v>92875</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R57" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685868</v>
+        <v>128685850</v>
       </c>
       <c r="B58" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810757</v>
+        <v>810978</v>
       </c>
       <c r="R58" t="n">
-        <v>7393053</v>
+        <v>7392914</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6311,7 +6311,7 @@
         <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685752</v>
+        <v>128685771</v>
       </c>
       <c r="B61" t="n">
-        <v>79695</v>
+        <v>87024</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811410</v>
+        <v>811112</v>
       </c>
       <c r="R61" t="n">
-        <v>7392970</v>
+        <v>7393038</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,6 +6484,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6502,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685859</v>
+        <v>128685789</v>
       </c>
       <c r="B62" t="n">
-        <v>92870</v>
+        <v>90416</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6537,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811498</v>
+        <v>811258</v>
       </c>
       <c r="R62" t="n">
-        <v>7393147</v>
+        <v>7392822</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6581,6 +6582,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6602,7 +6604,7 @@
         <v>128685800</v>
       </c>
       <c r="B63" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6696,32 +6698,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685788</v>
+        <v>128685859</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>92875</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6731,10 +6733,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811107</v>
+        <v>811498</v>
       </c>
       <c r="R64" t="n">
-        <v>7393022</v>
+        <v>7393147</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6793,32 +6795,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685771</v>
+        <v>128685812</v>
       </c>
       <c r="B65" t="n">
-        <v>87019</v>
+        <v>79105</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3690</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6828,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811112</v>
+        <v>810948</v>
       </c>
       <c r="R65" t="n">
-        <v>7393038</v>
+        <v>7392987</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6872,7 +6874,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6891,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685812</v>
+        <v>128685752</v>
       </c>
       <c r="B66" t="n">
-        <v>79100</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6926,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>810948</v>
+        <v>811410</v>
       </c>
       <c r="R66" t="n">
-        <v>7392987</v>
+        <v>7392970</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6988,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685789</v>
+        <v>128685806</v>
       </c>
       <c r="B67" t="n">
-        <v>90411</v>
+        <v>79105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6286</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7023,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811258</v>
+        <v>811056</v>
       </c>
       <c r="R67" t="n">
-        <v>7392822</v>
+        <v>7392881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7067,7 +7068,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685806</v>
+        <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>79100</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811056</v>
+        <v>811107</v>
       </c>
       <c r="R68" t="n">
-        <v>7392881</v>
+        <v>7393022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,32 +7183,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685840</v>
+        <v>128685754</v>
       </c>
       <c r="B69" t="n">
-        <v>92870</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810762</v>
+        <v>811026</v>
       </c>
       <c r="R69" t="n">
-        <v>7393078</v>
+        <v>7393053</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685872</v>
+        <v>128685838</v>
       </c>
       <c r="B70" t="n">
-        <v>92864</v>
+        <v>82916</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811269</v>
+        <v>810781</v>
       </c>
       <c r="R70" t="n">
-        <v>7392839</v>
+        <v>7392936</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685856</v>
+        <v>128685813</v>
       </c>
       <c r="B71" t="n">
-        <v>92870</v>
+        <v>91646</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811494</v>
+        <v>810934</v>
       </c>
       <c r="R71" t="n">
-        <v>7393153</v>
+        <v>7393019</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685838</v>
+        <v>128685872</v>
       </c>
       <c r="B72" t="n">
-        <v>82911</v>
+        <v>92869</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810781</v>
+        <v>811269</v>
       </c>
       <c r="R72" t="n">
-        <v>7392936</v>
+        <v>7392839</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685813</v>
+        <v>128685840</v>
       </c>
       <c r="B73" t="n">
-        <v>91641</v>
+        <v>92875</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>810934</v>
+        <v>810762</v>
       </c>
       <c r="R73" t="n">
-        <v>7393019</v>
+        <v>7393078</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685856</v>
       </c>
       <c r="B74" t="n">
-        <v>79695</v>
+        <v>92875</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>811494</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7393153</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685848</v>
+        <v>128685864</v>
       </c>
       <c r="B75" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810952</v>
+        <v>810814</v>
       </c>
       <c r="R75" t="n">
-        <v>7392920</v>
+        <v>7393022</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685846</v>
+        <v>128685848</v>
       </c>
       <c r="B76" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810911</v>
+        <v>810952</v>
       </c>
       <c r="R76" t="n">
-        <v>7392927</v>
+        <v>7392920</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685864</v>
+        <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810814</v>
+        <v>810911</v>
       </c>
       <c r="R77" t="n">
-        <v>7393022</v>
+        <v>7392927</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685851</v>
+        <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>92870</v>
+        <v>90218</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811062</v>
+        <v>810744</v>
       </c>
       <c r="R79" t="n">
-        <v>7392883</v>
+        <v>7393058</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685781</v>
+        <v>128685851</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>92875</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811507</v>
+        <v>811062</v>
       </c>
       <c r="R80" t="n">
-        <v>7393120</v>
+        <v>7392883</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685819</v>
+        <v>128685781</v>
       </c>
       <c r="B82" t="n">
-        <v>90213</v>
+        <v>57736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8455,21 +8455,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4962</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>810744</v>
+        <v>811507</v>
       </c>
       <c r="R82" t="n">
-        <v>7393058</v>
+        <v>7393120</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8544,7 +8544,7 @@
         <v>128685748</v>
       </c>
       <c r="B83" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B84" t="n">
-        <v>92870</v>
+        <v>90218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R84" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B85" t="n">
-        <v>90213</v>
+        <v>92875</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R85" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>79695</v>
+        <v>92875</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R86" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>78833</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R87" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>92870</v>
+        <v>78838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R88" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9126,7 +9126,7 @@
         <v>128685796</v>
       </c>
       <c r="B89" t="n">
-        <v>92901</v>
+        <v>92906</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>128685764</v>
       </c>
       <c r="B90" t="n">
-        <v>87019</v>
+        <v>87024</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>128685763</v>
       </c>
       <c r="B91" t="n">
-        <v>87019</v>
+        <v>87024</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685801</v>
+        <v>128685852</v>
       </c>
       <c r="B92" t="n">
-        <v>92882</v>
+        <v>92875</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9426,21 +9426,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811116</v>
+        <v>811057</v>
       </c>
       <c r="R92" t="n">
-        <v>7392980</v>
+        <v>7392877</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9512,10 +9512,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685852</v>
+        <v>128685801</v>
       </c>
       <c r="B93" t="n">
-        <v>92870</v>
+        <v>92887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9523,21 +9523,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811057</v>
+        <v>811116</v>
       </c>
       <c r="R93" t="n">
-        <v>7392877</v>
+        <v>7392980</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9612,7 +9612,7 @@
         <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>87019</v>
+        <v>87024</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9809,32 +9809,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685834</v>
+        <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>79076</v>
+        <v>92875</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811525</v>
+        <v>810964</v>
       </c>
       <c r="R96" t="n">
-        <v>7393139</v>
+        <v>7392920</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,10 +9906,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685849</v>
+        <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810964</v>
+        <v>810854</v>
       </c>
       <c r="R97" t="n">
-        <v>7392920</v>
+        <v>7393015</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10003,32 +10003,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128685863</v>
+        <v>128685834</v>
       </c>
       <c r="B98" t="n">
-        <v>92870</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>810854</v>
+        <v>811525</v>
       </c>
       <c r="R98" t="n">
-        <v>7393015</v>
+        <v>7393139</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685836</v>
+        <v>128685837</v>
       </c>
       <c r="B2" t="n">
         <v>79081</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811057</v>
+        <v>810756</v>
       </c>
       <c r="R2" t="n">
-        <v>7393046</v>
+        <v>7393036</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685790</v>
+        <v>128685836</v>
       </c>
       <c r="B3" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810977</v>
+        <v>811057</v>
       </c>
       <c r="R3" t="n">
-        <v>7393016</v>
+        <v>7393046</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685783</v>
+        <v>128685756</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811497</v>
+        <v>811013</v>
       </c>
       <c r="R4" t="n">
-        <v>7393112</v>
+        <v>7393006</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685837</v>
+        <v>128685790</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810756</v>
+        <v>810977</v>
       </c>
       <c r="R6" t="n">
-        <v>7393036</v>
+        <v>7393016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685756</v>
+        <v>128685783</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811013</v>
+        <v>811497</v>
       </c>
       <c r="R7" t="n">
-        <v>7393006</v>
+        <v>7393112</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685835</v>
+        <v>128685804</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>92887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811420</v>
+        <v>810710</v>
       </c>
       <c r="R8" t="n">
-        <v>7392954</v>
+        <v>7393058</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685804</v>
+        <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92887</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810710</v>
+        <v>811044</v>
       </c>
       <c r="R9" t="n">
-        <v>7393058</v>
+        <v>7392879</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685853</v>
+        <v>128685835</v>
       </c>
       <c r="B10" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811044</v>
+        <v>811420</v>
       </c>
       <c r="R10" t="n">
-        <v>7392879</v>
+        <v>7392954</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685769</v>
+        <v>128685810</v>
       </c>
       <c r="B11" t="n">
-        <v>87024</v>
+        <v>79105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3690</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810725</v>
+        <v>811027</v>
       </c>
       <c r="R11" t="n">
-        <v>7393066</v>
+        <v>7393051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685810</v>
+        <v>128685769</v>
       </c>
       <c r="B15" t="n">
-        <v>79105</v>
+        <v>87024</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811027</v>
+        <v>810725</v>
       </c>
       <c r="R15" t="n">
-        <v>7393051</v>
+        <v>7393066</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685753</v>
+        <v>128685826</v>
       </c>
       <c r="B17" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811087</v>
+        <v>811021</v>
       </c>
       <c r="R17" t="n">
-        <v>7393042</v>
+        <v>7392844</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685829</v>
+        <v>128685760</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685826</v>
+        <v>128685773</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>87024</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811021</v>
+        <v>811089</v>
       </c>
       <c r="R19" t="n">
-        <v>7392844</v>
+        <v>7393040</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2408,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2426,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685773</v>
+        <v>128685753</v>
       </c>
       <c r="B20" t="n">
-        <v>87024</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811089</v>
+        <v>811087</v>
       </c>
       <c r="R20" t="n">
-        <v>7393040</v>
+        <v>7393042</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2505,7 +2506,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685829</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685873</v>
+        <v>128685778</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811303</v>
+        <v>811517</v>
       </c>
       <c r="R22" t="n">
-        <v>7392893</v>
+        <v>7393148</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685802</v>
+        <v>128685873</v>
       </c>
       <c r="B24" t="n">
-        <v>92887</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811027</v>
+        <v>811303</v>
       </c>
       <c r="R24" t="n">
-        <v>7393042</v>
+        <v>7392893</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685869</v>
+        <v>128685802</v>
       </c>
       <c r="B25" t="n">
-        <v>92875</v>
+        <v>92887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810738</v>
+        <v>811027</v>
       </c>
       <c r="R25" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685831</v>
+        <v>128685869</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>92875</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810853</v>
+        <v>810738</v>
       </c>
       <c r="R26" t="n">
-        <v>7393047</v>
+        <v>7393051</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685778</v>
+        <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811517</v>
+        <v>810853</v>
       </c>
       <c r="R27" t="n">
-        <v>7393148</v>
+        <v>7393047</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685808</v>
+        <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>79105</v>
+        <v>92887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811520</v>
+        <v>810790</v>
       </c>
       <c r="R30" t="n">
-        <v>7393156</v>
+        <v>7392931</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685758</v>
+        <v>128685861</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810717</v>
+        <v>810965</v>
       </c>
       <c r="R31" t="n">
-        <v>7393072</v>
+        <v>7393009</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685799</v>
+        <v>128685785</v>
       </c>
       <c r="B32" t="n">
-        <v>92887</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810790</v>
+        <v>811518</v>
       </c>
       <c r="R32" t="n">
-        <v>7392931</v>
+        <v>7393070</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,32 +3688,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685861</v>
+        <v>128685776</v>
       </c>
       <c r="B33" t="n">
-        <v>92875</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810965</v>
+        <v>810803</v>
       </c>
       <c r="R33" t="n">
-        <v>7393009</v>
+        <v>7392998</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685785</v>
+        <v>128685808</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>79105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811518</v>
+        <v>811520</v>
       </c>
       <c r="R34" t="n">
-        <v>7393070</v>
+        <v>7393156</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685776</v>
+        <v>128685758</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810803</v>
+        <v>810717</v>
       </c>
       <c r="R35" t="n">
-        <v>7392998</v>
+        <v>7393072</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685877</v>
+        <v>128685798</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811258</v>
+        <v>810767</v>
       </c>
       <c r="R41" t="n">
-        <v>7392822</v>
+        <v>7393075</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685761</v>
+        <v>128685818</v>
       </c>
       <c r="B42" t="n">
-        <v>87024</v>
+        <v>90218</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3690</v>
+        <v>4962</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811014</v>
+        <v>811120</v>
       </c>
       <c r="R42" t="n">
-        <v>7392891</v>
+        <v>7392983</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4640,7 +4640,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4659,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685828</v>
+        <v>128685877</v>
       </c>
       <c r="B43" t="n">
-        <v>78838</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4670,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4694,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811225</v>
+        <v>811258</v>
       </c>
       <c r="R43" t="n">
-        <v>7392837</v>
+        <v>7392822</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4756,32 +4755,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685798</v>
+        <v>128685761</v>
       </c>
       <c r="B44" t="n">
-        <v>92887</v>
+        <v>87024</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810767</v>
+        <v>811014</v>
       </c>
       <c r="R44" t="n">
-        <v>7393075</v>
+        <v>7392891</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4835,6 +4834,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685818</v>
+        <v>128685828</v>
       </c>
       <c r="B45" t="n">
-        <v>90218</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4962</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811120</v>
+        <v>811225</v>
       </c>
       <c r="R45" t="n">
-        <v>7392983</v>
+        <v>7392837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685777</v>
+        <v>128685875</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>92869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811015</v>
+        <v>811283</v>
       </c>
       <c r="R48" t="n">
-        <v>7392800</v>
+        <v>7392844</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,7 +5241,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B49" t="n">
         <v>92900</v>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R49" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,7 +5338,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B50" t="n">
         <v>92900</v>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R50" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685875</v>
+        <v>128685777</v>
       </c>
       <c r="B51" t="n">
-        <v>92869</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811283</v>
+        <v>811015</v>
       </c>
       <c r="R51" t="n">
-        <v>7392844</v>
+        <v>7392800</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685767</v>
+        <v>128685844</v>
       </c>
       <c r="B52" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811516</v>
+        <v>810873</v>
       </c>
       <c r="R52" t="n">
-        <v>7393158</v>
+        <v>7392973</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685876</v>
+        <v>128685803</v>
       </c>
       <c r="B53" t="n">
-        <v>92869</v>
+        <v>92887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811269</v>
+        <v>810733</v>
       </c>
       <c r="R53" t="n">
-        <v>7392821</v>
+        <v>7393068</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685844</v>
+        <v>128685868</v>
       </c>
       <c r="B54" t="n">
         <v>92875</v>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810873</v>
+        <v>810757</v>
       </c>
       <c r="R54" t="n">
-        <v>7392973</v>
+        <v>7393053</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685803</v>
+        <v>128685876</v>
       </c>
       <c r="B55" t="n">
-        <v>92887</v>
+        <v>92869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810733</v>
+        <v>811269</v>
       </c>
       <c r="R55" t="n">
-        <v>7393068</v>
+        <v>7392821</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,7 +5920,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685868</v>
+        <v>128685855</v>
       </c>
       <c r="B56" t="n">
         <v>92875</v>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810757</v>
+        <v>811502</v>
       </c>
       <c r="R56" t="n">
-        <v>7393053</v>
+        <v>7393143</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685855</v>
+        <v>128685850</v>
       </c>
       <c r="B57" t="n">
         <v>92875</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811502</v>
+        <v>810978</v>
       </c>
       <c r="R57" t="n">
-        <v>7393143</v>
+        <v>7392914</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685850</v>
+        <v>128685823</v>
       </c>
       <c r="B58" t="n">
-        <v>92875</v>
+        <v>58106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810978</v>
+        <v>811127</v>
       </c>
       <c r="R58" t="n">
-        <v>7392914</v>
+        <v>7392976</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,32 +6211,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685823</v>
+        <v>128685767</v>
       </c>
       <c r="B59" t="n">
-        <v>58106</v>
+        <v>87024</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>3690</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811127</v>
+        <v>811516</v>
       </c>
       <c r="R59" t="n">
-        <v>7392976</v>
+        <v>7393158</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6503,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685789</v>
+        <v>128685788</v>
       </c>
       <c r="B62" t="n">
-        <v>90416</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6286</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811258</v>
+        <v>811107</v>
       </c>
       <c r="R62" t="n">
-        <v>7392822</v>
+        <v>7393022</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6582,7 +6582,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6795,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685812</v>
+        <v>128685789</v>
       </c>
       <c r="B65" t="n">
-        <v>79105</v>
+        <v>90416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6830,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810948</v>
+        <v>811258</v>
       </c>
       <c r="R65" t="n">
-        <v>7392987</v>
+        <v>7392822</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6874,6 +6873,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6892,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685752</v>
+        <v>128685812</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>79105</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811410</v>
+        <v>810948</v>
       </c>
       <c r="R66" t="n">
-        <v>7392970</v>
+        <v>7392987</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685806</v>
+        <v>128685752</v>
       </c>
       <c r="B67" t="n">
-        <v>79105</v>
+        <v>79700</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811056</v>
+        <v>811410</v>
       </c>
       <c r="R67" t="n">
-        <v>7392881</v>
+        <v>7392970</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685788</v>
+        <v>128685806</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79105</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811107</v>
+        <v>811056</v>
       </c>
       <c r="R68" t="n">
-        <v>7393022</v>
+        <v>7392881</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685754</v>
+        <v>128685813</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>91646</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811026</v>
+        <v>810934</v>
       </c>
       <c r="R69" t="n">
-        <v>7393053</v>
+        <v>7393019</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685813</v>
+        <v>128685840</v>
       </c>
       <c r="B71" t="n">
-        <v>91646</v>
+        <v>92875</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810934</v>
+        <v>810762</v>
       </c>
       <c r="R71" t="n">
-        <v>7393019</v>
+        <v>7393078</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7571,7 +7571,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685840</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
         <v>92875</v>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>810762</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7393078</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685748</v>
+        <v>128685817</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>90218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810767</v>
+        <v>811007</v>
       </c>
       <c r="R83" t="n">
-        <v>7392968</v>
+        <v>7392796</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B84" t="n">
-        <v>90218</v>
+        <v>92875</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685847</v>
+        <v>128685748</v>
       </c>
       <c r="B85" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810944</v>
+        <v>810767</v>
       </c>
       <c r="R85" t="n">
-        <v>7392948</v>
+        <v>7392968</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685764</v>
+        <v>128685852</v>
       </c>
       <c r="B90" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>810867</v>
+        <v>811057</v>
       </c>
       <c r="R90" t="n">
-        <v>7392967</v>
+        <v>7392877</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>87024</v>
+        <v>92887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R91" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,7 +9396,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,32 +9414,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685852</v>
+        <v>128685764</v>
       </c>
       <c r="B92" t="n">
-        <v>92875</v>
+        <v>87024</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9449,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811057</v>
+        <v>810867</v>
       </c>
       <c r="R92" t="n">
-        <v>7392877</v>
+        <v>7392967</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9512,32 +9511,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B93" t="n">
-        <v>92887</v>
+        <v>87024</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9546,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R93" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9591,6 +9590,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685837</v>
+        <v>128685790</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810756</v>
+        <v>810977</v>
       </c>
       <c r="R2" t="n">
-        <v>7393036</v>
+        <v>7393016</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685836</v>
+        <v>128685783</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811057</v>
+        <v>811497</v>
       </c>
       <c r="R3" t="n">
-        <v>7393046</v>
+        <v>7393112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685756</v>
+        <v>128685843</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811013</v>
+        <v>810858</v>
       </c>
       <c r="R4" t="n">
-        <v>7393006</v>
+        <v>7392973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685843</v>
+        <v>128685837</v>
       </c>
       <c r="B5" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810858</v>
+        <v>810756</v>
       </c>
       <c r="R5" t="n">
-        <v>7392973</v>
+        <v>7393036</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685790</v>
+        <v>128685756</v>
       </c>
       <c r="B6" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810977</v>
+        <v>811013</v>
       </c>
       <c r="R6" t="n">
-        <v>7393016</v>
+        <v>7393006</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685783</v>
+        <v>128685836</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811497</v>
+        <v>811057</v>
       </c>
       <c r="R7" t="n">
-        <v>7393112</v>
+        <v>7393046</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B13" t="n">
-        <v>92520</v>
+        <v>87024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R13" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685866</v>
+        <v>128685795</v>
       </c>
       <c r="B14" t="n">
-        <v>92875</v>
+        <v>92520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810789</v>
+        <v>810915</v>
       </c>
       <c r="R14" t="n">
-        <v>7393036</v>
+        <v>7393042</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685769</v>
+        <v>128685866</v>
       </c>
       <c r="B15" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810725</v>
+        <v>810789</v>
       </c>
       <c r="R15" t="n">
-        <v>7393066</v>
+        <v>7393036</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685826</v>
+        <v>128685773</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>87024</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811021</v>
+        <v>811089</v>
       </c>
       <c r="R17" t="n">
-        <v>7392844</v>
+        <v>7393040</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685760</v>
+        <v>128685829</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685773</v>
+        <v>128685826</v>
       </c>
       <c r="B19" t="n">
-        <v>87024</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811089</v>
+        <v>811021</v>
       </c>
       <c r="R19" t="n">
-        <v>7393040</v>
+        <v>7392844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2408,7 +2409,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685829</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685778</v>
+        <v>128685873</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811517</v>
+        <v>811303</v>
       </c>
       <c r="R22" t="n">
-        <v>7393148</v>
+        <v>7392893</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685873</v>
+        <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811303</v>
+        <v>811027</v>
       </c>
       <c r="R24" t="n">
-        <v>7392893</v>
+        <v>7393042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685802</v>
+        <v>128685869</v>
       </c>
       <c r="B25" t="n">
-        <v>92887</v>
+        <v>92875</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811027</v>
+        <v>810738</v>
       </c>
       <c r="R25" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685869</v>
+        <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810738</v>
+        <v>810853</v>
       </c>
       <c r="R26" t="n">
-        <v>7393051</v>
+        <v>7393047</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>811517</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7393148</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685839</v>
+        <v>128685808</v>
       </c>
       <c r="B29" t="n">
-        <v>78747</v>
+        <v>79105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811034</v>
+        <v>811520</v>
       </c>
       <c r="R29" t="n">
-        <v>7393002</v>
+        <v>7393156</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685799</v>
+        <v>128685758</v>
       </c>
       <c r="B30" t="n">
-        <v>92887</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810790</v>
+        <v>810717</v>
       </c>
       <c r="R30" t="n">
-        <v>7392931</v>
+        <v>7393072</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685861</v>
+        <v>128685785</v>
       </c>
       <c r="B31" t="n">
-        <v>92875</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810965</v>
+        <v>811518</v>
       </c>
       <c r="R31" t="n">
-        <v>7393009</v>
+        <v>7393070</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685785</v>
+        <v>128685776</v>
       </c>
       <c r="B32" t="n">
         <v>57736</v>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811518</v>
+        <v>810803</v>
       </c>
       <c r="R32" t="n">
-        <v>7393070</v>
+        <v>7392998</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685776</v>
+        <v>128685839</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>78747</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810803</v>
+        <v>811034</v>
       </c>
       <c r="R33" t="n">
-        <v>7392998</v>
+        <v>7393002</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685808</v>
+        <v>128685799</v>
       </c>
       <c r="B34" t="n">
-        <v>79105</v>
+        <v>92887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811520</v>
+        <v>810790</v>
       </c>
       <c r="R34" t="n">
-        <v>7393156</v>
+        <v>7392931</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685758</v>
+        <v>128685861</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810717</v>
+        <v>810965</v>
       </c>
       <c r="R35" t="n">
-        <v>7393072</v>
+        <v>7393009</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685807</v>
+        <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>79105</v>
+        <v>92875</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3990,21 +3990,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811004</v>
+        <v>811492</v>
       </c>
       <c r="R36" t="n">
-        <v>7392787</v>
+        <v>7393149</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,32 +4076,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685833</v>
+        <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>92875</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811464</v>
+        <v>810812</v>
       </c>
       <c r="R37" t="n">
-        <v>7393013</v>
+        <v>7392934</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685805</v>
+        <v>128685833</v>
       </c>
       <c r="B38" t="n">
-        <v>79105</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810973</v>
+        <v>811464</v>
       </c>
       <c r="R38" t="n">
-        <v>7392910</v>
+        <v>7393013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,10 +4270,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685857</v>
+        <v>128685807</v>
       </c>
       <c r="B39" t="n">
-        <v>92875</v>
+        <v>79105</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4281,21 +4281,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811492</v>
+        <v>811004</v>
       </c>
       <c r="R39" t="n">
-        <v>7393149</v>
+        <v>7392787</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,10 +4367,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685841</v>
+        <v>128685805</v>
       </c>
       <c r="B40" t="n">
-        <v>92875</v>
+        <v>79105</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4378,21 +4378,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810812</v>
+        <v>810973</v>
       </c>
       <c r="R40" t="n">
-        <v>7392934</v>
+        <v>7392910</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685877</v>
+        <v>128685814</v>
       </c>
       <c r="B43" t="n">
-        <v>92869</v>
+        <v>78839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811258</v>
+        <v>810773</v>
       </c>
       <c r="R43" t="n">
-        <v>7392822</v>
+        <v>7392966</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685761</v>
+        <v>128685877</v>
       </c>
       <c r="B44" t="n">
-        <v>87024</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811014</v>
+        <v>811258</v>
       </c>
       <c r="R44" t="n">
-        <v>7392891</v>
+        <v>7392822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4834,7 +4834,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4853,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685828</v>
+        <v>128685761</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>87024</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4863,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4887,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811225</v>
+        <v>811014</v>
       </c>
       <c r="R45" t="n">
-        <v>7392837</v>
+        <v>7392891</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4932,6 +4931,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685814</v>
+        <v>128685828</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810773</v>
+        <v>811225</v>
       </c>
       <c r="R46" t="n">
-        <v>7392966</v>
+        <v>7392837</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685809</v>
+        <v>128685792</v>
       </c>
       <c r="B47" t="n">
-        <v>79105</v>
+        <v>92900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>3100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811105</v>
+        <v>811023</v>
       </c>
       <c r="R47" t="n">
-        <v>7393054</v>
+        <v>7392776</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685875</v>
+        <v>128685793</v>
       </c>
       <c r="B48" t="n">
-        <v>92869</v>
+        <v>92900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811283</v>
+        <v>810740</v>
       </c>
       <c r="R48" t="n">
-        <v>7392844</v>
+        <v>7393062</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685792</v>
+        <v>128685875</v>
       </c>
       <c r="B49" t="n">
-        <v>92900</v>
+        <v>92869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811023</v>
+        <v>811283</v>
       </c>
       <c r="R49" t="n">
-        <v>7392776</v>
+        <v>7392844</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685793</v>
+        <v>128685809</v>
       </c>
       <c r="B50" t="n">
-        <v>92900</v>
+        <v>79105</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3100</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810740</v>
+        <v>811105</v>
       </c>
       <c r="R50" t="n">
-        <v>7393062</v>
+        <v>7393054</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B55" t="n">
-        <v>92869</v>
+        <v>92875</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R55" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,7 +5920,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685855</v>
+        <v>128685850</v>
       </c>
       <c r="B56" t="n">
         <v>92875</v>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811502</v>
+        <v>810978</v>
       </c>
       <c r="R56" t="n">
-        <v>7393143</v>
+        <v>7392914</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6017,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685850</v>
+        <v>128685815</v>
       </c>
       <c r="B57" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810978</v>
+        <v>810946</v>
       </c>
       <c r="R57" t="n">
-        <v>7392914</v>
+        <v>7392983</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685823</v>
+        <v>128685767</v>
       </c>
       <c r="B58" t="n">
-        <v>58106</v>
+        <v>87024</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>3690</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811127</v>
+        <v>811516</v>
       </c>
       <c r="R58" t="n">
-        <v>7392976</v>
+        <v>7393158</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685767</v>
+        <v>128685876</v>
       </c>
       <c r="B59" t="n">
-        <v>87024</v>
+        <v>92869</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811516</v>
+        <v>811269</v>
       </c>
       <c r="R59" t="n">
-        <v>7393158</v>
+        <v>7392821</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685815</v>
+        <v>128685823</v>
       </c>
       <c r="B60" t="n">
-        <v>78839</v>
+        <v>58106</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810946</v>
+        <v>811127</v>
       </c>
       <c r="R60" t="n">
-        <v>7392983</v>
+        <v>7392976</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6503,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685788</v>
+        <v>128685800</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>92887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811107</v>
+        <v>810861</v>
       </c>
       <c r="R62" t="n">
-        <v>7393022</v>
+        <v>7392976</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685800</v>
+        <v>128685859</v>
       </c>
       <c r="B63" t="n">
-        <v>92887</v>
+        <v>92875</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6611,21 +6611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>810861</v>
+        <v>811498</v>
       </c>
       <c r="R63" t="n">
-        <v>7392976</v>
+        <v>7393147</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,10 +6697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685859</v>
+        <v>128685812</v>
       </c>
       <c r="B64" t="n">
-        <v>92875</v>
+        <v>79105</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6708,21 +6708,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811498</v>
+        <v>810948</v>
       </c>
       <c r="R64" t="n">
-        <v>7393147</v>
+        <v>7392987</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685789</v>
+        <v>128685752</v>
       </c>
       <c r="B65" t="n">
-        <v>90416</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6286</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811258</v>
+        <v>811410</v>
       </c>
       <c r="R65" t="n">
-        <v>7392822</v>
+        <v>7392970</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6873,7 +6873,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6892,32 +6891,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685812</v>
+        <v>128685789</v>
       </c>
       <c r="B66" t="n">
-        <v>79105</v>
+        <v>90416</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6926,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>810948</v>
+        <v>811258</v>
       </c>
       <c r="R66" t="n">
-        <v>7392987</v>
+        <v>7392822</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6971,6 +6970,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685752</v>
+        <v>128685806</v>
       </c>
       <c r="B67" t="n">
-        <v>79700</v>
+        <v>79105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811410</v>
+        <v>811056</v>
       </c>
       <c r="R67" t="n">
-        <v>7392970</v>
+        <v>7392881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685806</v>
+        <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>79105</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811056</v>
+        <v>811107</v>
       </c>
       <c r="R68" t="n">
-        <v>7392881</v>
+        <v>7393022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685813</v>
+        <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>91646</v>
+        <v>82916</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810934</v>
+        <v>810781</v>
       </c>
       <c r="R69" t="n">
-        <v>7393019</v>
+        <v>7392936</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685838</v>
+        <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>82916</v>
+        <v>91646</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810781</v>
+        <v>810934</v>
       </c>
       <c r="R70" t="n">
-        <v>7392936</v>
+        <v>7393019</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685856</v>
       </c>
       <c r="B72" t="n">
-        <v>92869</v>
+        <v>92875</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>811494</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7393153</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B73" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685872</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>92869</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7679,21 +7679,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>811269</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7392839</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B83" t="n">
-        <v>90218</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R83" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B84" t="n">
-        <v>92875</v>
+        <v>90218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R84" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685748</v>
+        <v>128685847</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810767</v>
+        <v>810944</v>
       </c>
       <c r="R85" t="n">
-        <v>7392968</v>
+        <v>7392948</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685852</v>
+        <v>128685764</v>
       </c>
       <c r="B90" t="n">
-        <v>92875</v>
+        <v>87024</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811057</v>
+        <v>810867</v>
       </c>
       <c r="R90" t="n">
-        <v>7392877</v>
+        <v>7392967</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B91" t="n">
-        <v>92887</v>
+        <v>87024</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R91" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,6 +9396,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9414,32 +9415,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685764</v>
+        <v>128685852</v>
       </c>
       <c r="B92" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9449,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>810867</v>
+        <v>811057</v>
       </c>
       <c r="R92" t="n">
-        <v>7392967</v>
+        <v>7392877</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9511,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B93" t="n">
-        <v>87024</v>
+        <v>92887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9546,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R93" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9590,7 +9591,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685790</v>
+        <v>128685843</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810977</v>
+        <v>810858</v>
       </c>
       <c r="R2" t="n">
-        <v>7393016</v>
+        <v>7392973</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685783</v>
+        <v>128685837</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811497</v>
+        <v>810756</v>
       </c>
       <c r="R3" t="n">
-        <v>7393112</v>
+        <v>7393036</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685843</v>
+        <v>128685836</v>
       </c>
       <c r="B4" t="n">
-        <v>92875</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810858</v>
+        <v>811057</v>
       </c>
       <c r="R4" t="n">
-        <v>7392973</v>
+        <v>7393046</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685837</v>
+        <v>128685756</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810756</v>
+        <v>811013</v>
       </c>
       <c r="R5" t="n">
-        <v>7393036</v>
+        <v>7393006</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685756</v>
+        <v>128685790</v>
       </c>
       <c r="B6" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811013</v>
+        <v>810977</v>
       </c>
       <c r="R6" t="n">
-        <v>7393006</v>
+        <v>7393016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685836</v>
+        <v>128685783</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811057</v>
+        <v>811497</v>
       </c>
       <c r="R7" t="n">
-        <v>7393046</v>
+        <v>7393112</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685810</v>
+        <v>128685795</v>
       </c>
       <c r="B11" t="n">
-        <v>79105</v>
+        <v>92520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811027</v>
+        <v>810915</v>
       </c>
       <c r="R11" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685769</v>
+        <v>128685866</v>
       </c>
       <c r="B13" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810725</v>
+        <v>810789</v>
       </c>
       <c r="R13" t="n">
-        <v>7393066</v>
+        <v>7393036</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B14" t="n">
-        <v>92520</v>
+        <v>87024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R14" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685866</v>
+        <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>92875</v>
+        <v>79105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810789</v>
+        <v>811027</v>
       </c>
       <c r="R15" t="n">
-        <v>7393036</v>
+        <v>7393051</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685829</v>
+        <v>128685753</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685826</v>
+        <v>128685829</v>
       </c>
       <c r="B19" t="n">
         <v>78838</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R19" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685753</v>
+        <v>128685826</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811087</v>
+        <v>811021</v>
       </c>
       <c r="R20" t="n">
-        <v>7393042</v>
+        <v>7392844</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685873</v>
+        <v>128685778</v>
       </c>
       <c r="B22" t="n">
-        <v>92869</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811303</v>
+        <v>811517</v>
       </c>
       <c r="R22" t="n">
-        <v>7392893</v>
+        <v>7393148</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685802</v>
+        <v>128685873</v>
       </c>
       <c r="B24" t="n">
-        <v>92887</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811027</v>
+        <v>811303</v>
       </c>
       <c r="R24" t="n">
-        <v>7393042</v>
+        <v>7392893</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685869</v>
+        <v>128685802</v>
       </c>
       <c r="B25" t="n">
-        <v>92875</v>
+        <v>92887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810738</v>
+        <v>811027</v>
       </c>
       <c r="R25" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685831</v>
+        <v>128685869</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>92875</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810853</v>
+        <v>810738</v>
       </c>
       <c r="R26" t="n">
-        <v>7393047</v>
+        <v>7393051</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685778</v>
+        <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811517</v>
+        <v>810853</v>
       </c>
       <c r="R27" t="n">
-        <v>7393148</v>
+        <v>7393047</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685808</v>
+        <v>128685839</v>
       </c>
       <c r="B29" t="n">
-        <v>79105</v>
+        <v>78747</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811520</v>
+        <v>811034</v>
       </c>
       <c r="R29" t="n">
-        <v>7393156</v>
+        <v>7393002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685758</v>
+        <v>128685785</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810717</v>
+        <v>811518</v>
       </c>
       <c r="R30" t="n">
-        <v>7393072</v>
+        <v>7393070</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685785</v>
+        <v>128685776</v>
       </c>
       <c r="B31" t="n">
         <v>57736</v>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811518</v>
+        <v>810803</v>
       </c>
       <c r="R31" t="n">
-        <v>7393070</v>
+        <v>7392998</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685776</v>
+        <v>128685799</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>92887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810803</v>
+        <v>810790</v>
       </c>
       <c r="R32" t="n">
-        <v>7392998</v>
+        <v>7392931</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,32 +3688,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685839</v>
+        <v>128685861</v>
       </c>
       <c r="B33" t="n">
-        <v>78747</v>
+        <v>92875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811034</v>
+        <v>810965</v>
       </c>
       <c r="R33" t="n">
-        <v>7393002</v>
+        <v>7393009</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685799</v>
+        <v>128685808</v>
       </c>
       <c r="B34" t="n">
-        <v>92887</v>
+        <v>79105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810790</v>
+        <v>811520</v>
       </c>
       <c r="R34" t="n">
-        <v>7392931</v>
+        <v>7393156</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685861</v>
+        <v>128685758</v>
       </c>
       <c r="B35" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810965</v>
+        <v>810717</v>
       </c>
       <c r="R35" t="n">
-        <v>7393009</v>
+        <v>7393072</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685833</v>
+        <v>128685807</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79105</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811464</v>
+        <v>811004</v>
       </c>
       <c r="R38" t="n">
-        <v>7393013</v>
+        <v>7392787</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685807</v>
+        <v>128685833</v>
       </c>
       <c r="B39" t="n">
-        <v>79105</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811004</v>
+        <v>811464</v>
       </c>
       <c r="R39" t="n">
-        <v>7392787</v>
+        <v>7393013</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685798</v>
+        <v>128685818</v>
       </c>
       <c r="B41" t="n">
-        <v>92887</v>
+        <v>90218</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>4962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810767</v>
+        <v>811120</v>
       </c>
       <c r="R41" t="n">
-        <v>7393075</v>
+        <v>7392983</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685818</v>
+        <v>128685814</v>
       </c>
       <c r="B42" t="n">
-        <v>90218</v>
+        <v>78839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811120</v>
+        <v>810773</v>
       </c>
       <c r="R42" t="n">
-        <v>7392983</v>
+        <v>7392966</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685814</v>
+        <v>128685798</v>
       </c>
       <c r="B43" t="n">
-        <v>78839</v>
+        <v>92887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810773</v>
+        <v>810767</v>
       </c>
       <c r="R43" t="n">
-        <v>7392966</v>
+        <v>7393075</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685792</v>
+        <v>128685875</v>
       </c>
       <c r="B47" t="n">
-        <v>92900</v>
+        <v>92869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811023</v>
+        <v>811283</v>
       </c>
       <c r="R47" t="n">
-        <v>7392776</v>
+        <v>7392844</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B48" t="n">
         <v>92900</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R48" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685875</v>
+        <v>128685793</v>
       </c>
       <c r="B49" t="n">
-        <v>92869</v>
+        <v>92900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811283</v>
+        <v>810740</v>
       </c>
       <c r="R49" t="n">
-        <v>7392844</v>
+        <v>7393062</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685844</v>
+        <v>128685767</v>
       </c>
       <c r="B52" t="n">
-        <v>92875</v>
+        <v>87024</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810873</v>
+        <v>811516</v>
       </c>
       <c r="R52" t="n">
-        <v>7392973</v>
+        <v>7393158</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685803</v>
+        <v>128685844</v>
       </c>
       <c r="B53" t="n">
-        <v>92887</v>
+        <v>92875</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810733</v>
+        <v>810873</v>
       </c>
       <c r="R53" t="n">
-        <v>7393068</v>
+        <v>7392973</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685868</v>
+        <v>128685803</v>
       </c>
       <c r="B54" t="n">
-        <v>92875</v>
+        <v>92887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5737,21 +5737,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810757</v>
+        <v>810733</v>
       </c>
       <c r="R54" t="n">
-        <v>7393053</v>
+        <v>7393068</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685855</v>
+        <v>128685868</v>
       </c>
       <c r="B55" t="n">
         <v>92875</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811502</v>
+        <v>810757</v>
       </c>
       <c r="R55" t="n">
-        <v>7393143</v>
+        <v>7393053</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685850</v>
+        <v>128685876</v>
       </c>
       <c r="B56" t="n">
-        <v>92875</v>
+        <v>92869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810978</v>
+        <v>811269</v>
       </c>
       <c r="R56" t="n">
-        <v>7392914</v>
+        <v>7392821</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6017,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685815</v>
+        <v>128685855</v>
       </c>
       <c r="B57" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810946</v>
+        <v>811502</v>
       </c>
       <c r="R57" t="n">
-        <v>7392983</v>
+        <v>7393143</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685767</v>
+        <v>128685850</v>
       </c>
       <c r="B58" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811516</v>
+        <v>810978</v>
       </c>
       <c r="R58" t="n">
-        <v>7393158</v>
+        <v>7392914</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,32 +6211,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685876</v>
+        <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>92869</v>
+        <v>58106</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811269</v>
+        <v>811127</v>
       </c>
       <c r="R59" t="n">
-        <v>7392821</v>
+        <v>7392976</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685823</v>
+        <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>58106</v>
+        <v>78839</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811127</v>
+        <v>810946</v>
       </c>
       <c r="R60" t="n">
-        <v>7392976</v>
+        <v>7392983</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6891,32 +6891,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685789</v>
+        <v>128685806</v>
       </c>
       <c r="B66" t="n">
-        <v>90416</v>
+        <v>79105</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811258</v>
+        <v>811056</v>
       </c>
       <c r="R66" t="n">
-        <v>7392822</v>
+        <v>7392881</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6970,7 +6970,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -6989,32 +6988,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685806</v>
+        <v>128685789</v>
       </c>
       <c r="B67" t="n">
-        <v>79105</v>
+        <v>90416</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7023,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811056</v>
+        <v>811258</v>
       </c>
       <c r="R67" t="n">
-        <v>7392881</v>
+        <v>7392822</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7068,6 +7067,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685856</v>
+        <v>128685872</v>
       </c>
       <c r="B72" t="n">
-        <v>92875</v>
+        <v>92869</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811494</v>
+        <v>811269</v>
       </c>
       <c r="R72" t="n">
-        <v>7393153</v>
+        <v>7392839</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685754</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>79700</v>
+        <v>92875</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811026</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7393053</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685872</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92869</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7679,21 +7679,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811269</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7392839</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>90218</v>
+        <v>92875</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R79" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685851</v>
+        <v>128685819</v>
       </c>
       <c r="B80" t="n">
-        <v>92875</v>
+        <v>90218</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811062</v>
+        <v>810744</v>
       </c>
       <c r="R80" t="n">
-        <v>7392883</v>
+        <v>7393058</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685748</v>
+        <v>128685817</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>90218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810767</v>
+        <v>811007</v>
       </c>
       <c r="R83" t="n">
-        <v>7392968</v>
+        <v>7392796</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B84" t="n">
-        <v>90218</v>
+        <v>79700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8649,21 +8649,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9317,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685763</v>
+        <v>128685852</v>
       </c>
       <c r="B91" t="n">
-        <v>87024</v>
+        <v>92875</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811097</v>
+        <v>811057</v>
       </c>
       <c r="R91" t="n">
-        <v>7392723</v>
+        <v>7392877</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,7 +9396,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9414,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685852</v>
+        <v>128685801</v>
       </c>
       <c r="B92" t="n">
-        <v>92875</v>
+        <v>92887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9426,21 +9425,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9449,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811057</v>
+        <v>811116</v>
       </c>
       <c r="R92" t="n">
-        <v>7392877</v>
+        <v>7392980</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9512,32 +9511,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B93" t="n">
-        <v>92887</v>
+        <v>87024</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9546,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R93" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9591,6 +9590,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685843</v>
+        <v>128685790</v>
       </c>
       <c r="B2" t="n">
-        <v>92875</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810858</v>
+        <v>810977</v>
       </c>
       <c r="R2" t="n">
-        <v>7392973</v>
+        <v>7393016</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685790</v>
+        <v>128685783</v>
       </c>
       <c r="B6" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810977</v>
+        <v>811497</v>
       </c>
       <c r="R6" t="n">
-        <v>7393016</v>
+        <v>7393112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685783</v>
+        <v>128685843</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>92879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811497</v>
+        <v>810858</v>
       </c>
       <c r="R7" t="n">
-        <v>7393112</v>
+        <v>7392973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
         <v>128685804</v>
       </c>
       <c r="B8" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685795</v>
+        <v>128685874</v>
       </c>
       <c r="B11" t="n">
-        <v>92520</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810915</v>
+        <v>811502</v>
       </c>
       <c r="R11" t="n">
-        <v>7393042</v>
+        <v>7393150</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685874</v>
+        <v>128685866</v>
       </c>
       <c r="B12" t="n">
-        <v>92869</v>
+        <v>92879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811502</v>
+        <v>810789</v>
       </c>
       <c r="R12" t="n">
-        <v>7393150</v>
+        <v>7393036</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685866</v>
+        <v>128685769</v>
       </c>
       <c r="B13" t="n">
-        <v>92875</v>
+        <v>87028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810789</v>
+        <v>810725</v>
       </c>
       <c r="R13" t="n">
-        <v>7393036</v>
+        <v>7393066</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685769</v>
+        <v>128685795</v>
       </c>
       <c r="B14" t="n">
-        <v>87024</v>
+        <v>92524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810725</v>
+        <v>810915</v>
       </c>
       <c r="R14" t="n">
-        <v>7393066</v>
+        <v>7393042</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87024</v>
+        <v>87028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685773</v>
+        <v>128685826</v>
       </c>
       <c r="B17" t="n">
-        <v>87024</v>
+        <v>78838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811089</v>
+        <v>811021</v>
       </c>
       <c r="R17" t="n">
-        <v>7393040</v>
+        <v>7392844</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685753</v>
+        <v>128685760</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R18" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685829</v>
+        <v>128685773</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>87028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R19" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685826</v>
+        <v>128685753</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811021</v>
+        <v>811087</v>
       </c>
       <c r="R20" t="n">
-        <v>7392844</v>
+        <v>7393042</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685829</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685778</v>
+        <v>128685816</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811517</v>
+        <v>810920</v>
       </c>
       <c r="R22" t="n">
-        <v>7393148</v>
+        <v>7393003</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685854</v>
+        <v>128685831</v>
       </c>
       <c r="B23" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811441</v>
+        <v>810853</v>
       </c>
       <c r="R23" t="n">
-        <v>7393097</v>
+        <v>7393047</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685873</v>
+        <v>128685854</v>
       </c>
       <c r="B24" t="n">
-        <v>92869</v>
+        <v>92879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811303</v>
+        <v>811441</v>
       </c>
       <c r="R24" t="n">
-        <v>7392893</v>
+        <v>7393097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685802</v>
+        <v>128685873</v>
       </c>
       <c r="B25" t="n">
-        <v>92887</v>
+        <v>92873</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811027</v>
+        <v>811303</v>
       </c>
       <c r="R25" t="n">
-        <v>7393042</v>
+        <v>7392893</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685869</v>
+        <v>128685802</v>
       </c>
       <c r="B26" t="n">
-        <v>92875</v>
+        <v>92891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3020,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810738</v>
+        <v>811027</v>
       </c>
       <c r="R26" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685869</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>92879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>810738</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7393051</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685816</v>
+        <v>128685778</v>
       </c>
       <c r="B28" t="n">
-        <v>78839</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810920</v>
+        <v>811517</v>
       </c>
       <c r="R28" t="n">
-        <v>7393003</v>
+        <v>7393148</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685785</v>
+        <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>92891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811518</v>
+        <v>810790</v>
       </c>
       <c r="R30" t="n">
-        <v>7393070</v>
+        <v>7392931</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685776</v>
+        <v>128685861</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>92879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810803</v>
+        <v>810965</v>
       </c>
       <c r="R31" t="n">
-        <v>7392998</v>
+        <v>7393009</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685799</v>
+        <v>128685808</v>
       </c>
       <c r="B32" t="n">
-        <v>92887</v>
+        <v>79105</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3602,21 +3602,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810790</v>
+        <v>811520</v>
       </c>
       <c r="R32" t="n">
-        <v>7392931</v>
+        <v>7393156</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,32 +3688,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685861</v>
+        <v>128685758</v>
       </c>
       <c r="B33" t="n">
-        <v>92875</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810965</v>
+        <v>810717</v>
       </c>
       <c r="R33" t="n">
-        <v>7393009</v>
+        <v>7393072</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685808</v>
+        <v>128685785</v>
       </c>
       <c r="B34" t="n">
-        <v>79105</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811520</v>
+        <v>811518</v>
       </c>
       <c r="R34" t="n">
-        <v>7393156</v>
+        <v>7393070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685758</v>
+        <v>128685776</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810717</v>
+        <v>810803</v>
       </c>
       <c r="R35" t="n">
-        <v>7393072</v>
+        <v>7392998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
         <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685818</v>
+        <v>128685761</v>
       </c>
       <c r="B41" t="n">
-        <v>90218</v>
+        <v>87028</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4962</v>
+        <v>3690</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811120</v>
+        <v>811014</v>
       </c>
       <c r="R41" t="n">
-        <v>7392983</v>
+        <v>7392891</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4543,6 +4543,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4561,32 +4562,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685814</v>
+        <v>128685798</v>
       </c>
       <c r="B42" t="n">
-        <v>78839</v>
+        <v>92891</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4597,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810773</v>
+        <v>810767</v>
       </c>
       <c r="R42" t="n">
-        <v>7392966</v>
+        <v>7393075</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4659,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685798</v>
+        <v>128685877</v>
       </c>
       <c r="B43" t="n">
-        <v>92887</v>
+        <v>92873</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810767</v>
+        <v>811258</v>
       </c>
       <c r="R43" t="n">
-        <v>7393075</v>
+        <v>7392822</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685877</v>
+        <v>128685818</v>
       </c>
       <c r="B44" t="n">
-        <v>92869</v>
+        <v>90222</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811258</v>
+        <v>811120</v>
       </c>
       <c r="R44" t="n">
-        <v>7392822</v>
+        <v>7392983</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685761</v>
+        <v>128685828</v>
       </c>
       <c r="B45" t="n">
-        <v>87024</v>
+        <v>78838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811014</v>
+        <v>811225</v>
       </c>
       <c r="R45" t="n">
-        <v>7392891</v>
+        <v>7392837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4931,7 +4932,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685828</v>
+        <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811225</v>
+        <v>810773</v>
       </c>
       <c r="R46" t="n">
-        <v>7392837</v>
+        <v>7392966</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685875</v>
+        <v>128685792</v>
       </c>
       <c r="B47" t="n">
-        <v>92869</v>
+        <v>92904</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811283</v>
+        <v>811023</v>
       </c>
       <c r="R47" t="n">
-        <v>7392844</v>
+        <v>7392776</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B48" t="n">
-        <v>92900</v>
+        <v>92904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R48" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,32 +5241,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685793</v>
+        <v>128685809</v>
       </c>
       <c r="B49" t="n">
-        <v>92900</v>
+        <v>79105</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>6434</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810740</v>
+        <v>811105</v>
       </c>
       <c r="R49" t="n">
-        <v>7393062</v>
+        <v>7393054</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B50" t="n">
-        <v>79105</v>
+        <v>92873</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R50" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685767</v>
+        <v>128685844</v>
       </c>
       <c r="B52" t="n">
-        <v>87024</v>
+        <v>92879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811516</v>
+        <v>810873</v>
       </c>
       <c r="R52" t="n">
-        <v>7393158</v>
+        <v>7392973</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685844</v>
+        <v>128685803</v>
       </c>
       <c r="B53" t="n">
-        <v>92875</v>
+        <v>92891</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810873</v>
+        <v>810733</v>
       </c>
       <c r="R53" t="n">
-        <v>7392973</v>
+        <v>7393068</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685803</v>
+        <v>128685868</v>
       </c>
       <c r="B54" t="n">
-        <v>92887</v>
+        <v>92879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5737,21 +5737,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810733</v>
+        <v>810757</v>
       </c>
       <c r="R54" t="n">
-        <v>7393068</v>
+        <v>7393053</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685868</v>
+        <v>128685876</v>
       </c>
       <c r="B55" t="n">
-        <v>92875</v>
+        <v>92873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810757</v>
+        <v>811269</v>
       </c>
       <c r="R55" t="n">
-        <v>7393053</v>
+        <v>7392821</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B56" t="n">
-        <v>92869</v>
+        <v>92879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R56" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685855</v>
+        <v>128685850</v>
       </c>
       <c r="B57" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811502</v>
+        <v>810978</v>
       </c>
       <c r="R57" t="n">
-        <v>7393143</v>
+        <v>7392914</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685850</v>
+        <v>128685767</v>
       </c>
       <c r="B58" t="n">
-        <v>92875</v>
+        <v>87028</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810978</v>
+        <v>811516</v>
       </c>
       <c r="R58" t="n">
-        <v>7392914</v>
+        <v>7393158</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6408,7 +6408,7 @@
         <v>128685771</v>
       </c>
       <c r="B61" t="n">
-        <v>87024</v>
+        <v>87028</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>128685800</v>
       </c>
       <c r="B62" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>128685859</v>
       </c>
       <c r="B63" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685812</v>
+        <v>128685789</v>
       </c>
       <c r="B64" t="n">
-        <v>79105</v>
+        <v>90420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>810948</v>
+        <v>811258</v>
       </c>
       <c r="R64" t="n">
-        <v>7392987</v>
+        <v>7392822</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6776,6 +6776,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6794,32 +6795,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685752</v>
+        <v>128685812</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>79105</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6830,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811410</v>
+        <v>810948</v>
       </c>
       <c r="R65" t="n">
-        <v>7392970</v>
+        <v>7392987</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6891,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685806</v>
+        <v>128685752</v>
       </c>
       <c r="B66" t="n">
-        <v>79105</v>
+        <v>79700</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6926,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811056</v>
+        <v>811410</v>
       </c>
       <c r="R66" t="n">
-        <v>7392881</v>
+        <v>7392970</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6988,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685789</v>
+        <v>128685806</v>
       </c>
       <c r="B67" t="n">
-        <v>90416</v>
+        <v>79105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6286</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7023,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811258</v>
+        <v>811056</v>
       </c>
       <c r="R67" t="n">
-        <v>7392822</v>
+        <v>7392881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7067,7 +7068,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685838</v>
+        <v>128685754</v>
       </c>
       <c r="B69" t="n">
-        <v>82916</v>
+        <v>79700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810781</v>
+        <v>811026</v>
       </c>
       <c r="R69" t="n">
-        <v>7392936</v>
+        <v>7393053</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685813</v>
+        <v>128685838</v>
       </c>
       <c r="B70" t="n">
-        <v>91646</v>
+        <v>82916</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810934</v>
+        <v>810781</v>
       </c>
       <c r="R70" t="n">
-        <v>7393019</v>
+        <v>7392936</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685840</v>
+        <v>128685813</v>
       </c>
       <c r="B71" t="n">
-        <v>92875</v>
+        <v>91650</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810762</v>
+        <v>810934</v>
       </c>
       <c r="R71" t="n">
-        <v>7393078</v>
+        <v>7393019</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685840</v>
       </c>
       <c r="B72" t="n">
-        <v>92869</v>
+        <v>92879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>810762</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7393078</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685872</v>
       </c>
       <c r="B73" t="n">
-        <v>92875</v>
+        <v>92873</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>811269</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7392839</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685856</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>92879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>811494</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7393153</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685864</v>
+        <v>128685822</v>
       </c>
       <c r="B75" t="n">
-        <v>92875</v>
+        <v>57840</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810814</v>
+        <v>810901</v>
       </c>
       <c r="R75" t="n">
-        <v>7393022</v>
+        <v>7393040</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685848</v>
+        <v>128685864</v>
       </c>
       <c r="B76" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810952</v>
+        <v>810814</v>
       </c>
       <c r="R76" t="n">
-        <v>7392920</v>
+        <v>7393022</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685846</v>
+        <v>128685848</v>
       </c>
       <c r="B77" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810911</v>
+        <v>810952</v>
       </c>
       <c r="R77" t="n">
-        <v>7392927</v>
+        <v>7392920</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685822</v>
+        <v>128685846</v>
       </c>
       <c r="B78" t="n">
-        <v>57840</v>
+        <v>92879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810901</v>
+        <v>810911</v>
       </c>
       <c r="R78" t="n">
-        <v>7393040</v>
+        <v>7392927</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8156,7 +8156,7 @@
         <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128685819</v>
       </c>
       <c r="B80" t="n">
-        <v>90218</v>
+        <v>90222</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685780</v>
+        <v>128685781</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811531</v>
+        <v>811507</v>
       </c>
       <c r="R81" t="n">
-        <v>7393153</v>
+        <v>7393120</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,7 +8444,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685781</v>
+        <v>128685780</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811507</v>
+        <v>811531</v>
       </c>
       <c r="R82" t="n">
-        <v>7393120</v>
+        <v>7393153</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8541,10 +8541,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685817</v>
+        <v>128685748</v>
       </c>
       <c r="B83" t="n">
-        <v>90218</v>
+        <v>79700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8552,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811007</v>
+        <v>810767</v>
       </c>
       <c r="R83" t="n">
-        <v>7392796</v>
+        <v>7392968</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685748</v>
+        <v>128685847</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>92879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810767</v>
+        <v>810944</v>
       </c>
       <c r="R84" t="n">
-        <v>7392968</v>
+        <v>7392948</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B85" t="n">
-        <v>92875</v>
+        <v>90222</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R85" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B86" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R86" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,32 +8929,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>92879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R87" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,10 +9026,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B88" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9037,21 +9037,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R88" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685796</v>
+        <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>92906</v>
+        <v>87028</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>232140</v>
+        <v>3690</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810795</v>
+        <v>810867</v>
       </c>
       <c r="R89" t="n">
-        <v>7393042</v>
+        <v>7392967</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685764</v>
+        <v>128685763</v>
       </c>
       <c r="B90" t="n">
-        <v>87024</v>
+        <v>87028</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>810867</v>
+        <v>811097</v>
       </c>
       <c r="R90" t="n">
-        <v>7392967</v>
+        <v>7392723</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,6 +9299,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9320,7 +9321,7 @@
         <v>128685852</v>
       </c>
       <c r="B91" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9417,7 +9418,7 @@
         <v>128685801</v>
       </c>
       <c r="B92" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9511,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685763</v>
+        <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>87024</v>
+        <v>92910</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3690</v>
+        <v>232140</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9546,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811097</v>
+        <v>810795</v>
       </c>
       <c r="R93" t="n">
-        <v>7392723</v>
+        <v>7393042</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9590,7 +9591,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9612,7 +9612,7 @@
         <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>87024</v>
+        <v>87028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685790</v>
+        <v>128685843</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810977</v>
+        <v>810858</v>
       </c>
       <c r="R2" t="n">
-        <v>7393016</v>
+        <v>7392973</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685837</v>
+        <v>128685836</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810756</v>
+        <v>811057</v>
       </c>
       <c r="R3" t="n">
-        <v>7393036</v>
+        <v>7393046</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685836</v>
+        <v>128685837</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811057</v>
+        <v>810756</v>
       </c>
       <c r="R4" t="n">
-        <v>7393046</v>
+        <v>7393036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685783</v>
+        <v>128685790</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>56926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811497</v>
+        <v>810977</v>
       </c>
       <c r="R6" t="n">
-        <v>7393112</v>
+        <v>7393016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685843</v>
+        <v>128685783</v>
       </c>
       <c r="B7" t="n">
-        <v>92879</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810858</v>
+        <v>811497</v>
       </c>
       <c r="R7" t="n">
-        <v>7392973</v>
+        <v>7393112</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
         <v>128685804</v>
       </c>
       <c r="B8" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128685853</v>
       </c>
       <c r="B9" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685874</v>
+        <v>128685810</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>79105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811502</v>
+        <v>811027</v>
       </c>
       <c r="R11" t="n">
-        <v>7393150</v>
+        <v>7393051</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685866</v>
+        <v>128685874</v>
       </c>
       <c r="B12" t="n">
-        <v>92879</v>
+        <v>92875</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810789</v>
+        <v>811502</v>
       </c>
       <c r="R12" t="n">
-        <v>7393036</v>
+        <v>7393150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685769</v>
+        <v>128685795</v>
       </c>
       <c r="B13" t="n">
-        <v>87028</v>
+        <v>92526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810725</v>
+        <v>810915</v>
       </c>
       <c r="R13" t="n">
-        <v>7393066</v>
+        <v>7393042</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685795</v>
+        <v>128685866</v>
       </c>
       <c r="B14" t="n">
-        <v>92524</v>
+        <v>92881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810915</v>
+        <v>810789</v>
       </c>
       <c r="R14" t="n">
-        <v>7393042</v>
+        <v>7393036</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685810</v>
+        <v>128685769</v>
       </c>
       <c r="B15" t="n">
-        <v>79105</v>
+        <v>87030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811027</v>
+        <v>810725</v>
       </c>
       <c r="R15" t="n">
-        <v>7393051</v>
+        <v>7393066</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87028</v>
+        <v>87030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685826</v>
+        <v>128685760</v>
       </c>
       <c r="B17" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R17" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685760</v>
+        <v>128685753</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685773</v>
+        <v>128685829</v>
       </c>
       <c r="B19" t="n">
-        <v>87028</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811089</v>
+        <v>810920</v>
       </c>
       <c r="R19" t="n">
-        <v>7393040</v>
+        <v>7393003</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2408,7 +2408,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685753</v>
+        <v>128685826</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811087</v>
+        <v>811021</v>
       </c>
       <c r="R20" t="n">
-        <v>7393042</v>
+        <v>7392844</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2524,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685829</v>
+        <v>128685773</v>
       </c>
       <c r="B21" t="n">
-        <v>78838</v>
+        <v>87030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R21" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2603,6 +2602,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685816</v>
+        <v>128685831</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810920</v>
+        <v>810853</v>
       </c>
       <c r="R22" t="n">
-        <v>7393003</v>
+        <v>7393047</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685831</v>
+        <v>128685854</v>
       </c>
       <c r="B23" t="n">
-        <v>78838</v>
+        <v>92881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810853</v>
+        <v>811441</v>
       </c>
       <c r="R23" t="n">
-        <v>7393047</v>
+        <v>7393097</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685854</v>
+        <v>128685873</v>
       </c>
       <c r="B24" t="n">
-        <v>92879</v>
+        <v>92875</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811441</v>
+        <v>811303</v>
       </c>
       <c r="R24" t="n">
-        <v>7393097</v>
+        <v>7392893</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685873</v>
+        <v>128685802</v>
       </c>
       <c r="B25" t="n">
-        <v>92873</v>
+        <v>92893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811303</v>
+        <v>811027</v>
       </c>
       <c r="R25" t="n">
-        <v>7392893</v>
+        <v>7393042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685802</v>
+        <v>128685869</v>
       </c>
       <c r="B26" t="n">
-        <v>92891</v>
+        <v>92881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3020,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811027</v>
+        <v>810738</v>
       </c>
       <c r="R26" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,32 +3106,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685869</v>
+        <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>92879</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810738</v>
+        <v>811517</v>
       </c>
       <c r="R27" t="n">
-        <v>7393051</v>
+        <v>7393148</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685778</v>
+        <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>78839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811517</v>
+        <v>810920</v>
       </c>
       <c r="R28" t="n">
-        <v>7393148</v>
+        <v>7393003</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
         <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>128685861</v>
       </c>
       <c r="B31" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685808</v>
+        <v>128685776</v>
       </c>
       <c r="B32" t="n">
-        <v>79105</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811520</v>
+        <v>810803</v>
       </c>
       <c r="R32" t="n">
-        <v>7393156</v>
+        <v>7392998</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685758</v>
+        <v>128685785</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810717</v>
+        <v>811518</v>
       </c>
       <c r="R33" t="n">
-        <v>7393072</v>
+        <v>7393070</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685785</v>
+        <v>128685808</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>79105</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811518</v>
+        <v>811520</v>
       </c>
       <c r="R34" t="n">
-        <v>7393070</v>
+        <v>7393156</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685776</v>
+        <v>128685758</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810803</v>
+        <v>810717</v>
       </c>
       <c r="R35" t="n">
-        <v>7392998</v>
+        <v>7393072</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
         <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685761</v>
+        <v>128685798</v>
       </c>
       <c r="B41" t="n">
-        <v>87028</v>
+        <v>92893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811014</v>
+        <v>810767</v>
       </c>
       <c r="R41" t="n">
-        <v>7392891</v>
+        <v>7393075</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4543,7 +4543,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4562,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685798</v>
+        <v>128685877</v>
       </c>
       <c r="B42" t="n">
-        <v>92891</v>
+        <v>92875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4597,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810767</v>
+        <v>811258</v>
       </c>
       <c r="R42" t="n">
-        <v>7393075</v>
+        <v>7392822</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4659,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685877</v>
+        <v>128685761</v>
       </c>
       <c r="B43" t="n">
-        <v>92873</v>
+        <v>87030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4670,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4694,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811258</v>
+        <v>811014</v>
       </c>
       <c r="R43" t="n">
-        <v>7392822</v>
+        <v>7392891</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4738,6 +4737,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685818</v>
+        <v>128685828</v>
       </c>
       <c r="B44" t="n">
-        <v>90222</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4962</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811120</v>
+        <v>811225</v>
       </c>
       <c r="R44" t="n">
-        <v>7392983</v>
+        <v>7392837</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685828</v>
+        <v>128685814</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811225</v>
+        <v>810773</v>
       </c>
       <c r="R45" t="n">
-        <v>7392837</v>
+        <v>7392966</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685814</v>
+        <v>128685818</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>90224</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810773</v>
+        <v>811120</v>
       </c>
       <c r="R46" t="n">
-        <v>7392966</v>
+        <v>7392983</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5050,7 +5050,7 @@
         <v>128685792</v>
       </c>
       <c r="B47" t="n">
-        <v>92904</v>
+        <v>92906</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128685793</v>
       </c>
       <c r="B48" t="n">
-        <v>92904</v>
+        <v>92906</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5241,32 +5241,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B49" t="n">
-        <v>79105</v>
+        <v>92875</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R49" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685875</v>
+        <v>128685777</v>
       </c>
       <c r="B50" t="n">
-        <v>92873</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5349,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811283</v>
+        <v>811015</v>
       </c>
       <c r="R50" t="n">
-        <v>7392844</v>
+        <v>7392800</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>79105</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R51" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685844</v>
+        <v>128685823</v>
       </c>
       <c r="B52" t="n">
-        <v>92879</v>
+        <v>58106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810873</v>
+        <v>811127</v>
       </c>
       <c r="R52" t="n">
-        <v>7392973</v>
+        <v>7392976</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685803</v>
+        <v>128685815</v>
       </c>
       <c r="B53" t="n">
-        <v>92891</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810733</v>
+        <v>810946</v>
       </c>
       <c r="R53" t="n">
-        <v>7393068</v>
+        <v>7392983</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685868</v>
+        <v>128685767</v>
       </c>
       <c r="B54" t="n">
-        <v>92879</v>
+        <v>87030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810757</v>
+        <v>811516</v>
       </c>
       <c r="R54" t="n">
-        <v>7393053</v>
+        <v>7393158</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685876</v>
+        <v>128685844</v>
       </c>
       <c r="B55" t="n">
-        <v>92873</v>
+        <v>92881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811269</v>
+        <v>810873</v>
       </c>
       <c r="R55" t="n">
-        <v>7392821</v>
+        <v>7392973</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685855</v>
+        <v>128685803</v>
       </c>
       <c r="B56" t="n">
-        <v>92879</v>
+        <v>92893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811502</v>
+        <v>810733</v>
       </c>
       <c r="R56" t="n">
-        <v>7393143</v>
+        <v>7393068</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685850</v>
+        <v>128685868</v>
       </c>
       <c r="B57" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810978</v>
+        <v>810757</v>
       </c>
       <c r="R57" t="n">
-        <v>7392914</v>
+        <v>7393053</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685767</v>
+        <v>128685876</v>
       </c>
       <c r="B58" t="n">
-        <v>87028</v>
+        <v>92875</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811516</v>
+        <v>811269</v>
       </c>
       <c r="R58" t="n">
-        <v>7393158</v>
+        <v>7392821</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685823</v>
+        <v>128685855</v>
       </c>
       <c r="B59" t="n">
-        <v>58106</v>
+        <v>92881</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811127</v>
+        <v>811502</v>
       </c>
       <c r="R59" t="n">
-        <v>7392976</v>
+        <v>7393143</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685815</v>
+        <v>128685850</v>
       </c>
       <c r="B60" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810946</v>
+        <v>810978</v>
       </c>
       <c r="R60" t="n">
-        <v>7392983</v>
+        <v>7392914</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B61" t="n">
-        <v>87028</v>
+        <v>90422</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R61" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6503,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685800</v>
+        <v>128685788</v>
       </c>
       <c r="B62" t="n">
-        <v>92891</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810861</v>
+        <v>811107</v>
       </c>
       <c r="R62" t="n">
-        <v>7392976</v>
+        <v>7393022</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685859</v>
+        <v>128685812</v>
       </c>
       <c r="B63" t="n">
-        <v>92879</v>
+        <v>79105</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6611,21 +6611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811498</v>
+        <v>810948</v>
       </c>
       <c r="R63" t="n">
-        <v>7393147</v>
+        <v>7392987</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685789</v>
+        <v>128685752</v>
       </c>
       <c r="B64" t="n">
-        <v>90420</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811258</v>
+        <v>811410</v>
       </c>
       <c r="R64" t="n">
-        <v>7392822</v>
+        <v>7392970</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6776,7 +6776,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6795,7 +6794,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685812</v>
+        <v>128685806</v>
       </c>
       <c r="B65" t="n">
         <v>79105</v>
@@ -6830,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>810948</v>
+        <v>811056</v>
       </c>
       <c r="R65" t="n">
-        <v>7392987</v>
+        <v>7392881</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6892,10 +6891,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685752</v>
+        <v>128685771</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>87030</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6903,21 +6902,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6926,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811410</v>
+        <v>811112</v>
       </c>
       <c r="R66" t="n">
-        <v>7392970</v>
+        <v>7393038</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6971,6 +6970,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685806</v>
+        <v>128685800</v>
       </c>
       <c r="B67" t="n">
-        <v>79105</v>
+        <v>92893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811056</v>
+        <v>810861</v>
       </c>
       <c r="R67" t="n">
-        <v>7392881</v>
+        <v>7392976</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685788</v>
+        <v>128685859</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>92881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811107</v>
+        <v>811498</v>
       </c>
       <c r="R68" t="n">
-        <v>7393022</v>
+        <v>7393147</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685754</v>
+        <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>79700</v>
+        <v>82918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811026</v>
+        <v>810781</v>
       </c>
       <c r="R69" t="n">
-        <v>7393053</v>
+        <v>7392936</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685838</v>
+        <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>82916</v>
+        <v>91652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7291,21 +7291,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810781</v>
+        <v>810934</v>
       </c>
       <c r="R70" t="n">
-        <v>7392936</v>
+        <v>7393019</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685813</v>
+        <v>128685840</v>
       </c>
       <c r="B71" t="n">
-        <v>91650</v>
+        <v>92881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810934</v>
+        <v>810762</v>
       </c>
       <c r="R71" t="n">
-        <v>7393019</v>
+        <v>7393078</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685840</v>
+        <v>128685872</v>
       </c>
       <c r="B72" t="n">
-        <v>92879</v>
+        <v>92875</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810762</v>
+        <v>811269</v>
       </c>
       <c r="R72" t="n">
-        <v>7393078</v>
+        <v>7392839</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685872</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>92873</v>
+        <v>92881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811269</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7392839</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92879</v>
+        <v>79700</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685822</v>
+        <v>128685864</v>
       </c>
       <c r="B75" t="n">
-        <v>57840</v>
+        <v>92881</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810901</v>
+        <v>810814</v>
       </c>
       <c r="R75" t="n">
-        <v>7393040</v>
+        <v>7393022</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685864</v>
+        <v>128685848</v>
       </c>
       <c r="B76" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810814</v>
+        <v>810952</v>
       </c>
       <c r="R76" t="n">
-        <v>7393022</v>
+        <v>7392920</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685848</v>
+        <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810952</v>
+        <v>810911</v>
       </c>
       <c r="R77" t="n">
-        <v>7392920</v>
+        <v>7392927</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685846</v>
+        <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>92879</v>
+        <v>57840</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810911</v>
+        <v>810901</v>
       </c>
       <c r="R78" t="n">
-        <v>7392927</v>
+        <v>7393040</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8156,7 +8156,7 @@
         <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>128685819</v>
       </c>
       <c r="B80" t="n">
-        <v>90222</v>
+        <v>90224</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685781</v>
+        <v>128685780</v>
       </c>
       <c r="B81" t="n">
         <v>57736</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811507</v>
+        <v>811531</v>
       </c>
       <c r="R81" t="n">
-        <v>7393120</v>
+        <v>7393153</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,7 +8444,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685780</v>
+        <v>128685781</v>
       </c>
       <c r="B82" t="n">
         <v>57736</v>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811531</v>
+        <v>811507</v>
       </c>
       <c r="R82" t="n">
-        <v>7393153</v>
+        <v>7393120</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B84" t="n">
-        <v>92879</v>
+        <v>90224</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R84" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B85" t="n">
-        <v>90222</v>
+        <v>92881</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R85" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B86" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R86" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,32 +8929,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B87" t="n">
-        <v>92879</v>
+        <v>78838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R87" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R88" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9126,7 +9126,7 @@
         <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>87028</v>
+        <v>87030</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685763</v>
+        <v>128685852</v>
       </c>
       <c r="B90" t="n">
-        <v>87028</v>
+        <v>92881</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811097</v>
+        <v>811057</v>
       </c>
       <c r="R90" t="n">
-        <v>7392723</v>
+        <v>7392877</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,7 +9299,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9318,10 +9317,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685852</v>
+        <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>92879</v>
+        <v>92893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9329,21 +9328,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9353,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811057</v>
+        <v>811116</v>
       </c>
       <c r="R91" t="n">
-        <v>7392877</v>
+        <v>7392980</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9415,32 +9414,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685801</v>
+        <v>128685763</v>
       </c>
       <c r="B92" t="n">
-        <v>92891</v>
+        <v>87030</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9449,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811116</v>
+        <v>811097</v>
       </c>
       <c r="R92" t="n">
-        <v>7392980</v>
+        <v>7392723</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9494,6 +9493,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9515,7 +9515,7 @@
         <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92910</v>
+        <v>92912</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685770</v>
+        <v>128685751</v>
       </c>
       <c r="B94" t="n">
-        <v>87028</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811050</v>
+        <v>811254</v>
       </c>
       <c r="R94" t="n">
-        <v>7393050</v>
+        <v>7392831</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,18 +9682,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9712,10 +9706,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685751</v>
+        <v>128685770</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>87030</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9723,21 +9717,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9747,10 +9741,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811254</v>
+        <v>811050</v>
       </c>
       <c r="R95" t="n">
-        <v>7392831</v>
+        <v>7393050</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9785,12 +9779,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685810</v>
+        <v>128685874</v>
       </c>
       <c r="B11" t="n">
-        <v>79105</v>
+        <v>92875</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811027</v>
+        <v>811502</v>
       </c>
       <c r="R11" t="n">
-        <v>7393051</v>
+        <v>7393150</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685874</v>
+        <v>128685795</v>
       </c>
       <c r="B12" t="n">
-        <v>92875</v>
+        <v>92526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811502</v>
+        <v>810915</v>
       </c>
       <c r="R12" t="n">
-        <v>7393150</v>
+        <v>7393042</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685795</v>
+        <v>128685866</v>
       </c>
       <c r="B13" t="n">
-        <v>92526</v>
+        <v>92881</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810915</v>
+        <v>810789</v>
       </c>
       <c r="R13" t="n">
-        <v>7393042</v>
+        <v>7393036</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685866</v>
+        <v>128685769</v>
       </c>
       <c r="B14" t="n">
-        <v>92881</v>
+        <v>87030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810789</v>
+        <v>810725</v>
       </c>
       <c r="R14" t="n">
-        <v>7393036</v>
+        <v>7393066</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685769</v>
+        <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>87030</v>
+        <v>79105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3690</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810725</v>
+        <v>811027</v>
       </c>
       <c r="R15" t="n">
-        <v>7393066</v>
+        <v>7393051</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685831</v>
+        <v>128685816</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810853</v>
+        <v>810920</v>
       </c>
       <c r="R22" t="n">
-        <v>7393047</v>
+        <v>7393003</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685816</v>
+        <v>128685831</v>
       </c>
       <c r="B28" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810920</v>
+        <v>810853</v>
       </c>
       <c r="R28" t="n">
-        <v>7393003</v>
+        <v>7393047</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685798</v>
+        <v>128685828</v>
       </c>
       <c r="B41" t="n">
-        <v>92893</v>
+        <v>78838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810767</v>
+        <v>811225</v>
       </c>
       <c r="R41" t="n">
-        <v>7393075</v>
+        <v>7392837</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685877</v>
+        <v>128685814</v>
       </c>
       <c r="B42" t="n">
-        <v>92875</v>
+        <v>78839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811258</v>
+        <v>810773</v>
       </c>
       <c r="R42" t="n">
-        <v>7392822</v>
+        <v>7392966</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685761</v>
+        <v>128685798</v>
       </c>
       <c r="B43" t="n">
-        <v>87030</v>
+        <v>92893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811014</v>
+        <v>810767</v>
       </c>
       <c r="R43" t="n">
-        <v>7392891</v>
+        <v>7393075</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4737,7 +4737,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685828</v>
+        <v>128685877</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>92875</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811225</v>
+        <v>811258</v>
       </c>
       <c r="R44" t="n">
-        <v>7392837</v>
+        <v>7392822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685814</v>
+        <v>128685761</v>
       </c>
       <c r="B45" t="n">
-        <v>78839</v>
+        <v>87030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4863,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>3690</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4887,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810773</v>
+        <v>811014</v>
       </c>
       <c r="R45" t="n">
-        <v>7392966</v>
+        <v>7392891</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4932,6 +4931,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685823</v>
+        <v>128685767</v>
       </c>
       <c r="B52" t="n">
-        <v>58106</v>
+        <v>87030</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>3690</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811127</v>
+        <v>811516</v>
       </c>
       <c r="R52" t="n">
-        <v>7392976</v>
+        <v>7393158</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685815</v>
+        <v>128685844</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>92881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810946</v>
+        <v>810873</v>
       </c>
       <c r="R53" t="n">
-        <v>7392983</v>
+        <v>7392973</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685767</v>
+        <v>128685803</v>
       </c>
       <c r="B54" t="n">
-        <v>87030</v>
+        <v>92893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811516</v>
+        <v>810733</v>
       </c>
       <c r="R54" t="n">
-        <v>7393158</v>
+        <v>7393068</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685844</v>
+        <v>128685868</v>
       </c>
       <c r="B55" t="n">
         <v>92881</v>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810873</v>
+        <v>810757</v>
       </c>
       <c r="R55" t="n">
-        <v>7392973</v>
+        <v>7393053</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685803</v>
+        <v>128685876</v>
       </c>
       <c r="B56" t="n">
-        <v>92893</v>
+        <v>92875</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810733</v>
+        <v>811269</v>
       </c>
       <c r="R56" t="n">
-        <v>7393068</v>
+        <v>7392821</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685868</v>
+        <v>128685855</v>
       </c>
       <c r="B57" t="n">
         <v>92881</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810757</v>
+        <v>811502</v>
       </c>
       <c r="R57" t="n">
-        <v>7393053</v>
+        <v>7393143</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685876</v>
+        <v>128685850</v>
       </c>
       <c r="B58" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811269</v>
+        <v>810978</v>
       </c>
       <c r="R58" t="n">
-        <v>7392821</v>
+        <v>7392914</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685855</v>
+        <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>92881</v>
+        <v>58106</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811502</v>
+        <v>811127</v>
       </c>
       <c r="R59" t="n">
-        <v>7393143</v>
+        <v>7392976</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6308,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685850</v>
+        <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>92881</v>
+        <v>78839</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810978</v>
+        <v>810946</v>
       </c>
       <c r="R60" t="n">
-        <v>7392914</v>
+        <v>7392983</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685864</v>
+        <v>128685822</v>
       </c>
       <c r="B75" t="n">
-        <v>92881</v>
+        <v>57840</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810814</v>
+        <v>810901</v>
       </c>
       <c r="R75" t="n">
-        <v>7393022</v>
+        <v>7393040</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685848</v>
+        <v>128685864</v>
       </c>
       <c r="B76" t="n">
         <v>92881</v>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810952</v>
+        <v>810814</v>
       </c>
       <c r="R76" t="n">
-        <v>7392920</v>
+        <v>7393022</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685846</v>
+        <v>128685848</v>
       </c>
       <c r="B77" t="n">
         <v>92881</v>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810911</v>
+        <v>810952</v>
       </c>
       <c r="R77" t="n">
-        <v>7392927</v>
+        <v>7392920</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685822</v>
+        <v>128685846</v>
       </c>
       <c r="B78" t="n">
-        <v>57840</v>
+        <v>92881</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810901</v>
+        <v>810911</v>
       </c>
       <c r="R78" t="n">
-        <v>7393040</v>
+        <v>7392927</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685748</v>
+        <v>128685847</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810767</v>
+        <v>810944</v>
       </c>
       <c r="R83" t="n">
-        <v>7392968</v>
+        <v>7392948</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8735,32 +8735,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685847</v>
+        <v>128685748</v>
       </c>
       <c r="B85" t="n">
-        <v>92881</v>
+        <v>79700</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810944</v>
+        <v>810767</v>
       </c>
       <c r="R85" t="n">
-        <v>7392948</v>
+        <v>7392968</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685816</v>
+        <v>128685831</v>
       </c>
       <c r="B22" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810920</v>
+        <v>810853</v>
       </c>
       <c r="R22" t="n">
-        <v>7393003</v>
+        <v>7393047</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685831</v>
+        <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810853</v>
+        <v>810920</v>
       </c>
       <c r="R28" t="n">
-        <v>7393047</v>
+        <v>7393003</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685839</v>
+        <v>128685808</v>
       </c>
       <c r="B29" t="n">
-        <v>78747</v>
+        <v>79105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811034</v>
+        <v>811520</v>
       </c>
       <c r="R29" t="n">
-        <v>7393002</v>
+        <v>7393156</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685799</v>
+        <v>128685758</v>
       </c>
       <c r="B30" t="n">
-        <v>92893</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810790</v>
+        <v>810717</v>
       </c>
       <c r="R30" t="n">
-        <v>7392931</v>
+        <v>7393072</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685861</v>
+        <v>128685839</v>
       </c>
       <c r="B31" t="n">
-        <v>92881</v>
+        <v>78747</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810965</v>
+        <v>811034</v>
       </c>
       <c r="R31" t="n">
-        <v>7393009</v>
+        <v>7393002</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685776</v>
+        <v>128685799</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>92893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810803</v>
+        <v>810790</v>
       </c>
       <c r="R32" t="n">
-        <v>7392998</v>
+        <v>7392931</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,32 +3688,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685785</v>
+        <v>128685861</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>92881</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811518</v>
+        <v>810965</v>
       </c>
       <c r="R33" t="n">
-        <v>7393070</v>
+        <v>7393009</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685808</v>
+        <v>128685785</v>
       </c>
       <c r="B34" t="n">
-        <v>79105</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811520</v>
+        <v>811518</v>
       </c>
       <c r="R34" t="n">
-        <v>7393156</v>
+        <v>7393070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685758</v>
+        <v>128685776</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3893,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810717</v>
+        <v>810803</v>
       </c>
       <c r="R35" t="n">
-        <v>7393072</v>
+        <v>7392998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685828</v>
+        <v>128685798</v>
       </c>
       <c r="B41" t="n">
-        <v>78838</v>
+        <v>92893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811225</v>
+        <v>810767</v>
       </c>
       <c r="R41" t="n">
-        <v>7392837</v>
+        <v>7393075</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685814</v>
+        <v>128685877</v>
       </c>
       <c r="B42" t="n">
-        <v>78839</v>
+        <v>92875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810773</v>
+        <v>811258</v>
       </c>
       <c r="R42" t="n">
-        <v>7392966</v>
+        <v>7392822</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,32 +4658,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685798</v>
+        <v>128685761</v>
       </c>
       <c r="B43" t="n">
-        <v>92893</v>
+        <v>87030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810767</v>
+        <v>811014</v>
       </c>
       <c r="R43" t="n">
-        <v>7393075</v>
+        <v>7392891</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4737,6 +4737,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4755,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685877</v>
+        <v>128685828</v>
       </c>
       <c r="B44" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811258</v>
+        <v>811225</v>
       </c>
       <c r="R44" t="n">
-        <v>7392822</v>
+        <v>7392837</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685761</v>
+        <v>128685814</v>
       </c>
       <c r="B45" t="n">
-        <v>87030</v>
+        <v>78839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811014</v>
+        <v>810773</v>
       </c>
       <c r="R45" t="n">
-        <v>7392891</v>
+        <v>7392966</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4931,7 +4932,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R86" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R87" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>92881</v>
+        <v>78838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R88" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685760</v>
+        <v>128685773</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>87030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R17" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2523,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685773</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>87030</v>
+        <v>79671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3690</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811089</v>
+        <v>810920</v>
       </c>
       <c r="R21" t="n">
-        <v>7393040</v>
+        <v>7393003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2602,7 +2603,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685843</v>
+        <v>128685837</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810858</v>
+        <v>810756</v>
       </c>
       <c r="R2" t="n">
-        <v>7392973</v>
+        <v>7393036</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685836</v>
+        <v>128685756</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811057</v>
+        <v>811013</v>
       </c>
       <c r="R3" t="n">
-        <v>7393046</v>
+        <v>7393006</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685837</v>
+        <v>128685836</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810756</v>
+        <v>811057</v>
       </c>
       <c r="R4" t="n">
-        <v>7393036</v>
+        <v>7393046</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685756</v>
+        <v>128685790</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811013</v>
+        <v>810977</v>
       </c>
       <c r="R5" t="n">
-        <v>7393006</v>
+        <v>7393016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685790</v>
+        <v>128685783</v>
       </c>
       <c r="B6" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810977</v>
+        <v>811497</v>
       </c>
       <c r="R6" t="n">
-        <v>7393016</v>
+        <v>7393112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685783</v>
+        <v>128685843</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>92881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811497</v>
+        <v>810858</v>
       </c>
       <c r="R7" t="n">
-        <v>7393112</v>
+        <v>7392973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685804</v>
+        <v>128685835</v>
       </c>
       <c r="B8" t="n">
-        <v>92893</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>810710</v>
+        <v>811420</v>
       </c>
       <c r="R8" t="n">
-        <v>7393058</v>
+        <v>7392954</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685853</v>
+        <v>128685804</v>
       </c>
       <c r="B9" t="n">
-        <v>92881</v>
+        <v>92893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811044</v>
+        <v>810710</v>
       </c>
       <c r="R9" t="n">
-        <v>7392879</v>
+        <v>7393058</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685835</v>
+        <v>128685853</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811420</v>
+        <v>811044</v>
       </c>
       <c r="R10" t="n">
-        <v>7392954</v>
+        <v>7392879</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685874</v>
+        <v>128685866</v>
       </c>
       <c r="B11" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811502</v>
+        <v>810789</v>
       </c>
       <c r="R11" t="n">
-        <v>7393150</v>
+        <v>7393036</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B12" t="n">
-        <v>92526</v>
+        <v>87030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R12" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685866</v>
+        <v>128685874</v>
       </c>
       <c r="B13" t="n">
-        <v>92881</v>
+        <v>92875</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>810789</v>
+        <v>811502</v>
       </c>
       <c r="R13" t="n">
-        <v>7393036</v>
+        <v>7393150</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685769</v>
+        <v>128685795</v>
       </c>
       <c r="B14" t="n">
-        <v>87030</v>
+        <v>92526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3690</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810725</v>
+        <v>810915</v>
       </c>
       <c r="R14" t="n">
-        <v>7393066</v>
+        <v>7393042</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685753</v>
+        <v>128685829</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R18" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685829</v>
+        <v>128685826</v>
       </c>
       <c r="B19" t="n">
         <v>78838</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810920</v>
+        <v>811021</v>
       </c>
       <c r="R19" t="n">
-        <v>7393003</v>
+        <v>7392844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685826</v>
+        <v>128685753</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811021</v>
+        <v>811087</v>
       </c>
       <c r="R20" t="n">
-        <v>7392844</v>
+        <v>7393042</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685831</v>
+        <v>128685873</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>92875</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810853</v>
+        <v>811303</v>
       </c>
       <c r="R22" t="n">
-        <v>7393047</v>
+        <v>7392893</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685873</v>
+        <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92875</v>
+        <v>92893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811303</v>
+        <v>811027</v>
       </c>
       <c r="R24" t="n">
-        <v>7392893</v>
+        <v>7393042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685802</v>
+        <v>128685869</v>
       </c>
       <c r="B25" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811027</v>
+        <v>810738</v>
       </c>
       <c r="R25" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685869</v>
+        <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>92881</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810738</v>
+        <v>810853</v>
       </c>
       <c r="R26" t="n">
-        <v>7393051</v>
+        <v>7393047</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685808</v>
+        <v>128685799</v>
       </c>
       <c r="B29" t="n">
-        <v>79105</v>
+        <v>92893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811520</v>
+        <v>810790</v>
       </c>
       <c r="R29" t="n">
-        <v>7393156</v>
+        <v>7392931</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685758</v>
+        <v>128685861</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810717</v>
+        <v>810965</v>
       </c>
       <c r="R30" t="n">
-        <v>7393072</v>
+        <v>7393009</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685839</v>
+        <v>128685808</v>
       </c>
       <c r="B31" t="n">
-        <v>78747</v>
+        <v>79105</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811034</v>
+        <v>811520</v>
       </c>
       <c r="R31" t="n">
-        <v>7393002</v>
+        <v>7393156</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685799</v>
+        <v>128685758</v>
       </c>
       <c r="B32" t="n">
-        <v>92893</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810790</v>
+        <v>810717</v>
       </c>
       <c r="R32" t="n">
-        <v>7392931</v>
+        <v>7393072</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,32 +3688,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685861</v>
+        <v>128685776</v>
       </c>
       <c r="B33" t="n">
-        <v>92881</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810965</v>
+        <v>810803</v>
       </c>
       <c r="R33" t="n">
-        <v>7393009</v>
+        <v>7392998</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685785</v>
+        <v>128685839</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>78747</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811518</v>
+        <v>811034</v>
       </c>
       <c r="R34" t="n">
-        <v>7393070</v>
+        <v>7393002</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685776</v>
+        <v>128685785</v>
       </c>
       <c r="B35" t="n">
         <v>57736</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810803</v>
+        <v>811518</v>
       </c>
       <c r="R35" t="n">
-        <v>7392998</v>
+        <v>7393070</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685807</v>
+        <v>128685833</v>
       </c>
       <c r="B38" t="n">
-        <v>79105</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811004</v>
+        <v>811464</v>
       </c>
       <c r="R38" t="n">
-        <v>7392787</v>
+        <v>7393013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685833</v>
+        <v>128685807</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79105</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811464</v>
+        <v>811004</v>
       </c>
       <c r="R39" t="n">
-        <v>7393013</v>
+        <v>7392787</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685877</v>
+        <v>128685828</v>
       </c>
       <c r="B42" t="n">
-        <v>92875</v>
+        <v>78838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811258</v>
+        <v>811225</v>
       </c>
       <c r="R42" t="n">
-        <v>7392822</v>
+        <v>7392837</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685761</v>
+        <v>128685877</v>
       </c>
       <c r="B43" t="n">
-        <v>87030</v>
+        <v>92875</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811014</v>
+        <v>811258</v>
       </c>
       <c r="R43" t="n">
-        <v>7392891</v>
+        <v>7392822</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4737,7 +4737,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4756,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685828</v>
+        <v>128685761</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>87030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811225</v>
+        <v>811014</v>
       </c>
       <c r="R44" t="n">
-        <v>7392837</v>
+        <v>7392891</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4835,6 +4834,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4853,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685814</v>
+        <v>128685818</v>
       </c>
       <c r="B45" t="n">
-        <v>78839</v>
+        <v>90224</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810773</v>
+        <v>811120</v>
       </c>
       <c r="R45" t="n">
-        <v>7392966</v>
+        <v>7392983</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685818</v>
+        <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>90224</v>
+        <v>78839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811120</v>
+        <v>810773</v>
       </c>
       <c r="R46" t="n">
-        <v>7392983</v>
+        <v>7392966</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B47" t="n">
         <v>92906</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R47" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B48" t="n">
         <v>92906</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R48" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>79105</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R50" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685809</v>
+        <v>128685777</v>
       </c>
       <c r="B51" t="n">
-        <v>79105</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811105</v>
+        <v>811015</v>
       </c>
       <c r="R51" t="n">
-        <v>7393054</v>
+        <v>7392800</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5532,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685767</v>
+        <v>128685823</v>
       </c>
       <c r="B52" t="n">
-        <v>87030</v>
+        <v>58106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3690</v>
+        <v>103015</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811516</v>
+        <v>811127</v>
       </c>
       <c r="R52" t="n">
-        <v>7393158</v>
+        <v>7392976</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685844</v>
+        <v>128685767</v>
       </c>
       <c r="B53" t="n">
-        <v>92881</v>
+        <v>87030</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810873</v>
+        <v>811516</v>
       </c>
       <c r="R53" t="n">
-        <v>7392973</v>
+        <v>7393158</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,10 +5726,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685803</v>
+        <v>128685850</v>
       </c>
       <c r="B54" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5737,21 +5737,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810733</v>
+        <v>810978</v>
       </c>
       <c r="R54" t="n">
-        <v>7393068</v>
+        <v>7392914</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685868</v>
+        <v>128685876</v>
       </c>
       <c r="B55" t="n">
-        <v>92881</v>
+        <v>92875</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810757</v>
+        <v>811269</v>
       </c>
       <c r="R55" t="n">
-        <v>7393053</v>
+        <v>7392821</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B56" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R56" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685855</v>
+        <v>128685844</v>
       </c>
       <c r="B57" t="n">
         <v>92881</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811502</v>
+        <v>810873</v>
       </c>
       <c r="R57" t="n">
-        <v>7393143</v>
+        <v>7392973</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685850</v>
+        <v>128685803</v>
       </c>
       <c r="B58" t="n">
-        <v>92881</v>
+        <v>92893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810978</v>
+        <v>810733</v>
       </c>
       <c r="R58" t="n">
-        <v>7392914</v>
+        <v>7393068</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685823</v>
+        <v>128685868</v>
       </c>
       <c r="B59" t="n">
-        <v>58106</v>
+        <v>92881</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811127</v>
+        <v>810757</v>
       </c>
       <c r="R59" t="n">
-        <v>7392976</v>
+        <v>7393053</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685789</v>
+        <v>128685771</v>
       </c>
       <c r="B61" t="n">
-        <v>90422</v>
+        <v>87030</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811258</v>
+        <v>811112</v>
       </c>
       <c r="R61" t="n">
-        <v>7392822</v>
+        <v>7393038</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6503,32 +6503,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685788</v>
+        <v>128685800</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>92893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811107</v>
+        <v>810861</v>
       </c>
       <c r="R62" t="n">
-        <v>7393022</v>
+        <v>7392976</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,10 +6600,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685812</v>
+        <v>128685859</v>
       </c>
       <c r="B63" t="n">
-        <v>79105</v>
+        <v>92881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6611,21 +6611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>810948</v>
+        <v>811498</v>
       </c>
       <c r="R63" t="n">
-        <v>7392987</v>
+        <v>7393147</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685752</v>
+        <v>128685812</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>79105</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811410</v>
+        <v>810948</v>
       </c>
       <c r="R64" t="n">
-        <v>7392970</v>
+        <v>7392987</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685806</v>
+        <v>128685752</v>
       </c>
       <c r="B65" t="n">
-        <v>79105</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811056</v>
+        <v>811410</v>
       </c>
       <c r="R65" t="n">
-        <v>7392881</v>
+        <v>7392970</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6891,32 +6891,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B66" t="n">
-        <v>87030</v>
+        <v>90422</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R66" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685800</v>
+        <v>128685806</v>
       </c>
       <c r="B67" t="n">
-        <v>92893</v>
+        <v>79105</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>810861</v>
+        <v>811056</v>
       </c>
       <c r="R67" t="n">
-        <v>7392976</v>
+        <v>7392881</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685859</v>
+        <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>92881</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811498</v>
+        <v>811107</v>
       </c>
       <c r="R68" t="n">
-        <v>7393147</v>
+        <v>7393022</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685838</v>
+        <v>128685872</v>
       </c>
       <c r="B69" t="n">
-        <v>82918</v>
+        <v>92875</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810781</v>
+        <v>811269</v>
       </c>
       <c r="R69" t="n">
-        <v>7392936</v>
+        <v>7392839</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,32 +7280,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685813</v>
+        <v>128685840</v>
       </c>
       <c r="B70" t="n">
-        <v>91652</v>
+        <v>92881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810934</v>
+        <v>810762</v>
       </c>
       <c r="R70" t="n">
-        <v>7393019</v>
+        <v>7393078</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685840</v>
+        <v>128685856</v>
       </c>
       <c r="B71" t="n">
         <v>92881</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810762</v>
+        <v>811494</v>
       </c>
       <c r="R71" t="n">
-        <v>7393078</v>
+        <v>7393153</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,10 +7474,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685838</v>
       </c>
       <c r="B72" t="n">
-        <v>92875</v>
+        <v>82918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7485,21 +7485,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>810781</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7392936</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685813</v>
       </c>
       <c r="B73" t="n">
-        <v>92881</v>
+        <v>91652</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>810934</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7393019</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685822</v>
+        <v>128685846</v>
       </c>
       <c r="B75" t="n">
-        <v>57840</v>
+        <v>92881</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810901</v>
+        <v>810911</v>
       </c>
       <c r="R75" t="n">
-        <v>7393040</v>
+        <v>7392927</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685864</v>
+        <v>128685848</v>
       </c>
       <c r="B76" t="n">
         <v>92881</v>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810814</v>
+        <v>810952</v>
       </c>
       <c r="R76" t="n">
-        <v>7393022</v>
+        <v>7392920</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685848</v>
+        <v>128685822</v>
       </c>
       <c r="B77" t="n">
-        <v>92881</v>
+        <v>57840</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7970,21 +7970,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810952</v>
+        <v>810901</v>
       </c>
       <c r="R77" t="n">
-        <v>7392920</v>
+        <v>7393040</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,7 +8056,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685846</v>
+        <v>128685864</v>
       </c>
       <c r="B78" t="n">
         <v>92881</v>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810911</v>
+        <v>810814</v>
       </c>
       <c r="R78" t="n">
-        <v>7392927</v>
+        <v>7393022</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685851</v>
+        <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>92881</v>
+        <v>90224</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811062</v>
+        <v>810744</v>
       </c>
       <c r="R79" t="n">
-        <v>7392883</v>
+        <v>7393058</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B80" t="n">
-        <v>90224</v>
+        <v>92881</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R80" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B83" t="n">
-        <v>92881</v>
+        <v>90224</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R83" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B84" t="n">
-        <v>90224</v>
+        <v>92881</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685860</v>
+        <v>128685749</v>
       </c>
       <c r="B86" t="n">
-        <v>92881</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811528</v>
+        <v>811061</v>
       </c>
       <c r="R86" t="n">
-        <v>7393160</v>
+        <v>7392880</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685749</v>
+        <v>128685825</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811061</v>
+        <v>810871</v>
       </c>
       <c r="R87" t="n">
-        <v>7392880</v>
+        <v>7392966</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685825</v>
+        <v>128685860</v>
       </c>
       <c r="B88" t="n">
-        <v>78838</v>
+        <v>92881</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>810871</v>
+        <v>811528</v>
       </c>
       <c r="R88" t="n">
-        <v>7392966</v>
+        <v>7393160</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9220,32 +9220,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685852</v>
+        <v>128685763</v>
       </c>
       <c r="B90" t="n">
-        <v>92881</v>
+        <v>87030</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811057</v>
+        <v>811097</v>
       </c>
       <c r="R90" t="n">
-        <v>7392877</v>
+        <v>7392723</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,6 +9299,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9317,10 +9318,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685801</v>
+        <v>128685852</v>
       </c>
       <c r="B91" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9328,21 +9329,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9353,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811116</v>
+        <v>811057</v>
       </c>
       <c r="R91" t="n">
-        <v>7392980</v>
+        <v>7392877</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9414,32 +9415,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B92" t="n">
-        <v>87030</v>
+        <v>92893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9449,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R92" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9493,7 +9494,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9809,7 +9809,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685849</v>
+        <v>128685863</v>
       </c>
       <c r="B96" t="n">
         <v>92881</v>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810964</v>
+        <v>810854</v>
       </c>
       <c r="R96" t="n">
-        <v>7392920</v>
+        <v>7393015</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685863</v>
+        <v>128685849</v>
       </c>
       <c r="B97" t="n">
         <v>92881</v>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810854</v>
+        <v>810964</v>
       </c>
       <c r="R97" t="n">
-        <v>7393015</v>
+        <v>7392920</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685837</v>
+        <v>128685843</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810756</v>
+        <v>810858</v>
       </c>
       <c r="R2" t="n">
-        <v>7393036</v>
+        <v>7392973</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685756</v>
+        <v>128685836</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811013</v>
+        <v>811057</v>
       </c>
       <c r="R3" t="n">
-        <v>7393006</v>
+        <v>7393046</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685836</v>
+        <v>128685790</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811057</v>
+        <v>810977</v>
       </c>
       <c r="R4" t="n">
-        <v>7393046</v>
+        <v>7393016</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685790</v>
+        <v>128685783</v>
       </c>
       <c r="B5" t="n">
-        <v>56926</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810977</v>
+        <v>811497</v>
       </c>
       <c r="R5" t="n">
-        <v>7393016</v>
+        <v>7393112</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685783</v>
+        <v>128685837</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811497</v>
+        <v>810756</v>
       </c>
       <c r="R6" t="n">
-        <v>7393112</v>
+        <v>7393036</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685843</v>
+        <v>128685756</v>
       </c>
       <c r="B7" t="n">
-        <v>92881</v>
+        <v>79700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810858</v>
+        <v>811013</v>
       </c>
       <c r="R7" t="n">
-        <v>7392973</v>
+        <v>7393006</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685773</v>
+        <v>128685760</v>
       </c>
       <c r="B17" t="n">
-        <v>87030</v>
+        <v>79671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3690</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811089</v>
+        <v>810920</v>
       </c>
       <c r="R17" t="n">
-        <v>7393040</v>
+        <v>7393003</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685829</v>
+        <v>128685773</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>87030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2312,6 +2311,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685826</v>
+        <v>128685829</v>
       </c>
       <c r="B19" t="n">
         <v>78838</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R19" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685753</v>
+        <v>128685826</v>
       </c>
       <c r="B20" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811087</v>
+        <v>811021</v>
       </c>
       <c r="R20" t="n">
-        <v>7393042</v>
+        <v>7392844</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685753</v>
       </c>
       <c r="B21" t="n">
-        <v>79671</v>
+        <v>79700</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R21" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685854</v>
+        <v>128685778</v>
       </c>
       <c r="B23" t="n">
-        <v>92881</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811441</v>
+        <v>811517</v>
       </c>
       <c r="R23" t="n">
-        <v>7393097</v>
+        <v>7393148</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685802</v>
+        <v>128685854</v>
       </c>
       <c r="B24" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811027</v>
+        <v>811441</v>
       </c>
       <c r="R24" t="n">
-        <v>7393042</v>
+        <v>7393097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685869</v>
+        <v>128685802</v>
       </c>
       <c r="B25" t="n">
-        <v>92881</v>
+        <v>92893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810738</v>
+        <v>811027</v>
       </c>
       <c r="R25" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685831</v>
+        <v>128685869</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>92881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810853</v>
+        <v>810738</v>
       </c>
       <c r="R26" t="n">
-        <v>7393047</v>
+        <v>7393051</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685778</v>
+        <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811517</v>
+        <v>810853</v>
       </c>
       <c r="R27" t="n">
-        <v>7393148</v>
+        <v>7393047</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685823</v>
+        <v>128685868</v>
       </c>
       <c r="B52" t="n">
-        <v>58106</v>
+        <v>92881</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811127</v>
+        <v>810757</v>
       </c>
       <c r="R52" t="n">
-        <v>7392976</v>
+        <v>7393053</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,32 +5629,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685767</v>
+        <v>128685823</v>
       </c>
       <c r="B53" t="n">
-        <v>87030</v>
+        <v>58106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3690</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811516</v>
+        <v>811127</v>
       </c>
       <c r="R53" t="n">
-        <v>7393158</v>
+        <v>7392976</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685850</v>
+        <v>128685767</v>
       </c>
       <c r="B54" t="n">
-        <v>92881</v>
+        <v>87030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810978</v>
+        <v>811516</v>
       </c>
       <c r="R54" t="n">
-        <v>7392914</v>
+        <v>7393158</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685876</v>
+        <v>128685850</v>
       </c>
       <c r="B55" t="n">
-        <v>92875</v>
+        <v>92881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811269</v>
+        <v>810978</v>
       </c>
       <c r="R55" t="n">
-        <v>7392821</v>
+        <v>7392914</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685855</v>
+        <v>128685876</v>
       </c>
       <c r="B56" t="n">
-        <v>92881</v>
+        <v>92875</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811502</v>
+        <v>811269</v>
       </c>
       <c r="R56" t="n">
-        <v>7393143</v>
+        <v>7392821</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685844</v>
+        <v>128685855</v>
       </c>
       <c r="B57" t="n">
         <v>92881</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810873</v>
+        <v>811502</v>
       </c>
       <c r="R57" t="n">
-        <v>7392973</v>
+        <v>7393143</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685803</v>
+        <v>128685844</v>
       </c>
       <c r="B58" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6125,21 +6125,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810733</v>
+        <v>810873</v>
       </c>
       <c r="R58" t="n">
-        <v>7393068</v>
+        <v>7392973</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685868</v>
+        <v>128685803</v>
       </c>
       <c r="B59" t="n">
-        <v>92881</v>
+        <v>92893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810757</v>
+        <v>810733</v>
       </c>
       <c r="R59" t="n">
-        <v>7393053</v>
+        <v>7393068</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7280,32 +7280,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685840</v>
+        <v>128685838</v>
       </c>
       <c r="B70" t="n">
-        <v>92881</v>
+        <v>82918</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810762</v>
+        <v>810781</v>
       </c>
       <c r="R70" t="n">
-        <v>7393078</v>
+        <v>7392936</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685856</v>
+        <v>128685813</v>
       </c>
       <c r="B71" t="n">
-        <v>92881</v>
+        <v>91652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811494</v>
+        <v>810934</v>
       </c>
       <c r="R71" t="n">
-        <v>7393153</v>
+        <v>7393019</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685838</v>
+        <v>128685840</v>
       </c>
       <c r="B72" t="n">
-        <v>82918</v>
+        <v>92881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810781</v>
+        <v>810762</v>
       </c>
       <c r="R72" t="n">
-        <v>7392936</v>
+        <v>7393078</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685813</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>91652</v>
+        <v>92881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>810934</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7393019</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>92881</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R86" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R87" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>92881</v>
+        <v>78838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R88" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685764</v>
+        <v>128685796</v>
       </c>
       <c r="B89" t="n">
-        <v>87030</v>
+        <v>92912</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
+        <v>232140</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810867</v>
+        <v>810795</v>
       </c>
       <c r="R89" t="n">
-        <v>7392967</v>
+        <v>7393042</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685763</v>
+        <v>128685764</v>
       </c>
       <c r="B90" t="n">
         <v>87030</v>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811097</v>
+        <v>810867</v>
       </c>
       <c r="R90" t="n">
-        <v>7392723</v>
+        <v>7392967</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,7 +9299,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9318,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685852</v>
+        <v>128685763</v>
       </c>
       <c r="B91" t="n">
-        <v>92881</v>
+        <v>87030</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9353,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811057</v>
+        <v>811097</v>
       </c>
       <c r="R91" t="n">
-        <v>7392877</v>
+        <v>7392723</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9397,6 +9396,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685801</v>
+        <v>128685852</v>
       </c>
       <c r="B92" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9426,21 +9426,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811116</v>
+        <v>811057</v>
       </c>
       <c r="R92" t="n">
-        <v>7392980</v>
+        <v>7392877</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9512,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685796</v>
+        <v>128685801</v>
       </c>
       <c r="B93" t="n">
-        <v>92912</v>
+        <v>92893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232140</v>
+        <v>4366</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>810795</v>
+        <v>811116</v>
       </c>
       <c r="R93" t="n">
-        <v>7393042</v>
+        <v>7392980</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685751</v>
+        <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>87030</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811254</v>
+        <v>811050</v>
       </c>
       <c r="R94" t="n">
-        <v>7392831</v>
+        <v>7393050</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,12 +9682,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9706,10 +9712,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685770</v>
+        <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>87030</v>
+        <v>79700</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9717,21 +9723,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9741,10 +9747,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811050</v>
+        <v>811254</v>
       </c>
       <c r="R95" t="n">
-        <v>7393050</v>
+        <v>7392831</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9779,18 +9785,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -9809,7 +9809,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685863</v>
+        <v>128685849</v>
       </c>
       <c r="B96" t="n">
         <v>92881</v>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810854</v>
+        <v>810964</v>
       </c>
       <c r="R96" t="n">
-        <v>7393015</v>
+        <v>7392920</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,32 +9906,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685849</v>
+        <v>128685834</v>
       </c>
       <c r="B97" t="n">
-        <v>92881</v>
+        <v>79081</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810964</v>
+        <v>811525</v>
       </c>
       <c r="R97" t="n">
-        <v>7392920</v>
+        <v>7393139</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10003,32 +10003,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128685834</v>
+        <v>128685863</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>92881</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811525</v>
+        <v>810854</v>
       </c>
       <c r="R98" t="n">
-        <v>7393139</v>
+        <v>7393015</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685778</v>
+        <v>128685854</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>92881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811517</v>
+        <v>811441</v>
       </c>
       <c r="R23" t="n">
-        <v>7393148</v>
+        <v>7393097</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685854</v>
+        <v>128685802</v>
       </c>
       <c r="B24" t="n">
-        <v>92881</v>
+        <v>92893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811441</v>
+        <v>811027</v>
       </c>
       <c r="R24" t="n">
-        <v>7393097</v>
+        <v>7393042</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685802</v>
+        <v>128685869</v>
       </c>
       <c r="B25" t="n">
-        <v>92893</v>
+        <v>92881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811027</v>
+        <v>810738</v>
       </c>
       <c r="R25" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685869</v>
+        <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>92881</v>
+        <v>78838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810738</v>
+        <v>810853</v>
       </c>
       <c r="R26" t="n">
-        <v>7393051</v>
+        <v>7393047</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>811517</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7393148</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685793</v>
+        <v>128685777</v>
       </c>
       <c r="B47" t="n">
-        <v>92906</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810740</v>
+        <v>811015</v>
       </c>
       <c r="R47" t="n">
-        <v>7393062</v>
+        <v>7392800</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B48" t="n">
         <v>92906</v>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R48" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685875</v>
+        <v>128685792</v>
       </c>
       <c r="B49" t="n">
-        <v>92875</v>
+        <v>92906</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811283</v>
+        <v>811023</v>
       </c>
       <c r="R49" t="n">
-        <v>7392844</v>
+        <v>7392776</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685809</v>
+        <v>128685875</v>
       </c>
       <c r="B50" t="n">
-        <v>79105</v>
+        <v>92875</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811105</v>
+        <v>811283</v>
       </c>
       <c r="R50" t="n">
-        <v>7393054</v>
+        <v>7392844</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685777</v>
+        <v>128685809</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>79105</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811015</v>
+        <v>811105</v>
       </c>
       <c r="R51" t="n">
-        <v>7392800</v>
+        <v>7393054</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7280,32 +7280,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685838</v>
+        <v>128685840</v>
       </c>
       <c r="B70" t="n">
-        <v>82918</v>
+        <v>92881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810781</v>
+        <v>810762</v>
       </c>
       <c r="R70" t="n">
-        <v>7392936</v>
+        <v>7393078</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685813</v>
+        <v>128685856</v>
       </c>
       <c r="B71" t="n">
-        <v>91652</v>
+        <v>92881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810934</v>
+        <v>811494</v>
       </c>
       <c r="R71" t="n">
-        <v>7393019</v>
+        <v>7393153</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685840</v>
+        <v>128685838</v>
       </c>
       <c r="B72" t="n">
-        <v>92881</v>
+        <v>82918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810762</v>
+        <v>810781</v>
       </c>
       <c r="R72" t="n">
-        <v>7393078</v>
+        <v>7392936</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685813</v>
       </c>
       <c r="B73" t="n">
-        <v>92881</v>
+        <v>91652</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>810934</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7393019</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685770</v>
+        <v>128685751</v>
       </c>
       <c r="B94" t="n">
-        <v>87030</v>
+        <v>79700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811050</v>
+        <v>811254</v>
       </c>
       <c r="R94" t="n">
-        <v>7393050</v>
+        <v>7392831</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,18 +9682,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9712,10 +9706,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685751</v>
+        <v>128685770</v>
       </c>
       <c r="B95" t="n">
-        <v>79700</v>
+        <v>87030</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9723,21 +9717,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9747,10 +9741,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811254</v>
+        <v>811050</v>
       </c>
       <c r="R95" t="n">
-        <v>7392831</v>
+        <v>7393050</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9785,12 +9779,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685843</v>
+        <v>128685837</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810858</v>
+        <v>810756</v>
       </c>
       <c r="R2" t="n">
-        <v>7392973</v>
+        <v>7393036</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
         <v>128685836</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685790</v>
+        <v>128685783</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810977</v>
+        <v>811497</v>
       </c>
       <c r="R4" t="n">
-        <v>7393016</v>
+        <v>7393112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685783</v>
+        <v>128685790</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>56927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811497</v>
+        <v>810977</v>
       </c>
       <c r="R5" t="n">
-        <v>7393112</v>
+        <v>7393016</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685837</v>
+        <v>128685843</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>92884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810756</v>
+        <v>810858</v>
       </c>
       <c r="R6" t="n">
-        <v>7393036</v>
+        <v>7392973</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,7 +1168,7 @@
         <v>128685756</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685835</v>
+        <v>128685853</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>92884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811420</v>
+        <v>811044</v>
       </c>
       <c r="R8" t="n">
-        <v>7392954</v>
+        <v>7392879</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1362,7 +1362,7 @@
         <v>128685804</v>
       </c>
       <c r="B9" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685853</v>
+        <v>128685835</v>
       </c>
       <c r="B10" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811044</v>
+        <v>811420</v>
       </c>
       <c r="R10" t="n">
-        <v>7392879</v>
+        <v>7392954</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1556,7 +1556,7 @@
         <v>128685866</v>
       </c>
       <c r="B11" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>128685769</v>
       </c>
       <c r="B12" t="n">
-        <v>87030</v>
+        <v>87033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128685874</v>
       </c>
       <c r="B13" t="n">
-        <v>92875</v>
+        <v>92878</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685795</v>
+        <v>128685810</v>
       </c>
       <c r="B14" t="n">
-        <v>92526</v>
+        <v>79108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810915</v>
+        <v>811027</v>
       </c>
       <c r="R14" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685810</v>
+        <v>128685795</v>
       </c>
       <c r="B15" t="n">
-        <v>79105</v>
+        <v>92529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811027</v>
+        <v>810915</v>
       </c>
       <c r="R15" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87030</v>
+        <v>87033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685760</v>
+        <v>128685773</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>87033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R17" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685773</v>
+        <v>128685753</v>
       </c>
       <c r="B18" t="n">
-        <v>87030</v>
+        <v>79703</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811089</v>
+        <v>811087</v>
       </c>
       <c r="R18" t="n">
-        <v>7393040</v>
+        <v>7393042</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2311,7 +2312,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>128685829</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>128685826</v>
       </c>
       <c r="B20" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685753</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>79700</v>
+        <v>79674</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R21" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685873</v>
+        <v>128685869</v>
       </c>
       <c r="B22" t="n">
-        <v>92875</v>
+        <v>92884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811303</v>
+        <v>810738</v>
       </c>
       <c r="R22" t="n">
-        <v>7392893</v>
+        <v>7393051</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2721,7 +2721,7 @@
         <v>128685854</v>
       </c>
       <c r="B23" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685802</v>
+        <v>128685873</v>
       </c>
       <c r="B24" t="n">
-        <v>92893</v>
+        <v>92878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811027</v>
+        <v>811303</v>
       </c>
       <c r="R24" t="n">
-        <v>7393042</v>
+        <v>7392893</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685869</v>
+        <v>128685802</v>
       </c>
       <c r="B25" t="n">
-        <v>92881</v>
+        <v>92896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>810738</v>
+        <v>811027</v>
       </c>
       <c r="R25" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3012,7 +3012,7 @@
         <v>128685831</v>
       </c>
       <c r="B26" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>128685778</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685799</v>
+        <v>128685861</v>
       </c>
       <c r="B29" t="n">
-        <v>92893</v>
+        <v>92884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810790</v>
+        <v>810965</v>
       </c>
       <c r="R29" t="n">
-        <v>7392931</v>
+        <v>7393009</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685861</v>
+        <v>128685808</v>
       </c>
       <c r="B30" t="n">
-        <v>92881</v>
+        <v>79108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810965</v>
+        <v>811520</v>
       </c>
       <c r="R30" t="n">
-        <v>7393009</v>
+        <v>7393156</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685808</v>
+        <v>128685839</v>
       </c>
       <c r="B31" t="n">
-        <v>79105</v>
+        <v>78750</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811520</v>
+        <v>811034</v>
       </c>
       <c r="R31" t="n">
-        <v>7393156</v>
+        <v>7393002</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685758</v>
+        <v>128685799</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>92896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810717</v>
+        <v>810790</v>
       </c>
       <c r="R32" t="n">
-        <v>7393072</v>
+        <v>7392931</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685776</v>
+        <v>128685758</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>79703</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810803</v>
+        <v>810717</v>
       </c>
       <c r="R33" t="n">
-        <v>7392998</v>
+        <v>7393072</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685839</v>
+        <v>128685785</v>
       </c>
       <c r="B34" t="n">
-        <v>78747</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811034</v>
+        <v>811518</v>
       </c>
       <c r="R34" t="n">
-        <v>7393002</v>
+        <v>7393070</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685785</v>
+        <v>128685776</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811518</v>
+        <v>810803</v>
       </c>
       <c r="R35" t="n">
-        <v>7393070</v>
+        <v>7392998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
         <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4173,32 +4173,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685833</v>
+        <v>128685807</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79108</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811464</v>
+        <v>811004</v>
       </c>
       <c r="R38" t="n">
-        <v>7393013</v>
+        <v>7392787</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,32 +4270,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685807</v>
+        <v>128685833</v>
       </c>
       <c r="B39" t="n">
-        <v>79105</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811004</v>
+        <v>811464</v>
       </c>
       <c r="R39" t="n">
-        <v>7392787</v>
+        <v>7393013</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4370,7 +4370,7 @@
         <v>128685805</v>
       </c>
       <c r="B40" t="n">
-        <v>79105</v>
+        <v>79108</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4464,32 +4464,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685798</v>
+        <v>128685814</v>
       </c>
       <c r="B41" t="n">
-        <v>92893</v>
+        <v>78842</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810767</v>
+        <v>810773</v>
       </c>
       <c r="R41" t="n">
-        <v>7393075</v>
+        <v>7392966</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685828</v>
+        <v>128685798</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>92896</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811225</v>
+        <v>810767</v>
       </c>
       <c r="R42" t="n">
-        <v>7392837</v>
+        <v>7393075</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685877</v>
+        <v>128685818</v>
       </c>
       <c r="B43" t="n">
-        <v>92875</v>
+        <v>90227</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811258</v>
+        <v>811120</v>
       </c>
       <c r="R43" t="n">
-        <v>7392822</v>
+        <v>7392983</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,10 +4755,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685761</v>
+        <v>128685828</v>
       </c>
       <c r="B44" t="n">
-        <v>87030</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4766,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3690</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811014</v>
+        <v>811225</v>
       </c>
       <c r="R44" t="n">
-        <v>7392891</v>
+        <v>7392837</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4834,7 +4834,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4853,10 +4852,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685818</v>
+        <v>128685877</v>
       </c>
       <c r="B45" t="n">
-        <v>90224</v>
+        <v>92878</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4863,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4962</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4887,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811120</v>
+        <v>811258</v>
       </c>
       <c r="R45" t="n">
-        <v>7392983</v>
+        <v>7392822</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4950,10 +4949,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685814</v>
+        <v>128685761</v>
       </c>
       <c r="B46" t="n">
-        <v>78839</v>
+        <v>87033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4960,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>3690</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4984,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810773</v>
+        <v>811014</v>
       </c>
       <c r="R46" t="n">
-        <v>7392966</v>
+        <v>7392891</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5029,6 +5028,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5047,10 +5047,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685777</v>
+        <v>128685875</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>92878</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811015</v>
+        <v>811283</v>
       </c>
       <c r="R47" t="n">
-        <v>7392800</v>
+        <v>7392844</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B48" t="n">
-        <v>92906</v>
+        <v>92909</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R48" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685792</v>
+        <v>128685793</v>
       </c>
       <c r="B49" t="n">
-        <v>92906</v>
+        <v>92909</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811023</v>
+        <v>810740</v>
       </c>
       <c r="R49" t="n">
-        <v>7392776</v>
+        <v>7393062</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685875</v>
+        <v>128685809</v>
       </c>
       <c r="B50" t="n">
-        <v>92875</v>
+        <v>79108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811283</v>
+        <v>811105</v>
       </c>
       <c r="R50" t="n">
-        <v>7392844</v>
+        <v>7393054</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,32 +5435,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685809</v>
+        <v>128685777</v>
       </c>
       <c r="B51" t="n">
-        <v>79105</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811105</v>
+        <v>811015</v>
       </c>
       <c r="R51" t="n">
-        <v>7393054</v>
+        <v>7392800</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685868</v>
+        <v>128685844</v>
       </c>
       <c r="B52" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810757</v>
+        <v>810873</v>
       </c>
       <c r="R52" t="n">
-        <v>7393053</v>
+        <v>7392973</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,10 +5629,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685823</v>
+        <v>128685803</v>
       </c>
       <c r="B53" t="n">
-        <v>58106</v>
+        <v>92896</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5640,21 +5640,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811127</v>
+        <v>810733</v>
       </c>
       <c r="R53" t="n">
-        <v>7392976</v>
+        <v>7393068</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5729,7 +5729,7 @@
         <v>128685767</v>
       </c>
       <c r="B54" t="n">
-        <v>87030</v>
+        <v>87033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>128685850</v>
       </c>
       <c r="B55" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>128685876</v>
       </c>
       <c r="B56" t="n">
-        <v>92875</v>
+        <v>92878</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>128685855</v>
       </c>
       <c r="B57" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,10 +6114,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685844</v>
+        <v>128685868</v>
       </c>
       <c r="B58" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810873</v>
+        <v>810757</v>
       </c>
       <c r="R58" t="n">
-        <v>7392973</v>
+        <v>7393053</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6211,10 +6211,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685803</v>
+        <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>92893</v>
+        <v>58108</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6222,21 +6222,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6246,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810733</v>
+        <v>811127</v>
       </c>
       <c r="R59" t="n">
-        <v>7393068</v>
+        <v>7392976</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6311,7 +6311,7 @@
         <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B61" t="n">
-        <v>87030</v>
+        <v>90425</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R61" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685800</v>
+        <v>128685812</v>
       </c>
       <c r="B62" t="n">
-        <v>92893</v>
+        <v>79108</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810861</v>
+        <v>810948</v>
       </c>
       <c r="R62" t="n">
-        <v>7392976</v>
+        <v>7392987</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685859</v>
+        <v>128685752</v>
       </c>
       <c r="B63" t="n">
-        <v>92881</v>
+        <v>79703</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811498</v>
+        <v>811410</v>
       </c>
       <c r="R63" t="n">
-        <v>7393147</v>
+        <v>7392970</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,10 +6697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685812</v>
+        <v>128685806</v>
       </c>
       <c r="B64" t="n">
-        <v>79105</v>
+        <v>79108</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>810948</v>
+        <v>811056</v>
       </c>
       <c r="R64" t="n">
-        <v>7392987</v>
+        <v>7392881</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685752</v>
+        <v>128685771</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>87033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6805,21 +6805,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811410</v>
+        <v>811112</v>
       </c>
       <c r="R65" t="n">
-        <v>7392970</v>
+        <v>7393038</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6873,6 +6873,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6891,32 +6892,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685789</v>
+        <v>128685859</v>
       </c>
       <c r="B66" t="n">
-        <v>90422</v>
+        <v>92884</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6926,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811258</v>
+        <v>811498</v>
       </c>
       <c r="R66" t="n">
-        <v>7392822</v>
+        <v>7393147</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6970,7 +6971,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685806</v>
+        <v>128685800</v>
       </c>
       <c r="B67" t="n">
-        <v>79105</v>
+        <v>92896</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7000,21 +7000,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811056</v>
+        <v>810861</v>
       </c>
       <c r="R67" t="n">
-        <v>7392881</v>
+        <v>7392976</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7089,7 +7089,7 @@
         <v>128685788</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7183,10 +7183,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685872</v>
+        <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>92875</v>
+        <v>82921</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7194,21 +7194,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811269</v>
+        <v>810781</v>
       </c>
       <c r="R69" t="n">
-        <v>7392839</v>
+        <v>7392936</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,32 +7280,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685840</v>
+        <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>92881</v>
+        <v>91655</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810762</v>
+        <v>810934</v>
       </c>
       <c r="R70" t="n">
-        <v>7393078</v>
+        <v>7393019</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B71" t="n">
-        <v>92881</v>
+        <v>79703</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R71" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685838</v>
+        <v>128685840</v>
       </c>
       <c r="B72" t="n">
-        <v>82918</v>
+        <v>92884</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810781</v>
+        <v>810762</v>
       </c>
       <c r="R72" t="n">
-        <v>7392936</v>
+        <v>7393078</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,10 +7571,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685813</v>
+        <v>128685872</v>
       </c>
       <c r="B73" t="n">
-        <v>91652</v>
+        <v>92878</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7582,21 +7582,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>810934</v>
+        <v>811269</v>
       </c>
       <c r="R73" t="n">
-        <v>7393019</v>
+        <v>7392839</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685856</v>
       </c>
       <c r="B74" t="n">
-        <v>79700</v>
+        <v>92884</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>811494</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7393153</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685846</v>
+        <v>128685822</v>
       </c>
       <c r="B75" t="n">
-        <v>92881</v>
+        <v>57841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810911</v>
+        <v>810901</v>
       </c>
       <c r="R75" t="n">
-        <v>7392927</v>
+        <v>7393040</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7865,7 +7865,7 @@
         <v>128685848</v>
       </c>
       <c r="B76" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685822</v>
+        <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>57840</v>
+        <v>92884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7970,21 +7970,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810901</v>
+        <v>810911</v>
       </c>
       <c r="R77" t="n">
-        <v>7393040</v>
+        <v>7392927</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8059,7 +8059,7 @@
         <v>128685864</v>
       </c>
       <c r="B78" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B79" t="n">
-        <v>90224</v>
+        <v>92884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R79" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,32 +8250,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685851</v>
+        <v>128685819</v>
       </c>
       <c r="B80" t="n">
-        <v>92881</v>
+        <v>90227</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811062</v>
+        <v>810744</v>
       </c>
       <c r="R80" t="n">
-        <v>7392883</v>
+        <v>7393058</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8350,7 +8350,7 @@
         <v>128685780</v>
       </c>
       <c r="B81" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>128685781</v>
       </c>
       <c r="B82" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B83" t="n">
-        <v>90224</v>
+        <v>92884</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R83" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B84" t="n">
-        <v>92881</v>
+        <v>90227</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R84" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8738,7 +8738,7 @@
         <v>128685748</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685860</v>
+        <v>128685749</v>
       </c>
       <c r="B86" t="n">
-        <v>92881</v>
+        <v>79703</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811528</v>
+        <v>811061</v>
       </c>
       <c r="R86" t="n">
-        <v>7393160</v>
+        <v>7392880</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685749</v>
+        <v>128685825</v>
       </c>
       <c r="B87" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811061</v>
+        <v>810871</v>
       </c>
       <c r="R87" t="n">
-        <v>7392880</v>
+        <v>7392966</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685825</v>
+        <v>128685860</v>
       </c>
       <c r="B88" t="n">
-        <v>78838</v>
+        <v>92884</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>810871</v>
+        <v>811528</v>
       </c>
       <c r="R88" t="n">
-        <v>7392966</v>
+        <v>7393160</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685796</v>
+        <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>92912</v>
+        <v>87033</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>232140</v>
+        <v>3690</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810795</v>
+        <v>810867</v>
       </c>
       <c r="R89" t="n">
-        <v>7393042</v>
+        <v>7392967</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685764</v>
+        <v>128685763</v>
       </c>
       <c r="B90" t="n">
-        <v>87030</v>
+        <v>87033</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>810867</v>
+        <v>811097</v>
       </c>
       <c r="R90" t="n">
-        <v>7392967</v>
+        <v>7392723</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,6 +9299,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9317,32 +9318,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685763</v>
+        <v>128685852</v>
       </c>
       <c r="B91" t="n">
-        <v>87030</v>
+        <v>92884</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9353,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811097</v>
+        <v>811057</v>
       </c>
       <c r="R91" t="n">
-        <v>7392723</v>
+        <v>7392877</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,7 +9397,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685852</v>
+        <v>128685801</v>
       </c>
       <c r="B92" t="n">
-        <v>92881</v>
+        <v>92896</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9426,21 +9426,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811057</v>
+        <v>811116</v>
       </c>
       <c r="R92" t="n">
-        <v>7392877</v>
+        <v>7392980</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9512,32 +9512,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685801</v>
+        <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92893</v>
+        <v>92915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4366</v>
+        <v>232140</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811116</v>
+        <v>810795</v>
       </c>
       <c r="R93" t="n">
-        <v>7392980</v>
+        <v>7393042</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9612,7 +9612,7 @@
         <v>128685751</v>
       </c>
       <c r="B94" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>128685770</v>
       </c>
       <c r="B95" t="n">
-        <v>87030</v>
+        <v>87033</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9906,32 +9906,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685834</v>
+        <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>92884</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811525</v>
+        <v>810854</v>
       </c>
       <c r="R97" t="n">
-        <v>7393139</v>
+        <v>7393015</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10003,32 +10003,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128685863</v>
+        <v>128685834</v>
       </c>
       <c r="B98" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>810854</v>
+        <v>811525</v>
       </c>
       <c r="R98" t="n">
-        <v>7393015</v>
+        <v>7393139</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685837</v>
+        <v>128685756</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810756</v>
+        <v>811013</v>
       </c>
       <c r="R2" t="n">
-        <v>7393036</v>
+        <v>7393006</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685836</v>
+        <v>128685843</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>92884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811057</v>
+        <v>810858</v>
       </c>
       <c r="R3" t="n">
-        <v>7393046</v>
+        <v>7392973</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685783</v>
+        <v>128685837</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811497</v>
+        <v>810756</v>
       </c>
       <c r="R4" t="n">
-        <v>7393112</v>
+        <v>7393036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685790</v>
+        <v>128685836</v>
       </c>
       <c r="B5" t="n">
-        <v>56927</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810977</v>
+        <v>811057</v>
       </c>
       <c r="R5" t="n">
-        <v>7393016</v>
+        <v>7393046</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685843</v>
+        <v>128685783</v>
       </c>
       <c r="B6" t="n">
-        <v>92884</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810858</v>
+        <v>811497</v>
       </c>
       <c r="R6" t="n">
-        <v>7392973</v>
+        <v>7393112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685756</v>
+        <v>128685790</v>
       </c>
       <c r="B7" t="n">
-        <v>79703</v>
+        <v>56927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811013</v>
+        <v>810977</v>
       </c>
       <c r="R7" t="n">
-        <v>7393006</v>
+        <v>7393016</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685810</v>
+        <v>128685795</v>
       </c>
       <c r="B14" t="n">
-        <v>79108</v>
+        <v>92529</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811027</v>
+        <v>810915</v>
       </c>
       <c r="R14" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685795</v>
+        <v>128685810</v>
       </c>
       <c r="B15" t="n">
-        <v>92529</v>
+        <v>79108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810915</v>
+        <v>811027</v>
       </c>
       <c r="R15" t="n">
-        <v>7393042</v>
+        <v>7393051</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685753</v>
+        <v>128685760</v>
       </c>
       <c r="B18" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811087</v>
+        <v>810920</v>
       </c>
       <c r="R18" t="n">
-        <v>7393042</v>
+        <v>7393003</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685829</v>
+        <v>128685753</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>810920</v>
+        <v>811087</v>
       </c>
       <c r="R19" t="n">
-        <v>7393003</v>
+        <v>7393042</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685826</v>
+        <v>128685829</v>
       </c>
       <c r="B20" t="n">
         <v>78841</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R20" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685826</v>
       </c>
       <c r="B21" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810920</v>
+        <v>811021</v>
       </c>
       <c r="R21" t="n">
-        <v>7393003</v>
+        <v>7392844</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685869</v>
+        <v>128685816</v>
       </c>
       <c r="B22" t="n">
-        <v>92884</v>
+        <v>78842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810738</v>
+        <v>810920</v>
       </c>
       <c r="R22" t="n">
-        <v>7393051</v>
+        <v>7393003</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,7 +2718,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685854</v>
+        <v>128685869</v>
       </c>
       <c r="B23" t="n">
         <v>92884</v>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811441</v>
+        <v>810738</v>
       </c>
       <c r="R23" t="n">
-        <v>7393097</v>
+        <v>7393051</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685873</v>
+        <v>128685854</v>
       </c>
       <c r="B24" t="n">
-        <v>92878</v>
+        <v>92884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811303</v>
+        <v>811441</v>
       </c>
       <c r="R24" t="n">
-        <v>7392893</v>
+        <v>7393097</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,32 +2912,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685802</v>
+        <v>128685873</v>
       </c>
       <c r="B25" t="n">
-        <v>92896</v>
+        <v>92878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811027</v>
+        <v>811303</v>
       </c>
       <c r="R25" t="n">
-        <v>7393042</v>
+        <v>7392893</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685831</v>
+        <v>128685802</v>
       </c>
       <c r="B26" t="n">
-        <v>78841</v>
+        <v>92896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810853</v>
+        <v>811027</v>
       </c>
       <c r="R26" t="n">
-        <v>7393047</v>
+        <v>7393042</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685778</v>
+        <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811517</v>
+        <v>810853</v>
       </c>
       <c r="R27" t="n">
-        <v>7393148</v>
+        <v>7393047</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685816</v>
+        <v>128685778</v>
       </c>
       <c r="B28" t="n">
-        <v>78842</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810920</v>
+        <v>811517</v>
       </c>
       <c r="R28" t="n">
-        <v>7393003</v>
+        <v>7393148</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685861</v>
+        <v>128685839</v>
       </c>
       <c r="B29" t="n">
-        <v>92884</v>
+        <v>78750</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810965</v>
+        <v>811034</v>
       </c>
       <c r="R29" t="n">
-        <v>7393009</v>
+        <v>7393002</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685808</v>
+        <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>79108</v>
+        <v>92896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811520</v>
+        <v>810790</v>
       </c>
       <c r="R30" t="n">
-        <v>7393156</v>
+        <v>7392931</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685839</v>
+        <v>128685758</v>
       </c>
       <c r="B31" t="n">
-        <v>78750</v>
+        <v>79703</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811034</v>
+        <v>810717</v>
       </c>
       <c r="R31" t="n">
-        <v>7393002</v>
+        <v>7393072</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685799</v>
+        <v>128685785</v>
       </c>
       <c r="B32" t="n">
-        <v>92896</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810790</v>
+        <v>811518</v>
       </c>
       <c r="R32" t="n">
-        <v>7392931</v>
+        <v>7393070</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685758</v>
+        <v>128685776</v>
       </c>
       <c r="B33" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810717</v>
+        <v>810803</v>
       </c>
       <c r="R33" t="n">
-        <v>7393072</v>
+        <v>7392998</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3785,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685785</v>
+        <v>128685861</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>92884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811518</v>
+        <v>810965</v>
       </c>
       <c r="R34" t="n">
-        <v>7393070</v>
+        <v>7393009</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685776</v>
+        <v>128685808</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>79108</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810803</v>
+        <v>811520</v>
       </c>
       <c r="R35" t="n">
-        <v>7392998</v>
+        <v>7393156</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5823,32 +5823,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685850</v>
+        <v>128685876</v>
       </c>
       <c r="B55" t="n">
-        <v>92884</v>
+        <v>92878</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>810978</v>
+        <v>811269</v>
       </c>
       <c r="R55" t="n">
-        <v>7392914</v>
+        <v>7392821</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5920,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685876</v>
+        <v>128685855</v>
       </c>
       <c r="B56" t="n">
-        <v>92878</v>
+        <v>92884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5955,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811269</v>
+        <v>811502</v>
       </c>
       <c r="R56" t="n">
-        <v>7392821</v>
+        <v>7393143</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685855</v>
+        <v>128685868</v>
       </c>
       <c r="B57" t="n">
         <v>92884</v>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811502</v>
+        <v>810757</v>
       </c>
       <c r="R57" t="n">
-        <v>7393143</v>
+        <v>7393053</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685868</v>
+        <v>128685850</v>
       </c>
       <c r="B58" t="n">
         <v>92884</v>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810757</v>
+        <v>810978</v>
       </c>
       <c r="R58" t="n">
-        <v>7393053</v>
+        <v>7392914</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685822</v>
+        <v>128685848</v>
       </c>
       <c r="B75" t="n">
-        <v>57841</v>
+        <v>92884</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810901</v>
+        <v>810952</v>
       </c>
       <c r="R75" t="n">
-        <v>7393040</v>
+        <v>7392920</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,7 +7862,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685848</v>
+        <v>128685846</v>
       </c>
       <c r="B76" t="n">
         <v>92884</v>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810952</v>
+        <v>810911</v>
       </c>
       <c r="R76" t="n">
-        <v>7392920</v>
+        <v>7392927</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685846</v>
+        <v>128685864</v>
       </c>
       <c r="B77" t="n">
         <v>92884</v>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810911</v>
+        <v>810814</v>
       </c>
       <c r="R77" t="n">
-        <v>7392927</v>
+        <v>7393022</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685864</v>
+        <v>128685822</v>
       </c>
       <c r="B78" t="n">
-        <v>92884</v>
+        <v>57841</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810814</v>
+        <v>810901</v>
       </c>
       <c r="R78" t="n">
-        <v>7393022</v>
+        <v>7393040</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,32 +8153,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685851</v>
+        <v>128685780</v>
       </c>
       <c r="B79" t="n">
-        <v>92884</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811062</v>
+        <v>811531</v>
       </c>
       <c r="R79" t="n">
-        <v>7392883</v>
+        <v>7393153</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685819</v>
+        <v>128685781</v>
       </c>
       <c r="B80" t="n">
-        <v>90227</v>
+        <v>57737</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8261,21 +8261,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4962</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>810744</v>
+        <v>811507</v>
       </c>
       <c r="R80" t="n">
-        <v>7393058</v>
+        <v>7393120</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,32 +8347,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685780</v>
+        <v>128685851</v>
       </c>
       <c r="B81" t="n">
-        <v>57737</v>
+        <v>92884</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811531</v>
+        <v>811062</v>
       </c>
       <c r="R81" t="n">
-        <v>7393153</v>
+        <v>7392883</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685781</v>
+        <v>128685819</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>90227</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8455,21 +8455,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811507</v>
+        <v>810744</v>
       </c>
       <c r="R82" t="n">
-        <v>7393120</v>
+        <v>7393058</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685764</v>
+        <v>128685801</v>
       </c>
       <c r="B89" t="n">
-        <v>87033</v>
+        <v>92896</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810867</v>
+        <v>811116</v>
       </c>
       <c r="R89" t="n">
-        <v>7392967</v>
+        <v>7392980</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685763</v>
+        <v>128685764</v>
       </c>
       <c r="B90" t="n">
         <v>87033</v>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811097</v>
+        <v>810867</v>
       </c>
       <c r="R90" t="n">
-        <v>7392723</v>
+        <v>7392967</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,7 +9299,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9318,32 +9317,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685852</v>
+        <v>128685763</v>
       </c>
       <c r="B91" t="n">
-        <v>92884</v>
+        <v>87033</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9353,10 +9352,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811057</v>
+        <v>811097</v>
       </c>
       <c r="R91" t="n">
-        <v>7392877</v>
+        <v>7392723</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9397,6 +9396,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9415,10 +9415,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685801</v>
+        <v>128685852</v>
       </c>
       <c r="B92" t="n">
-        <v>92896</v>
+        <v>92884</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9426,21 +9426,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9450,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811116</v>
+        <v>811057</v>
       </c>
       <c r="R92" t="n">
-        <v>7392980</v>
+        <v>7392877</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9609,10 +9609,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685751</v>
+        <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>79703</v>
+        <v>87033</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9620,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811254</v>
+        <v>811050</v>
       </c>
       <c r="R94" t="n">
-        <v>7392831</v>
+        <v>7393050</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,12 +9682,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9706,10 +9712,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685770</v>
+        <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>87033</v>
+        <v>79703</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9717,21 +9723,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9741,10 +9747,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811050</v>
+        <v>811254</v>
       </c>
       <c r="R95" t="n">
-        <v>7393050</v>
+        <v>7392831</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9779,18 +9785,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685756</v>
+        <v>128685790</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811013</v>
+        <v>810977</v>
       </c>
       <c r="R2" t="n">
-        <v>7393006</v>
+        <v>7393016</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685843</v>
+        <v>128685783</v>
       </c>
       <c r="B3" t="n">
-        <v>92884</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>810858</v>
+        <v>811497</v>
       </c>
       <c r="R3" t="n">
-        <v>7392973</v>
+        <v>7393112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685837</v>
+        <v>128685843</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>92887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810756</v>
+        <v>810858</v>
       </c>
       <c r="R4" t="n">
-        <v>7393036</v>
+        <v>7392973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685836</v>
+        <v>128685837</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811057</v>
+        <v>810756</v>
       </c>
       <c r="R5" t="n">
-        <v>7393046</v>
+        <v>7393036</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685783</v>
+        <v>128685756</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811497</v>
+        <v>811013</v>
       </c>
       <c r="R6" t="n">
-        <v>7393112</v>
+        <v>7393006</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685790</v>
+        <v>128685836</v>
       </c>
       <c r="B7" t="n">
-        <v>56927</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810977</v>
+        <v>811057</v>
       </c>
       <c r="R7" t="n">
-        <v>7393016</v>
+        <v>7393046</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>128685853</v>
       </c>
       <c r="B8" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>128685804</v>
       </c>
       <c r="B9" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128685835</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128685866</v>
       </c>
       <c r="B11" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685769</v>
+        <v>128685874</v>
       </c>
       <c r="B12" t="n">
-        <v>87033</v>
+        <v>92881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>810725</v>
+        <v>811502</v>
       </c>
       <c r="R12" t="n">
-        <v>7393066</v>
+        <v>7393150</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685874</v>
+        <v>128685810</v>
       </c>
       <c r="B13" t="n">
-        <v>92878</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811502</v>
+        <v>811027</v>
       </c>
       <c r="R13" t="n">
-        <v>7393150</v>
+        <v>7393051</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685795</v>
+        <v>128685769</v>
       </c>
       <c r="B14" t="n">
-        <v>92529</v>
+        <v>87036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810915</v>
+        <v>810725</v>
       </c>
       <c r="R14" t="n">
-        <v>7393042</v>
+        <v>7393066</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685810</v>
+        <v>128685795</v>
       </c>
       <c r="B15" t="n">
-        <v>79108</v>
+        <v>92532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>4745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811027</v>
+        <v>810915</v>
       </c>
       <c r="R15" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2041,7 +2041,7 @@
         <v>128685766</v>
       </c>
       <c r="B16" t="n">
-        <v>87033</v>
+        <v>87036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685773</v>
+        <v>128685753</v>
       </c>
       <c r="B17" t="n">
-        <v>87033</v>
+        <v>79706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811089</v>
+        <v>811087</v>
       </c>
       <c r="R17" t="n">
-        <v>7393040</v>
+        <v>7393042</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685760</v>
+        <v>128685829</v>
       </c>
       <c r="B18" t="n">
-        <v>79674</v>
+        <v>78844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685753</v>
+        <v>128685826</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811087</v>
+        <v>811021</v>
       </c>
       <c r="R19" t="n">
-        <v>7393042</v>
+        <v>7392844</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685829</v>
+        <v>128685773</v>
       </c>
       <c r="B20" t="n">
-        <v>78841</v>
+        <v>87036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>810920</v>
+        <v>811089</v>
       </c>
       <c r="R20" t="n">
-        <v>7393003</v>
+        <v>7393040</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2506,6 +2505,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685826</v>
+        <v>128685760</v>
       </c>
       <c r="B21" t="n">
-        <v>78841</v>
+        <v>79677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811021</v>
+        <v>810920</v>
       </c>
       <c r="R21" t="n">
-        <v>7392844</v>
+        <v>7393003</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685816</v>
+        <v>128685869</v>
       </c>
       <c r="B22" t="n">
-        <v>78842</v>
+        <v>92887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810920</v>
+        <v>810738</v>
       </c>
       <c r="R22" t="n">
-        <v>7393003</v>
+        <v>7393051</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685869</v>
+        <v>128685802</v>
       </c>
       <c r="B23" t="n">
-        <v>92884</v>
+        <v>92899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2729,21 +2729,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810738</v>
+        <v>811027</v>
       </c>
       <c r="R23" t="n">
-        <v>7393051</v>
+        <v>7393042</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>128685854</v>
       </c>
       <c r="B24" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128685873</v>
       </c>
       <c r="B25" t="n">
-        <v>92878</v>
+        <v>92881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,32 +3009,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685802</v>
+        <v>128685778</v>
       </c>
       <c r="B26" t="n">
-        <v>92896</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811027</v>
+        <v>811517</v>
       </c>
       <c r="R26" t="n">
-        <v>7393042</v>
+        <v>7393148</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3109,7 +3109,7 @@
         <v>128685831</v>
       </c>
       <c r="B27" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685778</v>
+        <v>128685816</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3214,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811517</v>
+        <v>810920</v>
       </c>
       <c r="R28" t="n">
-        <v>7393148</v>
+        <v>7393003</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3300,32 +3300,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685839</v>
+        <v>128685861</v>
       </c>
       <c r="B29" t="n">
-        <v>78750</v>
+        <v>92887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811034</v>
+        <v>810965</v>
       </c>
       <c r="R29" t="n">
-        <v>7393002</v>
+        <v>7393009</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3400,7 +3400,7 @@
         <v>128685799</v>
       </c>
       <c r="B30" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685758</v>
+        <v>128685785</v>
       </c>
       <c r="B31" t="n">
-        <v>79703</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810717</v>
+        <v>811518</v>
       </c>
       <c r="R31" t="n">
-        <v>7393072</v>
+        <v>7393070</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,10 +3591,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685785</v>
+        <v>128685776</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811518</v>
+        <v>810803</v>
       </c>
       <c r="R32" t="n">
-        <v>7393070</v>
+        <v>7392998</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3688,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685776</v>
+        <v>128685839</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>78753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>810803</v>
+        <v>811034</v>
       </c>
       <c r="R33" t="n">
-        <v>7392998</v>
+        <v>7393002</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685861</v>
+        <v>128685808</v>
       </c>
       <c r="B34" t="n">
-        <v>92884</v>
+        <v>79111</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3796,21 +3796,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810965</v>
+        <v>811520</v>
       </c>
       <c r="R34" t="n">
-        <v>7393009</v>
+        <v>7393156</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,32 +3882,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685808</v>
+        <v>128685758</v>
       </c>
       <c r="B35" t="n">
-        <v>79108</v>
+        <v>79706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811520</v>
+        <v>810717</v>
       </c>
       <c r="R35" t="n">
-        <v>7393156</v>
+        <v>7393072</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
         <v>128685857</v>
       </c>
       <c r="B36" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>128685841</v>
       </c>
       <c r="B37" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>128685807</v>
       </c>
       <c r="B38" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>128685833</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>128685805</v>
       </c>
       <c r="B40" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685814</v>
+        <v>128685818</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>90230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4475,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>810773</v>
+        <v>811120</v>
       </c>
       <c r="R41" t="n">
-        <v>7392966</v>
+        <v>7392983</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,32 +4561,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685798</v>
+        <v>128685761</v>
       </c>
       <c r="B42" t="n">
-        <v>92896</v>
+        <v>87036</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810767</v>
+        <v>811014</v>
       </c>
       <c r="R42" t="n">
-        <v>7393075</v>
+        <v>7392891</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4640,6 +4640,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4658,32 +4659,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685818</v>
+        <v>128685798</v>
       </c>
       <c r="B43" t="n">
-        <v>90227</v>
+        <v>92899</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4693,10 +4694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811120</v>
+        <v>810767</v>
       </c>
       <c r="R43" t="n">
-        <v>7392983</v>
+        <v>7393075</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4755,10 +4756,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685828</v>
+        <v>128685877</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>92881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4766,21 +4767,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4790,10 +4791,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811225</v>
+        <v>811258</v>
       </c>
       <c r="R44" t="n">
-        <v>7392837</v>
+        <v>7392822</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4852,10 +4853,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685877</v>
+        <v>128685828</v>
       </c>
       <c r="B45" t="n">
-        <v>92878</v>
+        <v>78844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,21 +4864,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4887,10 +4888,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811258</v>
+        <v>811225</v>
       </c>
       <c r="R45" t="n">
-        <v>7392822</v>
+        <v>7392837</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4949,10 +4950,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685761</v>
+        <v>128685814</v>
       </c>
       <c r="B46" t="n">
-        <v>87033</v>
+        <v>78845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4960,21 +4961,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3690</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4984,10 +4985,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811014</v>
+        <v>810773</v>
       </c>
       <c r="R46" t="n">
-        <v>7392891</v>
+        <v>7392966</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5028,7 +5029,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5047,32 +5047,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685875</v>
+        <v>128685809</v>
       </c>
       <c r="B47" t="n">
-        <v>92878</v>
+        <v>79111</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811283</v>
+        <v>811105</v>
       </c>
       <c r="R47" t="n">
-        <v>7392844</v>
+        <v>7393054</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685792</v>
+        <v>128685777</v>
       </c>
       <c r="B48" t="n">
-        <v>92909</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5155,21 +5155,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3100</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5179,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811023</v>
+        <v>811015</v>
       </c>
       <c r="R48" t="n">
-        <v>7392776</v>
+        <v>7392800</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5241,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685793</v>
+        <v>128685792</v>
       </c>
       <c r="B49" t="n">
-        <v>92909</v>
+        <v>92912</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>810740</v>
+        <v>811023</v>
       </c>
       <c r="R49" t="n">
-        <v>7393062</v>
+        <v>7392776</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,32 +5338,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685809</v>
+        <v>128685793</v>
       </c>
       <c r="B50" t="n">
-        <v>79108</v>
+        <v>92912</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811105</v>
+        <v>810740</v>
       </c>
       <c r="R50" t="n">
-        <v>7393054</v>
+        <v>7393062</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685777</v>
+        <v>128685875</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>92881</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5446,21 +5446,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811015</v>
+        <v>811283</v>
       </c>
       <c r="R51" t="n">
-        <v>7392800</v>
+        <v>7392844</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5535,7 +5535,7 @@
         <v>128685844</v>
       </c>
       <c r="B52" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>128685803</v>
       </c>
       <c r="B53" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5726,32 +5726,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685767</v>
+        <v>128685850</v>
       </c>
       <c r="B54" t="n">
-        <v>87033</v>
+        <v>92887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811516</v>
+        <v>810978</v>
       </c>
       <c r="R54" t="n">
-        <v>7393158</v>
+        <v>7392914</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5826,7 +5826,7 @@
         <v>128685876</v>
       </c>
       <c r="B55" t="n">
-        <v>92878</v>
+        <v>92881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>128685855</v>
       </c>
       <c r="B56" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>128685868</v>
       </c>
       <c r="B57" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6114,32 +6114,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685850</v>
+        <v>128685767</v>
       </c>
       <c r="B58" t="n">
-        <v>92884</v>
+        <v>87036</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6149,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>810978</v>
+        <v>811516</v>
       </c>
       <c r="R58" t="n">
-        <v>7392914</v>
+        <v>7393158</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6214,7 +6214,7 @@
         <v>128685823</v>
       </c>
       <c r="B59" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>128685815</v>
       </c>
       <c r="B60" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6405,32 +6405,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685789</v>
+        <v>128685771</v>
       </c>
       <c r="B61" t="n">
-        <v>90425</v>
+        <v>87036</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6286</v>
+        <v>3690</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811258</v>
+        <v>811112</v>
       </c>
       <c r="R61" t="n">
-        <v>7392822</v>
+        <v>7393038</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6503,10 +6503,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685812</v>
+        <v>128685859</v>
       </c>
       <c r="B62" t="n">
-        <v>79108</v>
+        <v>92887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6514,21 +6514,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>810948</v>
+        <v>811498</v>
       </c>
       <c r="R62" t="n">
-        <v>7392987</v>
+        <v>7393147</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,32 +6600,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685752</v>
+        <v>128685800</v>
       </c>
       <c r="B63" t="n">
-        <v>79703</v>
+        <v>92899</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811410</v>
+        <v>810861</v>
       </c>
       <c r="R63" t="n">
-        <v>7392970</v>
+        <v>7392976</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6697,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685806</v>
+        <v>128685788</v>
       </c>
       <c r="B64" t="n">
-        <v>79108</v>
+        <v>57740</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811056</v>
+        <v>811107</v>
       </c>
       <c r="R64" t="n">
-        <v>7392881</v>
+        <v>7393022</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,32 +6794,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685771</v>
+        <v>128685789</v>
       </c>
       <c r="B65" t="n">
-        <v>87033</v>
+        <v>90428</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811112</v>
+        <v>811258</v>
       </c>
       <c r="R65" t="n">
-        <v>7393038</v>
+        <v>7392822</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685859</v>
+        <v>128685812</v>
       </c>
       <c r="B66" t="n">
-        <v>92884</v>
+        <v>79111</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6903,21 +6903,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811498</v>
+        <v>810948</v>
       </c>
       <c r="R66" t="n">
-        <v>7393147</v>
+        <v>7392987</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,32 +6989,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685800</v>
+        <v>128685752</v>
       </c>
       <c r="B67" t="n">
-        <v>92896</v>
+        <v>79706</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>810861</v>
+        <v>811410</v>
       </c>
       <c r="R67" t="n">
-        <v>7392976</v>
+        <v>7392970</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,32 +7086,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685788</v>
+        <v>128685806</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>79111</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811107</v>
+        <v>811056</v>
       </c>
       <c r="R68" t="n">
-        <v>7393022</v>
+        <v>7392881</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7186,7 +7186,7 @@
         <v>128685838</v>
       </c>
       <c r="B69" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>128685813</v>
       </c>
       <c r="B70" t="n">
-        <v>91655</v>
+        <v>91658</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7377,32 +7377,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685754</v>
+        <v>128685840</v>
       </c>
       <c r="B71" t="n">
-        <v>79703</v>
+        <v>92887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811026</v>
+        <v>810762</v>
       </c>
       <c r="R71" t="n">
-        <v>7393053</v>
+        <v>7393078</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,32 +7474,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685840</v>
+        <v>128685872</v>
       </c>
       <c r="B72" t="n">
-        <v>92884</v>
+        <v>92881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>810762</v>
+        <v>811269</v>
       </c>
       <c r="R72" t="n">
-        <v>7393078</v>
+        <v>7392839</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7571,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685872</v>
+        <v>128685856</v>
       </c>
       <c r="B73" t="n">
-        <v>92878</v>
+        <v>92887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811269</v>
+        <v>811494</v>
       </c>
       <c r="R73" t="n">
-        <v>7392839</v>
+        <v>7393153</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,32 +7668,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685856</v>
+        <v>128685754</v>
       </c>
       <c r="B74" t="n">
-        <v>92884</v>
+        <v>79706</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811494</v>
+        <v>811026</v>
       </c>
       <c r="R74" t="n">
-        <v>7393153</v>
+        <v>7393053</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685848</v>
+        <v>128685822</v>
       </c>
       <c r="B75" t="n">
-        <v>92884</v>
+        <v>57844</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810952</v>
+        <v>810901</v>
       </c>
       <c r="R75" t="n">
-        <v>7392920</v>
+        <v>7393040</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685846</v>
+        <v>128685848</v>
       </c>
       <c r="B76" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7897,10 +7897,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810911</v>
+        <v>810952</v>
       </c>
       <c r="R76" t="n">
-        <v>7392927</v>
+        <v>7392920</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685864</v>
+        <v>128685846</v>
       </c>
       <c r="B77" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810814</v>
+        <v>810911</v>
       </c>
       <c r="R77" t="n">
-        <v>7393022</v>
+        <v>7392927</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,10 +8056,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685822</v>
+        <v>128685864</v>
       </c>
       <c r="B78" t="n">
-        <v>57841</v>
+        <v>92887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8067,21 +8067,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810901</v>
+        <v>810814</v>
       </c>
       <c r="R78" t="n">
-        <v>7393040</v>
+        <v>7393022</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685780</v>
+        <v>128685819</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>90230</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8164,21 +8164,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>4962</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811531</v>
+        <v>810744</v>
       </c>
       <c r="R79" t="n">
-        <v>7393153</v>
+        <v>7393058</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8253,7 +8253,7 @@
         <v>128685781</v>
       </c>
       <c r="B80" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8347,32 +8347,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685851</v>
+        <v>128685780</v>
       </c>
       <c r="B81" t="n">
-        <v>92884</v>
+        <v>57740</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811062</v>
+        <v>811531</v>
       </c>
       <c r="R81" t="n">
-        <v>7392883</v>
+        <v>7393153</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,32 +8444,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685819</v>
+        <v>128685851</v>
       </c>
       <c r="B82" t="n">
-        <v>90227</v>
+        <v>92887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8479,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>810744</v>
+        <v>811062</v>
       </c>
       <c r="R82" t="n">
-        <v>7393058</v>
+        <v>7392883</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8541,32 +8541,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685847</v>
+        <v>128685817</v>
       </c>
       <c r="B83" t="n">
-        <v>92884</v>
+        <v>90230</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>810944</v>
+        <v>811007</v>
       </c>
       <c r="R83" t="n">
-        <v>7392948</v>
+        <v>7392796</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685817</v>
+        <v>128685847</v>
       </c>
       <c r="B84" t="n">
-        <v>90227</v>
+        <v>92887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811007</v>
+        <v>810944</v>
       </c>
       <c r="R84" t="n">
-        <v>7392796</v>
+        <v>7392948</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8738,7 +8738,7 @@
         <v>128685748</v>
       </c>
       <c r="B85" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8832,32 +8832,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685749</v>
+        <v>128685860</v>
       </c>
       <c r="B86" t="n">
-        <v>79703</v>
+        <v>92887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811061</v>
+        <v>811528</v>
       </c>
       <c r="R86" t="n">
-        <v>7392880</v>
+        <v>7393160</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8929,10 +8929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685825</v>
+        <v>128685749</v>
       </c>
       <c r="B87" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>810871</v>
+        <v>811061</v>
       </c>
       <c r="R87" t="n">
-        <v>7392966</v>
+        <v>7392880</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,32 +9026,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685860</v>
+        <v>128685825</v>
       </c>
       <c r="B88" t="n">
-        <v>92884</v>
+        <v>78844</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811528</v>
+        <v>810871</v>
       </c>
       <c r="R88" t="n">
-        <v>7393160</v>
+        <v>7392966</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,32 +9123,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685801</v>
+        <v>128685764</v>
       </c>
       <c r="B89" t="n">
-        <v>92896</v>
+        <v>87036</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811116</v>
+        <v>810867</v>
       </c>
       <c r="R89" t="n">
-        <v>7392980</v>
+        <v>7392967</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,10 +9220,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685764</v>
+        <v>128685763</v>
       </c>
       <c r="B90" t="n">
-        <v>87033</v>
+        <v>87036</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>810867</v>
+        <v>811097</v>
       </c>
       <c r="R90" t="n">
-        <v>7392967</v>
+        <v>7392723</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,6 +9299,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9317,32 +9318,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685763</v>
+        <v>128685801</v>
       </c>
       <c r="B91" t="n">
-        <v>87033</v>
+        <v>92899</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9352,10 +9353,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811097</v>
+        <v>811116</v>
       </c>
       <c r="R91" t="n">
-        <v>7392723</v>
+        <v>7392980</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9396,7 +9397,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>128685852</v>
       </c>
       <c r="B92" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>128685796</v>
       </c>
       <c r="B93" t="n">
-        <v>92915</v>
+        <v>92918</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>128685770</v>
       </c>
       <c r="B94" t="n">
-        <v>87033</v>
+        <v>87036</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>128685751</v>
       </c>
       <c r="B95" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>128685849</v>
       </c>
       <c r="B96" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>128685863</v>
       </c>
       <c r="B97" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>128685834</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 35449-2025 artfynd.xlsx
+++ b/artfynd/A 35449-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128685790</v>
+        <v>128685839</v>
       </c>
       <c r="B2" t="n">
-        <v>57092</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>810977</v>
+        <v>811034</v>
       </c>
       <c r="R2" t="n">
-        <v>7393016</v>
+        <v>7393002</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128685783</v>
+        <v>128685838</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811497</v>
+        <v>810781</v>
       </c>
       <c r="R3" t="n">
-        <v>7393112</v>
+        <v>7392936</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128685843</v>
+        <v>128685813</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>810858</v>
+        <v>810934</v>
       </c>
       <c r="R4" t="n">
-        <v>7392973</v>
+        <v>7393019</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128685837</v>
+        <v>128685792</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>93222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3100</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>810756</v>
+        <v>811023</v>
       </c>
       <c r="R5" t="n">
-        <v>7393036</v>
+        <v>7392776</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128685756</v>
+        <v>128685793</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>93222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811013</v>
+        <v>810740</v>
       </c>
       <c r="R6" t="n">
-        <v>7393006</v>
+        <v>7393062</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128685836</v>
+        <v>128685761</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>87325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811057</v>
+        <v>811014</v>
       </c>
       <c r="R7" t="n">
-        <v>7393046</v>
+        <v>7392891</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1244,6 +1239,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1262,32 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128685853</v>
+        <v>128685763</v>
       </c>
       <c r="B8" t="n">
-        <v>92887</v>
+        <v>87325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811044</v>
+        <v>811097</v>
       </c>
       <c r="R8" t="n">
-        <v>7392879</v>
+        <v>7392723</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1341,6 +1337,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1359,32 +1356,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128685804</v>
+        <v>128685764</v>
       </c>
       <c r="B9" t="n">
-        <v>92899</v>
+        <v>87325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1391,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>810710</v>
+        <v>810867</v>
       </c>
       <c r="R9" t="n">
-        <v>7393058</v>
+        <v>7392967</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,10 +1453,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128685835</v>
+        <v>128685766</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>87325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1464,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1488,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811420</v>
+        <v>810920</v>
       </c>
       <c r="R10" t="n">
-        <v>7392954</v>
+        <v>7392937</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1553,32 +1550,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128685866</v>
+        <v>128685767</v>
       </c>
       <c r="B11" t="n">
-        <v>92887</v>
+        <v>87325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1585,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810789</v>
+        <v>811516</v>
       </c>
       <c r="R11" t="n">
-        <v>7393036</v>
+        <v>7393158</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1650,10 +1647,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128685874</v>
+        <v>128685769</v>
       </c>
       <c r="B12" t="n">
-        <v>92881</v>
+        <v>87325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1658,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811502</v>
+        <v>810725</v>
       </c>
       <c r="R12" t="n">
-        <v>7393150</v>
+        <v>7393066</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1747,32 +1744,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128685810</v>
+        <v>128685770</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>87325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>3690</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811027</v>
+        <v>811050</v>
       </c>
       <c r="R13" t="n">
-        <v>7393051</v>
+        <v>7393050</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1820,12 +1817,18 @@
           <t>2025-09-24</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1844,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128685769</v>
+        <v>128685771</v>
       </c>
       <c r="B14" t="n">
-        <v>87036</v>
+        <v>87325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810725</v>
+        <v>811112</v>
       </c>
       <c r="R14" t="n">
-        <v>7393066</v>
+        <v>7393038</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1923,6 +1926,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1941,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128685795</v>
+        <v>128685773</v>
       </c>
       <c r="B15" t="n">
-        <v>92532</v>
+        <v>87325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4745</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>810915</v>
+        <v>811089</v>
       </c>
       <c r="R15" t="n">
-        <v>7393042</v>
+        <v>7393040</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2020,6 +2024,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2038,10 +2043,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128685766</v>
+        <v>128685872</v>
       </c>
       <c r="B16" t="n">
-        <v>87036</v>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2054,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810920</v>
+        <v>811269</v>
       </c>
       <c r="R16" t="n">
-        <v>7392937</v>
+        <v>7392839</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2135,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128685753</v>
+        <v>128685873</v>
       </c>
       <c r="B17" t="n">
-        <v>79706</v>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2151,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811087</v>
+        <v>811303</v>
       </c>
       <c r="R17" t="n">
-        <v>7393042</v>
+        <v>7392893</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2232,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128685829</v>
+        <v>128685874</v>
       </c>
       <c r="B18" t="n">
-        <v>78844</v>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2248,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810920</v>
+        <v>811502</v>
       </c>
       <c r="R18" t="n">
-        <v>7393003</v>
+        <v>7393150</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2329,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128685826</v>
+        <v>128685875</v>
       </c>
       <c r="B19" t="n">
-        <v>78844</v>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,7 +2369,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811021</v>
+        <v>811283</v>
       </c>
       <c r="R19" t="n">
         <v>7392844</v>
@@ -2426,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128685773</v>
+        <v>128685876</v>
       </c>
       <c r="B20" t="n">
-        <v>87036</v>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811089</v>
+        <v>811269</v>
       </c>
       <c r="R20" t="n">
-        <v>7393040</v>
+        <v>7392821</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2505,7 +2510,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2524,10 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128685760</v>
+        <v>128685877</v>
       </c>
       <c r="B21" t="n">
-        <v>79677</v>
+        <v>93191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810920</v>
+        <v>811258</v>
       </c>
       <c r="R21" t="n">
-        <v>7393003</v>
+        <v>7392822</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2621,14 +2625,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128685869</v>
+        <v>128685840</v>
       </c>
       <c r="B22" t="n">
-        <v>92887</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2656,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>810738</v>
+        <v>810762</v>
       </c>
       <c r="R22" t="n">
-        <v>7393051</v>
+        <v>7393078</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2718,32 +2722,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128685802</v>
+        <v>128685841</v>
       </c>
       <c r="B23" t="n">
-        <v>92899</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811027</v>
+        <v>810812</v>
       </c>
       <c r="R23" t="n">
-        <v>7393042</v>
+        <v>7392934</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2815,14 +2819,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128685854</v>
+        <v>128685843</v>
       </c>
       <c r="B24" t="n">
-        <v>92887</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2850,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811441</v>
+        <v>810858</v>
       </c>
       <c r="R24" t="n">
-        <v>7393097</v>
+        <v>7392973</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2912,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128685873</v>
+        <v>128685844</v>
       </c>
       <c r="B25" t="n">
-        <v>92881</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2923,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811303</v>
+        <v>810873</v>
       </c>
       <c r="R25" t="n">
-        <v>7392893</v>
+        <v>7392973</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3009,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128685778</v>
+        <v>128685846</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>93197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811517</v>
+        <v>810911</v>
       </c>
       <c r="R26" t="n">
-        <v>7393148</v>
+        <v>7392927</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3106,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128685831</v>
+        <v>128685847</v>
       </c>
       <c r="B27" t="n">
-        <v>78844</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>810853</v>
+        <v>810944</v>
       </c>
       <c r="R27" t="n">
-        <v>7393047</v>
+        <v>7392948</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3203,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128685816</v>
+        <v>128685848</v>
       </c>
       <c r="B28" t="n">
-        <v>78845</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3214,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810920</v>
+        <v>810952</v>
       </c>
       <c r="R28" t="n">
-        <v>7393003</v>
+        <v>7392920</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3300,14 +3304,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128685861</v>
+        <v>128685849</v>
       </c>
       <c r="B29" t="n">
-        <v>92887</v>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3335,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810965</v>
+        <v>810964</v>
       </c>
       <c r="R29" t="n">
-        <v>7393009</v>
+        <v>7392920</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3397,32 +3401,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128685799</v>
+        <v>128685850</v>
       </c>
       <c r="B30" t="n">
-        <v>92899</v>
+        <v>93197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>810790</v>
+        <v>810978</v>
       </c>
       <c r="R30" t="n">
-        <v>7392931</v>
+        <v>7392914</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3494,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128685785</v>
+        <v>128685851</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,21 +3509,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811518</v>
+        <v>811062</v>
       </c>
       <c r="R31" t="n">
-        <v>7393070</v>
+        <v>7392883</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3591,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128685776</v>
+        <v>128685852</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3602,21 +3606,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810803</v>
+        <v>811057</v>
       </c>
       <c r="R32" t="n">
-        <v>7392998</v>
+        <v>7392877</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3688,10 +3692,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128685839</v>
+        <v>128685853</v>
       </c>
       <c r="B33" t="n">
-        <v>78753</v>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3699,21 +3703,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3723,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811034</v>
+        <v>811044</v>
       </c>
       <c r="R33" t="n">
-        <v>7393002</v>
+        <v>7392879</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3785,32 +3789,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128685808</v>
+        <v>128685854</v>
       </c>
       <c r="B34" t="n">
-        <v>79111</v>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3820,10 +3824,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811520</v>
+        <v>811441</v>
       </c>
       <c r="R34" t="n">
-        <v>7393156</v>
+        <v>7393097</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3882,10 +3886,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128685758</v>
+        <v>128685855</v>
       </c>
       <c r="B35" t="n">
-        <v>79706</v>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3893,21 +3897,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3917,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810717</v>
+        <v>811502</v>
       </c>
       <c r="R35" t="n">
-        <v>7393072</v>
+        <v>7393143</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3979,14 +3983,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128685857</v>
+        <v>128685856</v>
       </c>
       <c r="B36" t="n">
-        <v>92887</v>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4014,10 +4018,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811492</v>
+        <v>811494</v>
       </c>
       <c r="R36" t="n">
-        <v>7393149</v>
+        <v>7393153</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4076,14 +4080,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128685841</v>
+        <v>128685857</v>
       </c>
       <c r="B37" t="n">
-        <v>92887</v>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4111,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810812</v>
+        <v>811492</v>
       </c>
       <c r="R37" t="n">
-        <v>7392934</v>
+        <v>7393149</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4173,32 +4177,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128685807</v>
+        <v>128685859</v>
       </c>
       <c r="B38" t="n">
-        <v>79111</v>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4208,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811004</v>
+        <v>811498</v>
       </c>
       <c r="R38" t="n">
-        <v>7392787</v>
+        <v>7393147</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4270,10 +4274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128685833</v>
+        <v>128685860</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4281,21 +4285,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4305,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811464</v>
+        <v>811528</v>
       </c>
       <c r="R39" t="n">
-        <v>7393013</v>
+        <v>7393160</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4367,32 +4371,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128685805</v>
+        <v>128685861</v>
       </c>
       <c r="B40" t="n">
-        <v>79111</v>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4402,10 +4406,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810973</v>
+        <v>810965</v>
       </c>
       <c r="R40" t="n">
-        <v>7392910</v>
+        <v>7393009</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4464,10 +4468,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128685818</v>
+        <v>128685863</v>
       </c>
       <c r="B41" t="n">
-        <v>90230</v>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4475,21 +4479,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4499,10 +4503,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811120</v>
+        <v>810854</v>
       </c>
       <c r="R41" t="n">
-        <v>7392983</v>
+        <v>7393015</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4561,10 +4565,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128685761</v>
+        <v>128685864</v>
       </c>
       <c r="B42" t="n">
-        <v>87036</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,21 +4576,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4596,10 +4600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811014</v>
+        <v>810814</v>
       </c>
       <c r="R42" t="n">
-        <v>7392891</v>
+        <v>7393022</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4640,7 +4644,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4659,32 +4662,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128685798</v>
+        <v>128685866</v>
       </c>
       <c r="B43" t="n">
-        <v>92899</v>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4694,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810767</v>
+        <v>810789</v>
       </c>
       <c r="R43" t="n">
-        <v>7393075</v>
+        <v>7393036</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4756,10 +4759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128685877</v>
+        <v>128685868</v>
       </c>
       <c r="B44" t="n">
-        <v>92881</v>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4767,21 +4770,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4791,10 +4794,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811258</v>
+        <v>810757</v>
       </c>
       <c r="R44" t="n">
-        <v>7392822</v>
+        <v>7393053</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4853,10 +4856,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128685828</v>
+        <v>128685869</v>
       </c>
       <c r="B45" t="n">
-        <v>78844</v>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4864,21 +4867,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4888,10 +4891,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811225</v>
+        <v>810738</v>
       </c>
       <c r="R45" t="n">
-        <v>7392837</v>
+        <v>7393051</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4950,10 +4953,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128685814</v>
+        <v>128685870</v>
       </c>
       <c r="B46" t="n">
-        <v>78845</v>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4961,21 +4964,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4985,10 +4988,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>810773</v>
+        <v>810713</v>
       </c>
       <c r="R46" t="n">
-        <v>7392966</v>
+        <v>7393084</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5047,32 +5050,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128685809</v>
+        <v>128685798</v>
       </c>
       <c r="B47" t="n">
-        <v>79111</v>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6434</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5082,10 +5085,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811105</v>
+        <v>810767</v>
       </c>
       <c r="R47" t="n">
-        <v>7393054</v>
+        <v>7393075</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5144,10 +5147,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128685777</v>
+        <v>128685799</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5155,21 +5158,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5179,10 +5182,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811015</v>
+        <v>810790</v>
       </c>
       <c r="R48" t="n">
-        <v>7392800</v>
+        <v>7392931</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5241,10 +5244,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128685792</v>
+        <v>128685800</v>
       </c>
       <c r="B49" t="n">
-        <v>92912</v>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5252,21 +5255,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5276,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811023</v>
+        <v>810861</v>
       </c>
       <c r="R49" t="n">
-        <v>7392776</v>
+        <v>7392976</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5338,10 +5341,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128685793</v>
+        <v>128685801</v>
       </c>
       <c r="B50" t="n">
-        <v>92912</v>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5349,21 +5352,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5373,10 +5376,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>810740</v>
+        <v>811116</v>
       </c>
       <c r="R50" t="n">
-        <v>7393062</v>
+        <v>7392980</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5435,10 +5438,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128685875</v>
+        <v>128685802</v>
       </c>
       <c r="B51" t="n">
-        <v>92881</v>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5446,21 +5449,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5470,10 +5473,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811283</v>
+        <v>811027</v>
       </c>
       <c r="R51" t="n">
-        <v>7392844</v>
+        <v>7393042</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5532,32 +5535,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128685844</v>
+        <v>128685803</v>
       </c>
       <c r="B52" t="n">
-        <v>92887</v>
+        <v>93209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5567,10 +5570,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>810873</v>
+        <v>810733</v>
       </c>
       <c r="R52" t="n">
-        <v>7392973</v>
+        <v>7393068</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5629,14 +5632,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128685803</v>
+        <v>128685804</v>
       </c>
       <c r="B53" t="n">
-        <v>92899</v>
+        <v>93209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5664,10 +5667,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810733</v>
+        <v>810710</v>
       </c>
       <c r="R53" t="n">
-        <v>7393068</v>
+        <v>7393058</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5726,32 +5729,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128685850</v>
+        <v>128685795</v>
       </c>
       <c r="B54" t="n">
-        <v>92887</v>
+        <v>92841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5761,10 +5764,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810978</v>
+        <v>810915</v>
       </c>
       <c r="R54" t="n">
-        <v>7392914</v>
+        <v>7393042</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5823,10 +5826,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128685876</v>
+        <v>128685817</v>
       </c>
       <c r="B55" t="n">
-        <v>92881</v>
+        <v>90522</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5834,21 +5837,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4962</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5858,10 +5861,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811269</v>
+        <v>811007</v>
       </c>
       <c r="R55" t="n">
-        <v>7392821</v>
+        <v>7392796</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5920,32 +5923,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128685855</v>
+        <v>128685818</v>
       </c>
       <c r="B56" t="n">
-        <v>92887</v>
+        <v>90522</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5955,10 +5958,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811502</v>
+        <v>811120</v>
       </c>
       <c r="R56" t="n">
-        <v>7393143</v>
+        <v>7392983</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6017,32 +6020,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128685868</v>
+        <v>128685819</v>
       </c>
       <c r="B57" t="n">
-        <v>92887</v>
+        <v>90522</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6052,10 +6055,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810757</v>
+        <v>810744</v>
       </c>
       <c r="R57" t="n">
-        <v>7393053</v>
+        <v>7393058</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6114,32 +6117,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128685767</v>
+        <v>128685789</v>
       </c>
       <c r="B58" t="n">
-        <v>87036</v>
+        <v>90710</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3690</v>
+        <v>6286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6149,10 +6152,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811516</v>
+        <v>811258</v>
       </c>
       <c r="R58" t="n">
-        <v>7393158</v>
+        <v>7392822</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6193,6 +6196,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6211,32 +6215,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128685823</v>
+        <v>128685832</v>
       </c>
       <c r="B59" t="n">
-        <v>58111</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6246,10 +6250,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811127</v>
+        <v>811008</v>
       </c>
       <c r="R59" t="n">
-        <v>7392976</v>
+        <v>7392848</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6308,32 +6312,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128685815</v>
+        <v>128685833</v>
       </c>
       <c r="B60" t="n">
-        <v>78845</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6343,10 +6347,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>810946</v>
+        <v>811464</v>
       </c>
       <c r="R60" t="n">
-        <v>7392983</v>
+        <v>7393013</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6405,32 +6409,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128685771</v>
+        <v>128685834</v>
       </c>
       <c r="B61" t="n">
-        <v>87036</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6440,10 +6444,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811112</v>
+        <v>811525</v>
       </c>
       <c r="R61" t="n">
-        <v>7393038</v>
+        <v>7393139</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6484,7 +6488,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6503,32 +6506,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128685859</v>
+        <v>128685835</v>
       </c>
       <c r="B62" t="n">
-        <v>92887</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6538,10 +6541,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811498</v>
+        <v>811420</v>
       </c>
       <c r="R62" t="n">
-        <v>7393147</v>
+        <v>7392954</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6600,32 +6603,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128685800</v>
+        <v>128685836</v>
       </c>
       <c r="B63" t="n">
-        <v>92899</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6635,10 +6638,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>810861</v>
+        <v>811057</v>
       </c>
       <c r="R63" t="n">
-        <v>7392976</v>
+        <v>7393046</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6697,32 +6700,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128685788</v>
+        <v>128685837</v>
       </c>
       <c r="B64" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6732,10 +6735,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811107</v>
+        <v>810756</v>
       </c>
       <c r="R64" t="n">
-        <v>7393022</v>
+        <v>7393036</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6794,32 +6797,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128685789</v>
+        <v>128685805</v>
       </c>
       <c r="B65" t="n">
-        <v>90428</v>
+        <v>79351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6286</v>
+        <v>6434</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6829,10 +6832,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811258</v>
+        <v>810973</v>
       </c>
       <c r="R65" t="n">
-        <v>7392822</v>
+        <v>7392910</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -6873,7 +6876,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -6892,10 +6894,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128685812</v>
+        <v>128685806</v>
       </c>
       <c r="B66" t="n">
-        <v>79111</v>
+        <v>79351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6927,10 +6929,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>810948</v>
+        <v>811056</v>
       </c>
       <c r="R66" t="n">
-        <v>7392987</v>
+        <v>7392881</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -6989,32 +6991,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128685752</v>
+        <v>128685807</v>
       </c>
       <c r="B67" t="n">
-        <v>79706</v>
+        <v>79351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7024,10 +7026,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811410</v>
+        <v>811004</v>
       </c>
       <c r="R67" t="n">
-        <v>7392970</v>
+        <v>7392787</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7086,10 +7088,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128685806</v>
+        <v>128685808</v>
       </c>
       <c r="B68" t="n">
-        <v>79111</v>
+        <v>79351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7121,10 +7123,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811056</v>
+        <v>811520</v>
       </c>
       <c r="R68" t="n">
-        <v>7392881</v>
+        <v>7393156</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7183,32 +7185,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128685838</v>
+        <v>128685809</v>
       </c>
       <c r="B69" t="n">
-        <v>82924</v>
+        <v>79351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7218,10 +7220,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>810781</v>
+        <v>811105</v>
       </c>
       <c r="R69" t="n">
-        <v>7392936</v>
+        <v>7393054</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7280,32 +7282,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128685813</v>
+        <v>128685810</v>
       </c>
       <c r="B70" t="n">
-        <v>91658</v>
+        <v>79351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7315,10 +7317,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>810934</v>
+        <v>811027</v>
       </c>
       <c r="R70" t="n">
-        <v>7393019</v>
+        <v>7393051</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7377,10 +7379,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128685840</v>
+        <v>128685812</v>
       </c>
       <c r="B71" t="n">
-        <v>92887</v>
+        <v>79351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7388,21 +7390,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7412,10 +7414,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>810762</v>
+        <v>810948</v>
       </c>
       <c r="R71" t="n">
-        <v>7393078</v>
+        <v>7392987</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7474,10 +7476,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128685872</v>
+        <v>128685825</v>
       </c>
       <c r="B72" t="n">
-        <v>92881</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7485,21 +7487,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7509,10 +7511,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811269</v>
+        <v>810871</v>
       </c>
       <c r="R72" t="n">
-        <v>7392839</v>
+        <v>7392966</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7571,32 +7573,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128685856</v>
+        <v>128685826</v>
       </c>
       <c r="B73" t="n">
-        <v>92887</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7606,10 +7608,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811494</v>
+        <v>811021</v>
       </c>
       <c r="R73" t="n">
-        <v>7393153</v>
+        <v>7392844</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7668,10 +7670,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128685754</v>
+        <v>128685827</v>
       </c>
       <c r="B74" t="n">
-        <v>79706</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7679,21 +7681,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7703,10 +7705,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811026</v>
+        <v>811426</v>
       </c>
       <c r="R74" t="n">
-        <v>7393053</v>
+        <v>7393101</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7765,32 +7767,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128685822</v>
+        <v>128685828</v>
       </c>
       <c r="B75" t="n">
-        <v>57844</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7800,10 +7802,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>810901</v>
+        <v>811225</v>
       </c>
       <c r="R75" t="n">
-        <v>7393040</v>
+        <v>7392837</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7862,32 +7864,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128685848</v>
+        <v>128685829</v>
       </c>
       <c r="B76" t="n">
-        <v>92887</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7897,10 +7899,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>810952</v>
+        <v>810920</v>
       </c>
       <c r="R76" t="n">
-        <v>7392920</v>
+        <v>7393003</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -7959,32 +7961,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128685846</v>
+        <v>128685831</v>
       </c>
       <c r="B77" t="n">
-        <v>92887</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -7994,10 +7996,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>810911</v>
+        <v>810853</v>
       </c>
       <c r="R77" t="n">
-        <v>7392927</v>
+        <v>7393047</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8056,32 +8058,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128685864</v>
+        <v>128685748</v>
       </c>
       <c r="B78" t="n">
-        <v>92887</v>
+        <v>79946</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8091,10 +8093,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>810814</v>
+        <v>810767</v>
       </c>
       <c r="R78" t="n">
-        <v>7393022</v>
+        <v>7392968</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8153,10 +8155,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128685819</v>
+        <v>128685749</v>
       </c>
       <c r="B79" t="n">
-        <v>90230</v>
+        <v>79946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8164,21 +8166,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8188,10 +8190,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>810744</v>
+        <v>811061</v>
       </c>
       <c r="R79" t="n">
-        <v>7393058</v>
+        <v>7392880</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8250,10 +8252,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128685781</v>
+        <v>128685751</v>
       </c>
       <c r="B80" t="n">
-        <v>57740</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8261,21 +8263,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8285,10 +8287,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811507</v>
+        <v>811254</v>
       </c>
       <c r="R80" t="n">
-        <v>7393120</v>
+        <v>7392831</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8347,10 +8349,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128685780</v>
+        <v>128685752</v>
       </c>
       <c r="B81" t="n">
-        <v>57740</v>
+        <v>79946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8358,21 +8360,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8382,10 +8384,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811531</v>
+        <v>811410</v>
       </c>
       <c r="R81" t="n">
-        <v>7393153</v>
+        <v>7392970</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8444,32 +8446,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128685851</v>
+        <v>128685753</v>
       </c>
       <c r="B82" t="n">
-        <v>92887</v>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8479,10 +8481,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811062</v>
+        <v>811087</v>
       </c>
       <c r="R82" t="n">
-        <v>7392883</v>
+        <v>7393042</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8541,10 +8543,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128685817</v>
+        <v>128685754</v>
       </c>
       <c r="B83" t="n">
-        <v>90230</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8552,21 +8554,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4962</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8576,10 +8578,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811007</v>
+        <v>811026</v>
       </c>
       <c r="R83" t="n">
-        <v>7392796</v>
+        <v>7393053</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8638,32 +8640,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128685847</v>
+        <v>128685756</v>
       </c>
       <c r="B84" t="n">
-        <v>92887</v>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8673,10 +8675,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>810944</v>
+        <v>811013</v>
       </c>
       <c r="R84" t="n">
-        <v>7392948</v>
+        <v>7393006</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8735,10 +8737,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128685748</v>
+        <v>128685758</v>
       </c>
       <c r="B85" t="n">
-        <v>79706</v>
+        <v>79946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8770,10 +8772,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>810767</v>
+        <v>810717</v>
       </c>
       <c r="R85" t="n">
-        <v>7392968</v>
+        <v>7393072</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8832,32 +8834,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128685860</v>
+        <v>128685774</v>
       </c>
       <c r="B86" t="n">
-        <v>92887</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8867,10 +8869,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811528</v>
+        <v>811337</v>
       </c>
       <c r="R86" t="n">
-        <v>7393160</v>
+        <v>7392854</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8903,6 +8905,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8929,10 +8936,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128685749</v>
+        <v>128685776</v>
       </c>
       <c r="B87" t="n">
-        <v>79706</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8940,21 +8947,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8964,10 +8971,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811061</v>
+        <v>810803</v>
       </c>
       <c r="R87" t="n">
-        <v>7392880</v>
+        <v>7392998</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9026,10 +9033,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128685825</v>
+        <v>128685777</v>
       </c>
       <c r="B88" t="n">
-        <v>78844</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9037,21 +9044,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9061,10 +9068,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>810871</v>
+        <v>811015</v>
       </c>
       <c r="R88" t="n">
-        <v>7392966</v>
+        <v>7392800</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9123,10 +9130,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128685764</v>
+        <v>128685778</v>
       </c>
       <c r="B89" t="n">
-        <v>87036</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9134,21 +9141,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9158,10 +9165,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>810867</v>
+        <v>811517</v>
       </c>
       <c r="R89" t="n">
-        <v>7392967</v>
+        <v>7393148</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9220,10 +9227,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128685763</v>
+        <v>128685780</v>
       </c>
       <c r="B90" t="n">
-        <v>87036</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9231,21 +9238,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3690</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9255,10 +9262,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811097</v>
+        <v>811531</v>
       </c>
       <c r="R90" t="n">
-        <v>7392723</v>
+        <v>7393153</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9299,7 +9306,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9318,32 +9324,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128685801</v>
+        <v>128685781</v>
       </c>
       <c r="B91" t="n">
-        <v>92899</v>
+        <v>57953</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9353,10 +9359,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811116</v>
+        <v>811507</v>
       </c>
       <c r="R91" t="n">
-        <v>7392980</v>
+        <v>7393120</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9415,32 +9421,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128685852</v>
+        <v>128685783</v>
       </c>
       <c r="B92" t="n">
-        <v>92887</v>
+        <v>57953</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9450,10 +9456,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811057</v>
+        <v>811497</v>
       </c>
       <c r="R92" t="n">
-        <v>7392877</v>
+        <v>7393112</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9512,32 +9518,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128685796</v>
+        <v>128685785</v>
       </c>
       <c r="B93" t="n">
-        <v>92918</v>
+        <v>57953</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>232140</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9547,10 +9553,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>810795</v>
+        <v>811518</v>
       </c>
       <c r="R93" t="n">
-        <v>7393042</v>
+        <v>7393070</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9609,10 +9615,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128685770</v>
+        <v>128685786</v>
       </c>
       <c r="B94" t="n">
-        <v>87036</v>
+        <v>57953</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9620,21 +9626,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3690</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9644,10 +9650,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811050</v>
+        <v>811340</v>
       </c>
       <c r="R94" t="n">
-        <v>7393050</v>
+        <v>7392845</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9682,18 +9688,12 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9712,10 +9712,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128685751</v>
+        <v>128685787</v>
       </c>
       <c r="B95" t="n">
-        <v>79706</v>
+        <v>57953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9723,21 +9723,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9747,10 +9747,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811254</v>
+        <v>811205</v>
       </c>
       <c r="R95" t="n">
-        <v>7392831</v>
+        <v>7392938</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -9809,32 +9809,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128685849</v>
+        <v>128685788</v>
       </c>
       <c r="B96" t="n">
-        <v>92887</v>
+        <v>57953</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810964</v>
+        <v>811107</v>
       </c>
       <c r="R96" t="n">
-        <v>7392920</v>
+        <v>7393022</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9906,10 +9906,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128685863</v>
+        <v>128685790</v>
       </c>
       <c r="B97" t="n">
-        <v>92887</v>
+        <v>57141</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9917,21 +9917,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>810854</v>
+        <v>810977</v>
       </c>
       <c r="R97" t="n">
-        <v>7393015</v>
+        <v>7393016</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -9977,6 +9977,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Gammal spelspillning.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10003,32 +10008,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128685834</v>
+        <v>128685791</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>57141</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10038,10 +10043,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811525</v>
+        <v>811007</v>
       </c>
       <c r="R98" t="n">
-        <v>7393139</v>
+        <v>7392841</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10097,6 +10102,782 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128685823</v>
+      </c>
+      <c r="B99" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>811127</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7392976</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128685822</v>
+      </c>
+      <c r="B100" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>810901</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7393040</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128685814</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>810773</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7392966</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128685815</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>810946</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7392983</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128685816</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>810920</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7393003</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128685760</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>810920</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7393003</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128685796</v>
+      </c>
+      <c r="B105" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>810795</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7393042</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128685794</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Norra Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>810772</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7392959</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
